--- a/site/nb_leads.xlsx
+++ b/site/nb_leads.xlsx
@@ -570,11 +570,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sloop Cove</t>
+          <t>Shin Creek</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
@@ -585,7 +585,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Ag, Mo, W</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -627,14 +627,14 @@
         <v>45</v>
       </c>
       <c r="V2" t="n">
-        <v>44.68722</v>
+        <v>45.55224</v>
       </c>
       <c r="W2" t="n">
-        <v>-66.87302</v>
+        <v>-66.63357999999999</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=31</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=8</t>
         </is>
       </c>
     </row>
@@ -644,11 +644,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Quispamsis</t>
+          <t>Evandale Stock *</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -659,7 +659,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ag, Au, Cu, Pb, Zn</t>
+          <t>Ag, Au, Cu</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -701,14 +701,14 @@
         <v>45</v>
       </c>
       <c r="V3" t="n">
-        <v>45.42362</v>
+        <v>45.58501</v>
       </c>
       <c r="W3" t="n">
-        <v>-65.95802</v>
+        <v>-66.09690999999999</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=4</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=11</t>
         </is>
       </c>
     </row>
@@ -718,11 +718,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Melanson Brook E</t>
+          <t>Quispamsis</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1026</v>
+        <v>4</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -733,7 +733,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ag, Pb, Zn</t>
+          <t>Ag, Au, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -775,14 +775,14 @@
         <v>45</v>
       </c>
       <c r="V4" t="n">
-        <v>47.73447</v>
+        <v>45.42362</v>
       </c>
       <c r="W4" t="n">
-        <v>-65.98719</v>
+        <v>-65.95802</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1026</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=4</t>
         </is>
       </c>
     </row>
@@ -792,11 +792,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nigadoo 8</t>
+          <t>Pender Brook</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1028</v>
+        <v>10</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -807,7 +807,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ag, Au, Pb, Zn</t>
+          <t>Sb</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -840,23 +840,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T5" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U5" t="n">
         <v>45</v>
       </c>
       <c r="V5" t="n">
-        <v>47.74616</v>
+        <v>45.57888</v>
       </c>
       <c r="W5" t="n">
-        <v>-65.88711000000001</v>
+        <v>-66.30664</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1028</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=10</t>
         </is>
       </c>
     </row>
@@ -866,11 +866,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Antinouri Lake West B</t>
+          <t>Taylor Village</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1021</v>
+        <v>57</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -881,7 +881,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pb, Zn</t>
+          <t>Ti</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -923,14 +923,14 @@
         <v>45</v>
       </c>
       <c r="V6" t="n">
-        <v>47.78921</v>
+        <v>45.93834</v>
       </c>
       <c r="W6" t="n">
-        <v>-65.99773</v>
+        <v>-64.55385</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1021</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=57</t>
         </is>
       </c>
     </row>
@@ -940,11 +940,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Payne Brook</t>
+          <t>Quisibis Mountain</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1036</v>
+        <v>58</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -955,7 +955,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ag, Pb, Zn</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -997,14 +997,14 @@
         <v>45</v>
       </c>
       <c r="V7" t="n">
-        <v>47.74032</v>
+        <v>47.42337</v>
       </c>
       <c r="W7" t="n">
-        <v>-65.91246</v>
+        <v>-67.96913000000001</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1036</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=58</t>
         </is>
       </c>
     </row>
@@ -1014,11 +1014,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Belledune Pond</t>
+          <t>Levesque Gulch</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>72</v>
+        <v>1115</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ag, Cu, Pb, Zn</t>
+          <t>Au, Cu, Sb</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1062,23 +1062,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T8" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U8" t="n">
         <v>45</v>
       </c>
       <c r="V8" t="n">
-        <v>47.82638</v>
+        <v>47.6649</v>
       </c>
       <c r="W8" t="n">
-        <v>-65.97922</v>
+        <v>-66.69267000000001</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=72</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1115</t>
         </is>
       </c>
     </row>
@@ -1088,11 +1088,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>St. Leonard Iron-Manganese</t>
+          <t>Antinouri Lake West A</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Ag, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1145,14 +1145,14 @@
         <v>45</v>
       </c>
       <c r="V9" t="n">
-        <v>47.2053</v>
+        <v>47.78952</v>
       </c>
       <c r="W9" t="n">
-        <v>-67.88663</v>
+        <v>-65.98515</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=101</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=85</t>
         </is>
       </c>
     </row>
@@ -1236,11 +1236,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Antinouri Lake West A</t>
+          <t>St. Leonard Iron-Manganese</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ag, Cu, Pb, Zn</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1293,14 +1293,14 @@
         <v>45</v>
       </c>
       <c r="V11" t="n">
-        <v>47.78952</v>
+        <v>47.2053</v>
       </c>
       <c r="W11" t="n">
-        <v>-65.98515</v>
+        <v>-67.88663</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=85</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=101</t>
         </is>
       </c>
     </row>
@@ -1310,11 +1310,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Levesque Gulch</t>
+          <t>Belledune Pond</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1115</v>
+        <v>72</v>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Au, Cu, Sb</t>
+          <t>Ag, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1358,23 +1358,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T12" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U12" t="n">
         <v>45</v>
       </c>
       <c r="V12" t="n">
-        <v>47.6649</v>
+        <v>47.82638</v>
       </c>
       <c r="W12" t="n">
-        <v>-66.69267000000001</v>
+        <v>-65.97922</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1115</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=72</t>
         </is>
       </c>
     </row>
@@ -1384,11 +1384,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Gordon Meadow Brook East</t>
+          <t>Red Pine Brook</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1252</v>
+        <v>1408</v>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ag, Pb, Zn</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1441,14 +1441,14 @@
         <v>45</v>
       </c>
       <c r="V13" t="n">
-        <v>47.39279</v>
+        <v>47.4492</v>
       </c>
       <c r="W13" t="n">
-        <v>-65.68568999999999</v>
+        <v>-65.62412999999999</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1252</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1408</t>
         </is>
       </c>
     </row>
@@ -1458,11 +1458,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kenny Lake</t>
+          <t>Little Sevogle River 1</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1278</v>
+        <v>60</v>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pb, Zn</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1506,23 +1506,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T14" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U14" t="n">
         <v>45</v>
       </c>
       <c r="V14" t="n">
-        <v>47.23226</v>
+        <v>47.0005</v>
       </c>
       <c r="W14" t="n">
-        <v>-66.2908</v>
+        <v>-65.98999999999999</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1278</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=60</t>
         </is>
       </c>
     </row>
@@ -1532,11 +1532,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Green Creek North</t>
+          <t>Peekaboo Corner *</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1334</v>
+        <v>27</v>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
@@ -1589,14 +1589,14 @@
         <v>45</v>
       </c>
       <c r="V15" t="n">
-        <v>45.79059</v>
+        <v>45.65473</v>
       </c>
       <c r="W15" t="n">
-        <v>-64.44385</v>
+        <v>-65.71941</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1334</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=27</t>
         </is>
       </c>
     </row>
@@ -1606,11 +1606,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Peekaboo Corner *</t>
+          <t>Gordon Meadow Brook East</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>27</v>
+        <v>1252</v>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Ag, Pb, Zn</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1663,14 +1663,14 @@
         <v>45</v>
       </c>
       <c r="V16" t="n">
-        <v>45.65473</v>
+        <v>47.39279</v>
       </c>
       <c r="W16" t="n">
-        <v>-65.71941</v>
+        <v>-65.68568999999999</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=27</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1252</t>
         </is>
       </c>
     </row>
@@ -1680,11 +1680,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Shin Creek</t>
+          <t>Nigadoo 8</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>1028</v>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ag, Mo, W</t>
+          <t>Ag, Au, Pb, Zn</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1728,23 +1728,23 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T17" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U17" t="n">
         <v>45</v>
       </c>
       <c r="V17" t="n">
-        <v>45.55224</v>
+        <v>47.74616</v>
       </c>
       <c r="W17" t="n">
-        <v>-66.63357999999999</v>
+        <v>-65.88711000000001</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=8</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1028</t>
         </is>
       </c>
     </row>
@@ -1754,11 +1754,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Quisibis Mountain</t>
+          <t>Melanson Brook E</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>58</v>
+        <v>1026</v>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Ag, Pb, Zn</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1811,14 +1811,14 @@
         <v>45</v>
       </c>
       <c r="V18" t="n">
-        <v>47.42337</v>
+        <v>47.73447</v>
       </c>
       <c r="W18" t="n">
-        <v>-67.96913000000001</v>
+        <v>-65.98719</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=58</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1026</t>
         </is>
       </c>
     </row>
@@ -1828,11 +1828,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Little Sevogle River 1</t>
+          <t>Antinouri Lake West B</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>1021</v>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Pb, Zn</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1885,14 +1885,14 @@
         <v>45</v>
       </c>
       <c r="V19" t="n">
-        <v>47.0005</v>
+        <v>47.78921</v>
       </c>
       <c r="W19" t="n">
-        <v>-65.98999999999999</v>
+        <v>-65.99773</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=60</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1021</t>
         </is>
       </c>
     </row>
@@ -1902,11 +1902,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Taylor Village</t>
+          <t>Kenny Lake</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>57</v>
+        <v>1278</v>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ti</t>
+          <t>Pb, Zn</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1950,23 +1950,23 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T20" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U20" t="n">
         <v>45</v>
       </c>
       <c r="V20" t="n">
-        <v>45.93834</v>
+        <v>47.23226</v>
       </c>
       <c r="W20" t="n">
-        <v>-64.55385</v>
+        <v>-66.2908</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=57</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1278</t>
         </is>
       </c>
     </row>
@@ -1976,11 +1976,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>South Glassville</t>
+          <t>Sloop Cove</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1504</v>
+        <v>31</v>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2033,14 +2033,14 @@
         <v>45</v>
       </c>
       <c r="V21" t="n">
-        <v>46.48057</v>
+        <v>44.68722</v>
       </c>
       <c r="W21" t="n">
-        <v>-67.42028000000001</v>
+        <v>-66.87302</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1504</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=31</t>
         </is>
       </c>
     </row>
@@ -2050,11 +2050,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Red Pine Brook</t>
+          <t>South Glassville</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1408</v>
+        <v>1504</v>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2107,14 +2107,14 @@
         <v>45</v>
       </c>
       <c r="V22" t="n">
-        <v>47.4492</v>
+        <v>46.48057</v>
       </c>
       <c r="W22" t="n">
-        <v>-65.62412999999999</v>
+        <v>-67.42028000000001</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1408</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1504</t>
         </is>
       </c>
     </row>
@@ -2124,11 +2124,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pender Brook</t>
+          <t>Green Creek North</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>10</v>
+        <v>1334</v>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sb</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2181,14 +2181,14 @@
         <v>45</v>
       </c>
       <c r="V23" t="n">
-        <v>45.57888</v>
+        <v>45.79059</v>
       </c>
       <c r="W23" t="n">
-        <v>-66.30664</v>
+        <v>-64.44385</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=10</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1334</t>
         </is>
       </c>
     </row>
@@ -2198,11 +2198,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Evandale Stock *</t>
+          <t>Payne Brook</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>11</v>
+        <v>1036</v>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ag, Au, Cu</t>
+          <t>Ag, Pb, Zn</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2255,14 +2255,14 @@
         <v>45</v>
       </c>
       <c r="V24" t="n">
-        <v>45.58501</v>
+        <v>47.74032</v>
       </c>
       <c r="W24" t="n">
-        <v>-66.09690999999999</v>
+        <v>-65.91246</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=11</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1036</t>
         </is>
       </c>
     </row>
@@ -2272,11 +2272,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Joliffs Brook</t>
+          <t>Hayward Pinnacle</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>555</v>
+        <v>1575</v>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Zn</t>
+          <t>U</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2329,14 +2329,14 @@
         <v>43</v>
       </c>
       <c r="V25" t="n">
-        <v>45.73919</v>
+        <v>45.82761</v>
       </c>
       <c r="W25" t="n">
-        <v>-65.75996000000001</v>
+        <v>-64.9164</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=555</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1575</t>
         </is>
       </c>
     </row>
@@ -2346,11 +2346,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Martins Bluff</t>
+          <t>Crory Farm</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>562</v>
+        <v>605</v>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
@@ -2359,7 +2359,11 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Cu, Pb, Zn</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -2399,14 +2403,14 @@
         <v>43</v>
       </c>
       <c r="V26" t="n">
-        <v>46.93142</v>
+        <v>45.08058</v>
       </c>
       <c r="W26" t="n">
-        <v>-66.64663</v>
+        <v>-66.80913</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=562</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=605</t>
         </is>
       </c>
     </row>
@@ -2416,11 +2420,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ragged Falls &amp;quot;I&amp;quot;</t>
+          <t>Tennants Cove *</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>570</v>
+        <v>372</v>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
@@ -2431,7 +2435,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Th, U</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2464,23 +2468,23 @@
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T27" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U27" t="n">
         <v>43</v>
       </c>
       <c r="V27" t="n">
-        <v>45.2353</v>
+        <v>45.58694</v>
       </c>
       <c r="W27" t="n">
-        <v>-66.48052</v>
+        <v>-66.01414</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=570</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=372</t>
         </is>
       </c>
     </row>
@@ -2490,11 +2494,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Crory Farm</t>
+          <t>Ragged Falls &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>605</v>
+        <v>570</v>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
@@ -2505,7 +2509,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Th, U</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2538,23 +2542,23 @@
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T28" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U28" t="n">
         <v>43</v>
       </c>
       <c r="V28" t="n">
-        <v>45.08058</v>
+        <v>45.2353</v>
       </c>
       <c r="W28" t="n">
-        <v>-66.80913</v>
+        <v>-66.48052</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=605</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=570</t>
         </is>
       </c>
     </row>
@@ -2564,11 +2568,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Dickson Brook A,B,C</t>
+          <t>Martins Bluff</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>639</v>
+        <v>562</v>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
@@ -2577,11 +2581,7 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Cu</t>
-        </is>
-      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -2621,14 +2621,14 @@
         <v>43</v>
       </c>
       <c r="V29" t="n">
-        <v>45.58364</v>
+        <v>46.93142</v>
       </c>
       <c r="W29" t="n">
-        <v>-64.98524</v>
+        <v>-66.64663</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=639</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=562</t>
         </is>
       </c>
     </row>
@@ -2638,11 +2638,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Three Bridge Brook East *</t>
+          <t>Joliffs Brook</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>793</v>
+        <v>555</v>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ag, Au, Pb, Zn</t>
+          <t>Zn</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2686,23 +2686,23 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T30" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U30" t="n">
         <v>43</v>
       </c>
       <c r="V30" t="n">
-        <v>45.49419</v>
+        <v>45.73919</v>
       </c>
       <c r="W30" t="n">
-        <v>-66.48581</v>
+        <v>-65.75996000000001</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=793</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=555</t>
         </is>
       </c>
     </row>
@@ -2712,11 +2712,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Eel Ground</t>
+          <t>Dickson Brook A,B,C</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>746</v>
+        <v>639</v>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2769,14 +2769,14 @@
         <v>43</v>
       </c>
       <c r="V31" t="n">
-        <v>46.96447</v>
+        <v>45.58364</v>
       </c>
       <c r="W31" t="n">
-        <v>-65.59441</v>
+        <v>-64.98524</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=746</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=639</t>
         </is>
       </c>
     </row>
@@ -2786,11 +2786,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Halls Hill</t>
+          <t>Quaco Road &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1324</v>
+        <v>678</v>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cu, Zn</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2843,14 +2843,14 @@
         <v>43</v>
       </c>
       <c r="V32" t="n">
-        <v>45.96809</v>
+        <v>45.38336</v>
       </c>
       <c r="W32" t="n">
-        <v>-64.16996</v>
+        <v>-65.74996</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1324</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=678</t>
         </is>
       </c>
     </row>
@@ -2860,11 +2860,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Jacquet River M</t>
+          <t>Gowland Mountain *</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>955</v>
+        <v>643</v>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ba, Cu</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2917,14 +2917,14 @@
         <v>43</v>
       </c>
       <c r="V33" t="n">
-        <v>47.82559</v>
+        <v>45.81975</v>
       </c>
       <c r="W33" t="n">
-        <v>-66.01662</v>
+        <v>-65.0483</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=955</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=643</t>
         </is>
       </c>
     </row>
@@ -2934,11 +2934,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Letang Harbour North</t>
+          <t>Deed Brook</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1291</v>
+        <v>717</v>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2982,23 +2982,23 @@
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T34" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U34" t="n">
         <v>43</v>
       </c>
       <c r="V34" t="n">
-        <v>45.08726</v>
+        <v>45.78808</v>
       </c>
       <c r="W34" t="n">
-        <v>-66.7833</v>
+        <v>-64.85692</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1291</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=717</t>
         </is>
       </c>
     </row>
@@ -3008,11 +3008,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Dennis Stream - Upper &amp;quot;I&amp;quot;</t>
+          <t>Irving</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1306</v>
+        <v>1238</v>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
@@ -3021,7 +3021,11 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Co, Cu, Ni</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -3052,23 +3056,23 @@
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T35" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="U35" t="n">
         <v>43</v>
       </c>
       <c r="V35" t="n">
-        <v>45.22199</v>
+        <v>45.19116</v>
       </c>
       <c r="W35" t="n">
-        <v>-67.27109</v>
+        <v>-67.25942000000001</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1306</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1238</t>
         </is>
       </c>
     </row>
@@ -3078,11 +3082,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Gowland Mountain *</t>
+          <t>St Stephen Ni - O Zone &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>643</v>
+        <v>1236</v>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
@@ -3093,7 +3097,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Co, Cu, Ni</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3126,23 +3130,23 @@
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T36" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U36" t="n">
         <v>43</v>
       </c>
       <c r="V36" t="n">
-        <v>45.81975</v>
+        <v>45.23088</v>
       </c>
       <c r="W36" t="n">
-        <v>-65.0483</v>
+        <v>-67.27692</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=643</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1236</t>
         </is>
       </c>
     </row>
@@ -3152,11 +3156,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Quaco Road &amp;quot;I&amp;quot;</t>
+          <t>Memramcook Gold &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>678</v>
+        <v>723</v>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
@@ -3167,7 +3171,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3200,23 +3204,23 @@
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T37" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U37" t="n">
         <v>43</v>
       </c>
       <c r="V37" t="n">
-        <v>45.38336</v>
+        <v>45.96531</v>
       </c>
       <c r="W37" t="n">
-        <v>-65.74996</v>
+        <v>-64.53885</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=678</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=723</t>
         </is>
       </c>
     </row>
@@ -3226,11 +3230,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>St Stephen Ni - O Zone &amp;quot;I&amp;quot;</t>
+          <t>Halls Hill</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1236</v>
+        <v>1324</v>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
@@ -3241,7 +3245,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Co, Cu, Ni</t>
+          <t>Cu, Zn</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3274,23 +3278,23 @@
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T38" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U38" t="n">
         <v>43</v>
       </c>
       <c r="V38" t="n">
-        <v>45.23088</v>
+        <v>45.96809</v>
       </c>
       <c r="W38" t="n">
-        <v>-67.27692</v>
+        <v>-64.16996</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1236</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1324</t>
         </is>
       </c>
     </row>
@@ -3300,11 +3304,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Irving</t>
+          <t>Letang Harbour North</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1238</v>
+        <v>1291</v>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
@@ -3315,7 +3319,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Co, Cu, Ni</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3348,23 +3352,23 @@
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T39" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U39" t="n">
         <v>43</v>
       </c>
       <c r="V39" t="n">
-        <v>45.19116</v>
+        <v>45.08726</v>
       </c>
       <c r="W39" t="n">
-        <v>-67.25942000000001</v>
+        <v>-66.7833</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1238</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1291</t>
         </is>
       </c>
     </row>
@@ -3374,11 +3378,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Pabineau River North Manganese</t>
+          <t>Dennis Stream - Upper &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
@@ -3387,11 +3391,7 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Mn</t>
-        </is>
-      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -3422,23 +3422,23 @@
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T40" t="n">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="U40" t="n">
         <v>43</v>
       </c>
       <c r="V40" t="n">
-        <v>47.49558</v>
+        <v>45.22199</v>
       </c>
       <c r="W40" t="n">
-        <v>-65.90329</v>
+        <v>-67.27109</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1272</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1306</t>
         </is>
       </c>
     </row>
@@ -3448,11 +3448,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Bass River Cu-Ni</t>
+          <t>Jacquet River M</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1254</v>
+        <v>955</v>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cu, Ni</t>
+          <t>Ba, Cu</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3505,14 +3505,14 @@
         <v>43</v>
       </c>
       <c r="V41" t="n">
-        <v>47.46421</v>
+        <v>47.82559</v>
       </c>
       <c r="W41" t="n">
-        <v>-65.56607</v>
+        <v>-66.01662</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1254</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=955</t>
         </is>
       </c>
     </row>
@@ -3522,11 +3522,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Memramcook Gold &amp;quot;I&amp;quot;</t>
+          <t>Eel Ground</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>723</v>
+        <v>746</v>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
@@ -3537,7 +3537,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3570,23 +3570,23 @@
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T42" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U42" t="n">
         <v>43</v>
       </c>
       <c r="V42" t="n">
-        <v>45.96531</v>
+        <v>46.96447</v>
       </c>
       <c r="W42" t="n">
-        <v>-64.53885</v>
+        <v>-65.59441</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=723</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=746</t>
         </is>
       </c>
     </row>
@@ -3596,11 +3596,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Deed Brook</t>
+          <t>Three Bridge Brook East *</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>717</v>
+        <v>793</v>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Ag, Au, Pb, Zn</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3644,23 +3644,23 @@
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T43" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="U43" t="n">
         <v>43</v>
       </c>
       <c r="V43" t="n">
-        <v>45.78808</v>
+        <v>45.49419</v>
       </c>
       <c r="W43" t="n">
-        <v>-64.85692</v>
+        <v>-66.48581</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=717</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=793</t>
         </is>
       </c>
     </row>
@@ -3670,11 +3670,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Hayward Pinnacle</t>
+          <t>Pabineau River North Manganese</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1575</v>
+        <v>1272</v>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3718,23 +3718,23 @@
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T44" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U44" t="n">
         <v>43</v>
       </c>
       <c r="V44" t="n">
-        <v>45.82761</v>
+        <v>47.49558</v>
       </c>
       <c r="W44" t="n">
-        <v>-64.9164</v>
+        <v>-65.90329</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1575</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1272</t>
         </is>
       </c>
     </row>
@@ -3744,11 +3744,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Tennants Cove *</t>
+          <t>Bass River Cu-Ni</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>372</v>
+        <v>1254</v>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Cu, Ni</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3801,14 +3801,14 @@
         <v>43</v>
       </c>
       <c r="V45" t="n">
-        <v>45.58694</v>
+        <v>47.46421</v>
       </c>
       <c r="W45" t="n">
-        <v>-66.01414</v>
+        <v>-65.56607</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=372</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1254</t>
         </is>
       </c>
     </row>
@@ -3892,11 +3892,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Brunswick No. 12</t>
+          <t>Lower Birch Island</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>54</v>
+        <v>172</v>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Ba, Fe, Mn</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>88.8 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -3949,14 +3949,14 @@
         <v>38</v>
       </c>
       <c r="V47" t="n">
-        <v>47.47889</v>
+        <v>46.56864</v>
       </c>
       <c r="W47" t="n">
-        <v>-65.89218</v>
+        <v>-66.57080000000001</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=54</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=172</t>
         </is>
       </c>
     </row>
@@ -3966,11 +3966,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Anomaly 102 &amp;quot;I&amp;quot;</t>
+          <t>Nigadoo River Mine</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1151</v>
+        <v>128</v>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Ag, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>1.1 Mt</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -4023,14 +4023,14 @@
         <v>38</v>
       </c>
       <c r="V48" t="n">
-        <v>46.47865</v>
+        <v>47.73307</v>
       </c>
       <c r="W48" t="n">
-        <v>-66.72996999999999</v>
+        <v>-65.80642</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1151</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=128</t>
         </is>
       </c>
     </row>
@@ -4040,11 +4040,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nigadoo River Mine</t>
+          <t>Austin Brook</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>128</v>
+        <v>69</v>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
@@ -4055,7 +4055,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ag, Cu, Pb, Zn</t>
+          <t>Ag, Fe, Pb, Zn</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>1.1 Mt</t>
+          <t>164 kt</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -4088,23 +4088,23 @@
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T49" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U49" t="n">
         <v>38</v>
       </c>
       <c r="V49" t="n">
-        <v>47.73307</v>
+        <v>47.39779</v>
       </c>
       <c r="W49" t="n">
-        <v>-65.80642</v>
+        <v>-65.82302</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=128</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=69</t>
         </is>
       </c>
     </row>
@@ -4114,11 +4114,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Lower Birch Island</t>
+          <t>Brunswick No. 12</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>172</v>
+        <v>54</v>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ba, Fe, Mn</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>88.8 Mt</t>
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
@@ -4171,14 +4171,14 @@
         <v>38</v>
       </c>
       <c r="V50" t="n">
-        <v>46.56864</v>
+        <v>47.47889</v>
       </c>
       <c r="W50" t="n">
-        <v>-66.57080000000001</v>
+        <v>-65.89218</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=172</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=54</t>
         </is>
       </c>
     </row>
@@ -4188,11 +4188,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Austin Brook</t>
+          <t>Anomaly 102 &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>69</v>
+        <v>1151</v>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ag, Fe, Pb, Zn</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>164 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
@@ -4236,23 +4236,23 @@
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T51" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U51" t="n">
         <v>38</v>
       </c>
       <c r="V51" t="n">
-        <v>47.39779</v>
+        <v>46.47865</v>
       </c>
       <c r="W51" t="n">
-        <v>-65.82302</v>
+        <v>-66.72996999999999</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=69</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1151</t>
         </is>
       </c>
     </row>
@@ -4262,11 +4262,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Taylors Island</t>
+          <t>Black Point</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>32</v>
+        <v>1333</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Pb, Zn</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4315,14 +4315,14 @@
         <v>37</v>
       </c>
       <c r="V52" t="n">
-        <v>45.22336</v>
+        <v>45.79448</v>
       </c>
       <c r="W52" t="n">
-        <v>-66.12747</v>
+        <v>-64.42218</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=32</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1333</t>
         </is>
       </c>
     </row>
@@ -4332,11 +4332,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Henry Lake</t>
+          <t>Jeanne Mance</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1510</v>
+        <v>1249</v>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
@@ -4385,14 +4385,14 @@
         <v>37</v>
       </c>
       <c r="V53" t="n">
-        <v>45.39473</v>
+        <v>47.36337</v>
       </c>
       <c r="W53" t="n">
-        <v>-65.60417</v>
+        <v>-65.44329999999999</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1510</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1249</t>
         </is>
       </c>
     </row>
@@ -4472,11 +4472,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Church Showing</t>
+          <t>Gaspereau River</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>726</v>
+        <v>1300</v>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
@@ -4525,14 +4525,14 @@
         <v>37</v>
       </c>
       <c r="V55" t="n">
-        <v>44.88974</v>
+        <v>46.08059</v>
       </c>
       <c r="W55" t="n">
-        <v>-66.95386000000001</v>
+        <v>-64.20996</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=726</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1300</t>
         </is>
       </c>
     </row>
@@ -4542,11 +4542,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Jeanne Mance</t>
+          <t>Church Showing</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1249</v>
+        <v>726</v>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
@@ -4595,14 +4595,14 @@
         <v>37</v>
       </c>
       <c r="V56" t="n">
-        <v>47.36337</v>
+        <v>44.88974</v>
       </c>
       <c r="W56" t="n">
-        <v>-65.44329999999999</v>
+        <v>-66.95386000000001</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1249</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=726</t>
         </is>
       </c>
     </row>
@@ -4612,11 +4612,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Black Point</t>
+          <t>Basaltic Island West *</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1333</v>
+        <v>1347</v>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
@@ -4665,14 +4665,14 @@
         <v>37</v>
       </c>
       <c r="V57" t="n">
-        <v>45.79448</v>
+        <v>45.1392</v>
       </c>
       <c r="W57" t="n">
-        <v>-64.42218</v>
+        <v>-66.92413999999999</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1333</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1347</t>
         </is>
       </c>
     </row>
@@ -4682,11 +4682,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Quispamsis Exit</t>
+          <t>Grande Anse</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1338</v>
+        <v>1370</v>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ag, Au, Cu, Pb</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4735,14 +4735,14 @@
         <v>37</v>
       </c>
       <c r="V58" t="n">
-        <v>45.42378</v>
+        <v>45.79615</v>
       </c>
       <c r="W58" t="n">
-        <v>-65.92708</v>
+        <v>-64.50107</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1338</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1370</t>
         </is>
       </c>
     </row>
@@ -4752,11 +4752,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Basaltic Island West *</t>
+          <t>Johnson Mills</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1347</v>
+        <v>1371</v>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
@@ -4767,7 +4767,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pb, Zn</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4805,14 +4805,14 @@
         <v>37</v>
       </c>
       <c r="V59" t="n">
-        <v>45.1392</v>
+        <v>45.76365</v>
       </c>
       <c r="W59" t="n">
-        <v>-66.92413999999999</v>
+        <v>-64.52218000000001</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1347</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1371</t>
         </is>
       </c>
     </row>
@@ -4822,11 +4822,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Frye Island North</t>
+          <t>Moores Mills #2</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1353</v>
+        <v>1374</v>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ag, Cu, F, Pb, Sb, Zn</t>
+          <t>Ag, Cu, Pb</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4866,23 +4866,23 @@
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T60" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U60" t="n">
         <v>37</v>
       </c>
       <c r="V60" t="n">
-        <v>45.04753</v>
+        <v>45.29977</v>
       </c>
       <c r="W60" t="n">
-        <v>-66.84469</v>
+        <v>-67.2533</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1353</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1374</t>
         </is>
       </c>
     </row>
@@ -4892,11 +4892,11 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Gaspereau River</t>
+          <t>Scoudouc River Quarry</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1300</v>
+        <v>1367</v>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Pb, Zn</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4945,14 +4945,14 @@
         <v>37</v>
       </c>
       <c r="V61" t="n">
-        <v>46.08059</v>
+        <v>46.19643</v>
       </c>
       <c r="W61" t="n">
-        <v>-64.20996</v>
+        <v>-64.54385000000001</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1300</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1367</t>
         </is>
       </c>
     </row>
@@ -4962,11 +4962,11 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Cape Maringouin # 1</t>
+          <t>Black Point North</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1360</v>
+        <v>1368</v>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
@@ -4977,7 +4977,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cu, Pb</t>
+          <t>Cu, Zn</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5015,14 +5015,14 @@
         <v>37</v>
       </c>
       <c r="V62" t="n">
-        <v>45.73532</v>
+        <v>45.80448</v>
       </c>
       <c r="W62" t="n">
-        <v>-64.54191</v>
+        <v>-64.41634999999999</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1360</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1368</t>
         </is>
       </c>
     </row>
@@ -5032,11 +5032,11 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Cape Maringouin # 2</t>
+          <t>Shediac River # 2</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
@@ -5047,7 +5047,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ag, Cu, Pb, Zn</t>
+          <t>As</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5085,14 +5085,14 @@
         <v>37</v>
       </c>
       <c r="V63" t="n">
-        <v>45.73782</v>
+        <v>46.2417</v>
       </c>
       <c r="W63" t="n">
-        <v>-64.53246</v>
+        <v>-64.6858</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1361</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1365</t>
         </is>
       </c>
     </row>
@@ -5102,11 +5102,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Digdeguash Cu *</t>
+          <t>Rockport Shore</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1344</v>
+        <v>1362</v>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cu, Zn</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5155,14 +5155,14 @@
         <v>37</v>
       </c>
       <c r="V64" t="n">
-        <v>45.18698</v>
+        <v>45.72365</v>
       </c>
       <c r="W64" t="n">
-        <v>-66.93774999999999</v>
+        <v>-64.50663</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1344</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1362</t>
         </is>
       </c>
     </row>
@@ -5172,11 +5172,11 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Rockport Shore</t>
+          <t>Cape Maringouin # 2</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Ag, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5225,14 +5225,14 @@
         <v>37</v>
       </c>
       <c r="V65" t="n">
-        <v>45.72365</v>
+        <v>45.73782</v>
       </c>
       <c r="W65" t="n">
-        <v>-64.50663</v>
+        <v>-64.53246</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1362</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1361</t>
         </is>
       </c>
     </row>
@@ -5242,11 +5242,11 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Black Point North</t>
+          <t>Cape Maringouin # 1</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1368</v>
+        <v>1360</v>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
@@ -5257,7 +5257,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cu, Zn</t>
+          <t>Cu, Pb</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5295,14 +5295,14 @@
         <v>37</v>
       </c>
       <c r="V66" t="n">
-        <v>45.80448</v>
+        <v>45.73532</v>
       </c>
       <c r="W66" t="n">
-        <v>-64.41634999999999</v>
+        <v>-64.54191</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1368</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1360</t>
         </is>
       </c>
     </row>
@@ -5312,11 +5312,11 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Grande Anse</t>
+          <t>Frye Island North</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1370</v>
+        <v>1353</v>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
@@ -5327,7 +5327,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Ag, Cu, F, Pb, Sb, Zn</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5365,14 +5365,14 @@
         <v>37</v>
       </c>
       <c r="V67" t="n">
-        <v>45.79615</v>
+        <v>45.04753</v>
       </c>
       <c r="W67" t="n">
-        <v>-64.50107</v>
+        <v>-66.84469</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1370</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1353</t>
         </is>
       </c>
     </row>
@@ -5382,11 +5382,11 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Sinclair Hill</t>
+          <t>Quispamsis Exit</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>9</v>
+        <v>1338</v>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ag, Au, Cu</t>
+          <t>Ag, Au, Cu, Pb</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5435,14 +5435,14 @@
         <v>37</v>
       </c>
       <c r="V68" t="n">
-        <v>45.63113</v>
+        <v>45.42378</v>
       </c>
       <c r="W68" t="n">
-        <v>-64.92274999999999</v>
+        <v>-65.92708</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=9</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1338</t>
         </is>
       </c>
     </row>
@@ -5452,11 +5452,11 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Scoudouc River Quarry</t>
+          <t>Digdeguash Cu *</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1367</v>
+        <v>1344</v>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
@@ -5467,7 +5467,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pb, Zn</t>
+          <t>Cu, Zn</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5505,14 +5505,14 @@
         <v>37</v>
       </c>
       <c r="V69" t="n">
-        <v>46.19643</v>
+        <v>45.18698</v>
       </c>
       <c r="W69" t="n">
-        <v>-64.54385000000001</v>
+        <v>-66.93774999999999</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1367</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1344</t>
         </is>
       </c>
     </row>
@@ -5522,11 +5522,11 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Shediac River # 2</t>
+          <t>Sinclair Hill</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1365</v>
+        <v>9</v>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
@@ -5537,7 +5537,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>As</t>
+          <t>Ag, Au, Cu</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5575,14 +5575,14 @@
         <v>37</v>
       </c>
       <c r="V70" t="n">
-        <v>46.2417</v>
+        <v>45.63113</v>
       </c>
       <c r="W70" t="n">
-        <v>-64.6858</v>
+        <v>-64.92274999999999</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1365</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=9</t>
         </is>
       </c>
     </row>
@@ -5592,11 +5592,11 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Johnson Mills</t>
+          <t>Taylors Island</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1371</v>
+        <v>32</v>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5645,14 +5645,14 @@
         <v>37</v>
       </c>
       <c r="V71" t="n">
-        <v>45.76365</v>
+        <v>45.22336</v>
       </c>
       <c r="W71" t="n">
-        <v>-64.52218000000001</v>
+        <v>-66.12747</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1371</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=32</t>
         </is>
       </c>
     </row>
@@ -5662,11 +5662,11 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Moores Mills #2</t>
+          <t>Henry Lake</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1374</v>
+        <v>1510</v>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
@@ -5677,7 +5677,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ag, Cu, Pb</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5706,23 +5706,23 @@
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T72" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U72" t="n">
         <v>37</v>
       </c>
       <c r="V72" t="n">
-        <v>45.29977</v>
+        <v>45.39473</v>
       </c>
       <c r="W72" t="n">
-        <v>-67.2533</v>
+        <v>-65.60417</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1374</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1510</t>
         </is>
       </c>
     </row>
@@ -5802,11 +5802,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Jacquet River Cu - A</t>
+          <t>Four Mile Lake B</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>462</v>
+        <v>1175</v>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
@@ -5815,11 +5815,7 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Cu</t>
-        </is>
-      </c>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -5855,14 +5851,14 @@
         <v>35</v>
       </c>
       <c r="V74" t="n">
-        <v>47.85476</v>
+        <v>46.63643</v>
       </c>
       <c r="W74" t="n">
-        <v>-66.01551000000001</v>
+        <v>-66.58274</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=462</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1175</t>
         </is>
       </c>
     </row>
@@ -5872,11 +5868,11 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Brewers Mills</t>
+          <t>Caledonia Mountain</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>904</v>
+        <v>1609</v>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
@@ -5887,7 +5883,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>As, Au</t>
+          <t>Ti, V</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5916,23 +5912,23 @@
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T75" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U75" t="n">
         <v>35</v>
       </c>
       <c r="V75" t="n">
-        <v>46.0692</v>
+        <v>45.8698</v>
       </c>
       <c r="W75" t="n">
-        <v>-67.0283</v>
+        <v>-64.73159</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=904</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1609</t>
         </is>
       </c>
     </row>
@@ -5942,11 +5938,11 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Jacquet River K</t>
+          <t>Jacquet River Cu - Mitchell Rd</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>973</v>
+        <v>461</v>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr"/>
@@ -5991,14 +5987,14 @@
         <v>35</v>
       </c>
       <c r="V76" t="n">
-        <v>47.83142</v>
+        <v>47.82725</v>
       </c>
       <c r="W76" t="n">
-        <v>-66.03246</v>
+        <v>-66.00606999999999</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=973</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=461</t>
         </is>
       </c>
     </row>
@@ -6008,11 +6004,11 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Caledonia Mountain</t>
+          <t>Jacquet River Cu - A</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1609</v>
+        <v>462</v>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
@@ -6023,7 +6019,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ti, V</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6052,23 +6048,23 @@
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T77" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U77" t="n">
         <v>35</v>
       </c>
       <c r="V77" t="n">
-        <v>45.8698</v>
+        <v>47.85476</v>
       </c>
       <c r="W77" t="n">
-        <v>-64.73159</v>
+        <v>-66.01551000000001</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1609</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=462</t>
         </is>
       </c>
     </row>
@@ -6078,11 +6074,11 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Centreville &amp;quot;I&amp;quot;</t>
+          <t>Dumfries *</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>263</v>
+        <v>535</v>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
@@ -6093,7 +6089,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -6131,14 +6127,14 @@
         <v>35</v>
       </c>
       <c r="V78" t="n">
-        <v>46.44281</v>
+        <v>45.95029</v>
       </c>
       <c r="W78" t="n">
-        <v>-67.6808</v>
+        <v>-67.12273999999999</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=263</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=535</t>
         </is>
       </c>
     </row>
@@ -6148,11 +6144,11 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Waterville Prospect &amp;quot;I&amp;quot;</t>
+          <t>Letete Mine</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1413</v>
+        <v>311</v>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
@@ -6163,12 +6159,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Au, Sb</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I79" t="b">
@@ -6179,11 +6175,15 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>1.9 Mt</t>
         </is>
       </c>
       <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="n">
         <v>0</v>
@@ -6192,23 +6192,23 @@
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T79" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U79" t="n">
         <v>35</v>
       </c>
       <c r="V79" t="n">
-        <v>46.05921</v>
+        <v>45.06529</v>
       </c>
       <c r="W79" t="n">
-        <v>-67.30663</v>
+        <v>-66.91136</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1413</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=311</t>
         </is>
       </c>
     </row>
@@ -6218,11 +6218,11 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Indian Brook</t>
+          <t>Silver Island</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>262</v>
+        <v>586</v>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
@@ -6231,7 +6231,11 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Ag, Pb, Zn</t>
+        </is>
+      </c>
       <c r="H80" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -6267,14 +6271,14 @@
         <v>35</v>
       </c>
       <c r="V80" t="n">
-        <v>46.73226</v>
+        <v>45.12114</v>
       </c>
       <c r="W80" t="n">
-        <v>-67.42440999999999</v>
+        <v>-66.8458</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=262</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=586</t>
         </is>
       </c>
     </row>
@@ -6284,11 +6288,11 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Brummagen Brook Bog</t>
+          <t>Forty Five River &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>188</v>
+        <v>647</v>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
@@ -6299,7 +6303,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -6328,23 +6332,23 @@
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T81" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U81" t="n">
         <v>35</v>
       </c>
       <c r="V81" t="n">
-        <v>46.39003</v>
+        <v>45.74309</v>
       </c>
       <c r="W81" t="n">
-        <v>-67.29386</v>
+        <v>-64.93053</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=188</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=647</t>
         </is>
       </c>
     </row>
@@ -6354,11 +6358,11 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Pecks Point South</t>
+          <t>Phyllis Creek &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1329</v>
+        <v>655</v>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
@@ -6369,7 +6373,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ag, Cu, Pb, Zn</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -6407,14 +6411,14 @@
         <v>35</v>
       </c>
       <c r="V82" t="n">
-        <v>45.73809</v>
+        <v>45.94808</v>
       </c>
       <c r="W82" t="n">
-        <v>-64.48524</v>
+        <v>-66.69441</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1329</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=655</t>
         </is>
       </c>
     </row>
@@ -6424,11 +6428,11 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Dumfries *</t>
+          <t>Pirate Lake</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>535</v>
+        <v>516</v>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
@@ -6439,7 +6443,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -6477,14 +6481,14 @@
         <v>35</v>
       </c>
       <c r="V83" t="n">
-        <v>45.95029</v>
+        <v>45.72697</v>
       </c>
       <c r="W83" t="n">
-        <v>-67.12273999999999</v>
+        <v>-67.67525000000001</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=535</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=516</t>
         </is>
       </c>
     </row>
@@ -6494,11 +6498,11 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Pirate Lake</t>
+          <t>Pecks Point South</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>516</v>
+        <v>1329</v>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
@@ -6509,7 +6513,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Ag, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -6547,14 +6551,14 @@
         <v>35</v>
       </c>
       <c r="V84" t="n">
-        <v>45.72697</v>
+        <v>45.73809</v>
       </c>
       <c r="W84" t="n">
-        <v>-67.67525000000001</v>
+        <v>-64.48524</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=516</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1329</t>
         </is>
       </c>
     </row>
@@ -6564,11 +6568,11 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Elmtree 7B</t>
+          <t>East Quoddy Head</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>854</v>
+        <v>737</v>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
@@ -6579,7 +6583,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cu, Ni</t>
+          <t>Pb</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -6608,23 +6612,23 @@
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
       <c r="S85" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T85" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U85" t="n">
         <v>35</v>
       </c>
       <c r="V85" t="n">
-        <v>47.78253</v>
+        <v>44.95391</v>
       </c>
       <c r="W85" t="n">
-        <v>-65.87246</v>
+        <v>-66.90831</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=854</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=737</t>
         </is>
       </c>
     </row>
@@ -6634,11 +6638,11 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Four Mile Lake B</t>
+          <t>Meadow Brook Cove</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1175</v>
+        <v>727</v>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
@@ -6647,7 +6651,11 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Fe, Zn</t>
+        </is>
+      </c>
       <c r="H86" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -6683,14 +6691,14 @@
         <v>35</v>
       </c>
       <c r="V86" t="n">
-        <v>46.63643</v>
+        <v>44.88281</v>
       </c>
       <c r="W86" t="n">
-        <v>-66.58274</v>
+        <v>-66.90774999999999</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1175</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=727</t>
         </is>
       </c>
     </row>
@@ -6700,11 +6708,11 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Meadow Brook Cove</t>
+          <t>Jacquet River K</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>727</v>
+        <v>973</v>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
@@ -6713,11 +6721,7 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Fe, Zn</t>
-        </is>
-      </c>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -6753,14 +6757,14 @@
         <v>35</v>
       </c>
       <c r="V87" t="n">
-        <v>44.88281</v>
+        <v>47.83142</v>
       </c>
       <c r="W87" t="n">
-        <v>-66.90774999999999</v>
+        <v>-66.03246</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=727</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=973</t>
         </is>
       </c>
     </row>
@@ -6770,11 +6774,11 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>East Quoddy Head</t>
+          <t>Little Southwest Miramichi</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>737</v>
+        <v>621</v>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
@@ -6783,11 +6787,7 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Pb</t>
-        </is>
-      </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -6823,14 +6823,14 @@
         <v>35</v>
       </c>
       <c r="V88" t="n">
-        <v>44.95391</v>
+        <v>46.89643</v>
       </c>
       <c r="W88" t="n">
-        <v>-66.90831</v>
+        <v>-66.34998</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=737</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=621</t>
         </is>
       </c>
     </row>
@@ -6840,11 +6840,11 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Silver Island</t>
+          <t>Waterside Manganese</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>586</v>
+        <v>645</v>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
@@ -6855,7 +6855,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ag, Pb, Zn</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6884,23 +6884,23 @@
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr"/>
       <c r="S89" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T89" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U89" t="n">
         <v>35</v>
       </c>
       <c r="V89" t="n">
-        <v>45.12114</v>
+        <v>45.63058</v>
       </c>
       <c r="W89" t="n">
-        <v>-66.8458</v>
+        <v>-64.82858</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=586</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=645</t>
         </is>
       </c>
     </row>
@@ -6910,11 +6910,11 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Phyllis Creek &amp;quot;I&amp;quot;</t>
+          <t>Brewers Mills</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>655</v>
+        <v>904</v>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr"/>
@@ -6925,7 +6925,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>As, Au</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6963,14 +6963,14 @@
         <v>35</v>
       </c>
       <c r="V90" t="n">
-        <v>45.94808</v>
+        <v>46.0692</v>
       </c>
       <c r="W90" t="n">
-        <v>-66.69441</v>
+        <v>-67.0283</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=655</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=904</t>
         </is>
       </c>
     </row>
@@ -6980,11 +6980,11 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Jacquet River Cu - Mitchell Rd</t>
+          <t>Elmtree 7B</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>461</v>
+        <v>854</v>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
@@ -6993,7 +6993,11 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Cu, Ni</t>
+        </is>
+      </c>
       <c r="H91" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -7020,23 +7024,23 @@
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr"/>
       <c r="S91" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T91" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U91" t="n">
         <v>35</v>
       </c>
       <c r="V91" t="n">
-        <v>47.82725</v>
+        <v>47.78253</v>
       </c>
       <c r="W91" t="n">
-        <v>-66.00606999999999</v>
+        <v>-65.87246</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=461</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=854</t>
         </is>
       </c>
     </row>
@@ -7046,11 +7050,11 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Maple Ridge</t>
+          <t>MacIntosh Brook</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>152</v>
+        <v>192</v>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr"/>
@@ -7061,7 +7065,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Mo, W</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -7090,23 +7094,23 @@
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr"/>
       <c r="S92" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T92" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U92" t="n">
         <v>35</v>
       </c>
       <c r="V92" t="n">
-        <v>46.10003</v>
+        <v>46.35335</v>
       </c>
       <c r="W92" t="n">
-        <v>-67.21413</v>
+        <v>-67.27636</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=152</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=192</t>
         </is>
       </c>
     </row>
@@ -7116,11 +7120,11 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>MacIntosh Brook</t>
+          <t>Maple Ridge</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>192</v>
+        <v>152</v>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
@@ -7131,7 +7135,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Mo, W</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -7160,23 +7164,23 @@
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr"/>
       <c r="S93" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T93" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U93" t="n">
         <v>35</v>
       </c>
       <c r="V93" t="n">
-        <v>46.35335</v>
+        <v>46.10003</v>
       </c>
       <c r="W93" t="n">
-        <v>-67.27636</v>
+        <v>-67.21413</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=192</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=152</t>
         </is>
       </c>
     </row>
@@ -7186,11 +7190,11 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Letete Mine</t>
+          <t>Indian Brook</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>311</v>
+        <v>262</v>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
@@ -7199,14 +7203,10 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Cu</t>
-        </is>
-      </c>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I94" t="b">
@@ -7217,15 +7217,11 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>1.9 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
+      <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="n">
         <v>0</v>
@@ -7234,23 +7230,23 @@
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr"/>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T94" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U94" t="n">
         <v>35</v>
       </c>
       <c r="V94" t="n">
-        <v>45.06529</v>
+        <v>46.73226</v>
       </c>
       <c r="W94" t="n">
-        <v>-66.91136</v>
+        <v>-67.42440999999999</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=311</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=262</t>
         </is>
       </c>
     </row>
@@ -7260,11 +7256,11 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Forty Five River &amp;quot;I&amp;quot;</t>
+          <t>Centreville &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>647</v>
+        <v>263</v>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
@@ -7275,7 +7271,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -7304,23 +7300,23 @@
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="inlineStr"/>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T95" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U95" t="n">
         <v>35</v>
       </c>
       <c r="V95" t="n">
-        <v>45.74309</v>
+        <v>46.44281</v>
       </c>
       <c r="W95" t="n">
-        <v>-64.93053</v>
+        <v>-67.6808</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=647</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=263</t>
         </is>
       </c>
     </row>
@@ -7330,11 +7326,11 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Waterside Manganese</t>
+          <t>Brummagen Brook Bog</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>645</v>
+        <v>188</v>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
@@ -7374,23 +7370,23 @@
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr"/>
       <c r="S96" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T96" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U96" t="n">
         <v>35</v>
       </c>
       <c r="V96" t="n">
-        <v>45.63058</v>
+        <v>46.39003</v>
       </c>
       <c r="W96" t="n">
-        <v>-64.82858</v>
+        <v>-67.29386</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=645</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=188</t>
         </is>
       </c>
     </row>
@@ -7400,11 +7396,11 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Little Southwest Miramichi</t>
+          <t>Waterville Prospect &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>621</v>
+        <v>1413</v>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
@@ -7413,7 +7409,11 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Au, Sb</t>
+        </is>
+      </c>
       <c r="H97" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -7449,14 +7449,14 @@
         <v>35</v>
       </c>
       <c r="V97" t="n">
-        <v>46.89643</v>
+        <v>46.05921</v>
       </c>
       <c r="W97" t="n">
-        <v>-66.34998</v>
+        <v>-67.30663</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=621</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1413</t>
         </is>
       </c>
     </row>
@@ -7466,11 +7466,11 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Shepody Mountain Manganese</t>
+          <t>Meridian Brook Crossing</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>721</v>
+        <v>630</v>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
@@ -7479,11 +7479,7 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>Mn</t>
-        </is>
-      </c>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
           <t>Past Producer</t>
@@ -7510,23 +7506,23 @@
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr"/>
       <c r="S98" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="T98" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="U98" t="n">
         <v>30</v>
       </c>
       <c r="V98" t="n">
-        <v>45.80502</v>
+        <v>47.26747</v>
       </c>
       <c r="W98" t="n">
-        <v>-64.65774</v>
+        <v>-66.68077</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=721</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=630</t>
         </is>
       </c>
     </row>
@@ -7536,11 +7532,11 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>South Hamilton Road</t>
+          <t>Shepody Mountain Manganese</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1412</v>
+        <v>721</v>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr"/>
@@ -7551,7 +7547,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Ag, Au, Cu, Pb, Zn</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -7580,23 +7576,23 @@
       <c r="Q99" t="inlineStr"/>
       <c r="R99" t="inlineStr"/>
       <c r="S99" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T99" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U99" t="n">
         <v>30</v>
       </c>
       <c r="V99" t="n">
-        <v>45.56892</v>
+        <v>45.80502</v>
       </c>
       <c r="W99" t="n">
-        <v>-66.16552</v>
+        <v>-64.65774</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1412</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=721</t>
         </is>
       </c>
     </row>
@@ -7676,11 +7672,11 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Meridian Brook Crossing</t>
+          <t>South Hamilton Road</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>630</v>
+        <v>1412</v>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr"/>
@@ -7689,7 +7685,11 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Ag, Au, Cu, Pb, Zn</t>
+        </is>
+      </c>
       <c r="H101" t="inlineStr">
         <is>
           <t>Past Producer</t>
@@ -7716,23 +7716,23 @@
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr"/>
       <c r="S101" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T101" t="n">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="U101" t="n">
         <v>30</v>
       </c>
       <c r="V101" t="n">
-        <v>47.26747</v>
+        <v>45.56892</v>
       </c>
       <c r="W101" t="n">
-        <v>-66.68077</v>
+        <v>-66.16552</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=630</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1412</t>
         </is>
       </c>
     </row>

--- a/site/nb_leads.xlsx
+++ b/site/nb_leads.xlsx
@@ -570,11 +570,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Shin Creek</t>
+          <t>Sloop Cove</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
@@ -585,7 +585,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ag, Mo, W</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -627,14 +627,14 @@
         <v>45</v>
       </c>
       <c r="V2" t="n">
-        <v>45.55224</v>
+        <v>44.68722</v>
       </c>
       <c r="W2" t="n">
-        <v>-66.63357999999999</v>
+        <v>-66.87302</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=8</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=31</t>
         </is>
       </c>
     </row>
@@ -644,11 +644,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Evandale Stock *</t>
+          <t>Quispamsis</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -659,7 +659,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ag, Au, Cu</t>
+          <t>Ag, Au, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -701,14 +701,14 @@
         <v>45</v>
       </c>
       <c r="V3" t="n">
-        <v>45.58501</v>
+        <v>45.42362</v>
       </c>
       <c r="W3" t="n">
-        <v>-66.09690999999999</v>
+        <v>-65.95802</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=11</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=4</t>
         </is>
       </c>
     </row>
@@ -718,11 +718,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Quispamsis</t>
+          <t>Melanson Brook E</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>1026</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -733,7 +733,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ag, Au, Cu, Pb, Zn</t>
+          <t>Ag, Pb, Zn</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -775,14 +775,14 @@
         <v>45</v>
       </c>
       <c r="V4" t="n">
-        <v>45.42362</v>
+        <v>47.73447</v>
       </c>
       <c r="W4" t="n">
-        <v>-65.95802</v>
+        <v>-65.98719</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=4</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1026</t>
         </is>
       </c>
     </row>
@@ -792,11 +792,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pender Brook</t>
+          <t>Nigadoo 8</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>1028</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -807,7 +807,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sb</t>
+          <t>Ag, Au, Pb, Zn</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -840,23 +840,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T5" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U5" t="n">
         <v>45</v>
       </c>
       <c r="V5" t="n">
-        <v>45.57888</v>
+        <v>47.74616</v>
       </c>
       <c r="W5" t="n">
-        <v>-66.30664</v>
+        <v>-65.88711000000001</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=10</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1028</t>
         </is>
       </c>
     </row>
@@ -866,11 +866,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Taylor Village</t>
+          <t>Antinouri Lake West B</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>57</v>
+        <v>1021</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -881,7 +881,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ti</t>
+          <t>Pb, Zn</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -923,14 +923,14 @@
         <v>45</v>
       </c>
       <c r="V6" t="n">
-        <v>45.93834</v>
+        <v>47.78921</v>
       </c>
       <c r="W6" t="n">
-        <v>-64.55385</v>
+        <v>-65.99773</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=57</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1021</t>
         </is>
       </c>
     </row>
@@ -940,11 +940,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Quisibis Mountain</t>
+          <t>Payne Brook</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>58</v>
+        <v>1036</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -955,7 +955,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Ag, Pb, Zn</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -997,14 +997,14 @@
         <v>45</v>
       </c>
       <c r="V7" t="n">
-        <v>47.42337</v>
+        <v>47.74032</v>
       </c>
       <c r="W7" t="n">
-        <v>-67.96913000000001</v>
+        <v>-65.91246</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=58</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1036</t>
         </is>
       </c>
     </row>
@@ -1014,11 +1014,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Levesque Gulch</t>
+          <t>Belledune Pond</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1115</v>
+        <v>72</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Au, Cu, Sb</t>
+          <t>Ag, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1062,23 +1062,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T8" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U8" t="n">
         <v>45</v>
       </c>
       <c r="V8" t="n">
-        <v>47.6649</v>
+        <v>47.82638</v>
       </c>
       <c r="W8" t="n">
-        <v>-66.69267000000001</v>
+        <v>-65.97922</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1115</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=72</t>
         </is>
       </c>
     </row>
@@ -1088,11 +1088,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Antinouri Lake West A</t>
+          <t>St. Leonard Iron-Manganese</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ag, Cu, Pb, Zn</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1145,14 +1145,14 @@
         <v>45</v>
       </c>
       <c r="V9" t="n">
-        <v>47.78952</v>
+        <v>47.2053</v>
       </c>
       <c r="W9" t="n">
-        <v>-65.98515</v>
+        <v>-67.88663</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=85</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=101</t>
         </is>
       </c>
     </row>
@@ -1236,11 +1236,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>St. Leonard Iron-Manganese</t>
+          <t>Antinouri Lake West A</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Ag, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1293,14 +1293,14 @@
         <v>45</v>
       </c>
       <c r="V11" t="n">
-        <v>47.2053</v>
+        <v>47.78952</v>
       </c>
       <c r="W11" t="n">
-        <v>-67.88663</v>
+        <v>-65.98515</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=101</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=85</t>
         </is>
       </c>
     </row>
@@ -1310,11 +1310,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Belledune Pond</t>
+          <t>Levesque Gulch</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>72</v>
+        <v>1115</v>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ag, Cu, Pb, Zn</t>
+          <t>Au, Cu, Sb</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1358,23 +1358,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T12" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U12" t="n">
         <v>45</v>
       </c>
       <c r="V12" t="n">
-        <v>47.82638</v>
+        <v>47.6649</v>
       </c>
       <c r="W12" t="n">
-        <v>-65.97922</v>
+        <v>-66.69267000000001</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=72</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1115</t>
         </is>
       </c>
     </row>
@@ -1384,11 +1384,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Red Pine Brook</t>
+          <t>Gordon Meadow Brook East</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1408</v>
+        <v>1252</v>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Ag, Pb, Zn</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1441,14 +1441,14 @@
         <v>45</v>
       </c>
       <c r="V13" t="n">
-        <v>47.4492</v>
+        <v>47.39279</v>
       </c>
       <c r="W13" t="n">
-        <v>-65.62412999999999</v>
+        <v>-65.68568999999999</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1408</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1252</t>
         </is>
       </c>
     </row>
@@ -1458,11 +1458,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Little Sevogle River 1</t>
+          <t>Kenny Lake</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>60</v>
+        <v>1278</v>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Pb, Zn</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1506,23 +1506,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T14" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U14" t="n">
         <v>45</v>
       </c>
       <c r="V14" t="n">
-        <v>47.0005</v>
+        <v>47.23226</v>
       </c>
       <c r="W14" t="n">
-        <v>-65.98999999999999</v>
+        <v>-66.2908</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=60</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1278</t>
         </is>
       </c>
     </row>
@@ -1532,11 +1532,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Peekaboo Corner *</t>
+          <t>Green Creek North</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>27</v>
+        <v>1334</v>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
@@ -1589,14 +1589,14 @@
         <v>45</v>
       </c>
       <c r="V15" t="n">
-        <v>45.65473</v>
+        <v>45.79059</v>
       </c>
       <c r="W15" t="n">
-        <v>-65.71941</v>
+        <v>-64.44385</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=27</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1334</t>
         </is>
       </c>
     </row>
@@ -1606,11 +1606,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Gordon Meadow Brook East</t>
+          <t>Peekaboo Corner *</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1252</v>
+        <v>27</v>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ag, Pb, Zn</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1663,14 +1663,14 @@
         <v>45</v>
       </c>
       <c r="V16" t="n">
-        <v>47.39279</v>
+        <v>45.65473</v>
       </c>
       <c r="W16" t="n">
-        <v>-65.68568999999999</v>
+        <v>-65.71941</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1252</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=27</t>
         </is>
       </c>
     </row>
@@ -1680,11 +1680,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nigadoo 8</t>
+          <t>Shin Creek</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1028</v>
+        <v>8</v>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ag, Au, Pb, Zn</t>
+          <t>Ag, Mo, W</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1728,23 +1728,23 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T17" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U17" t="n">
         <v>45</v>
       </c>
       <c r="V17" t="n">
-        <v>47.74616</v>
+        <v>45.55224</v>
       </c>
       <c r="W17" t="n">
-        <v>-65.88711000000001</v>
+        <v>-66.63357999999999</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1028</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=8</t>
         </is>
       </c>
     </row>
@@ -1754,11 +1754,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Melanson Brook E</t>
+          <t>Quisibis Mountain</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1026</v>
+        <v>58</v>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ag, Pb, Zn</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1811,14 +1811,14 @@
         <v>45</v>
       </c>
       <c r="V18" t="n">
-        <v>47.73447</v>
+        <v>47.42337</v>
       </c>
       <c r="W18" t="n">
-        <v>-65.98719</v>
+        <v>-67.96913000000001</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1026</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=58</t>
         </is>
       </c>
     </row>
@@ -1828,11 +1828,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Antinouri Lake West B</t>
+          <t>Little Sevogle River 1</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1021</v>
+        <v>60</v>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pb, Zn</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1885,14 +1885,14 @@
         <v>45</v>
       </c>
       <c r="V19" t="n">
-        <v>47.78921</v>
+        <v>47.0005</v>
       </c>
       <c r="W19" t="n">
-        <v>-65.99773</v>
+        <v>-65.98999999999999</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1021</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=60</t>
         </is>
       </c>
     </row>
@@ -1902,11 +1902,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Kenny Lake</t>
+          <t>Taylor Village</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1278</v>
+        <v>57</v>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pb, Zn</t>
+          <t>Ti</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1950,23 +1950,23 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T20" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U20" t="n">
         <v>45</v>
       </c>
       <c r="V20" t="n">
-        <v>47.23226</v>
+        <v>45.93834</v>
       </c>
       <c r="W20" t="n">
-        <v>-66.2908</v>
+        <v>-64.55385</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1278</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=57</t>
         </is>
       </c>
     </row>
@@ -1976,11 +1976,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sloop Cove</t>
+          <t>South Glassville</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>31</v>
+        <v>1504</v>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2033,14 +2033,14 @@
         <v>45</v>
       </c>
       <c r="V21" t="n">
-        <v>44.68722</v>
+        <v>46.48057</v>
       </c>
       <c r="W21" t="n">
-        <v>-66.87302</v>
+        <v>-67.42028000000001</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=31</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1504</t>
         </is>
       </c>
     </row>
@@ -2050,11 +2050,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>South Glassville</t>
+          <t>Red Pine Brook</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1504</v>
+        <v>1408</v>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2107,14 +2107,14 @@
         <v>45</v>
       </c>
       <c r="V22" t="n">
-        <v>46.48057</v>
+        <v>47.4492</v>
       </c>
       <c r="W22" t="n">
-        <v>-67.42028000000001</v>
+        <v>-65.62412999999999</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1504</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1408</t>
         </is>
       </c>
     </row>
@@ -2124,11 +2124,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Green Creek North</t>
+          <t>Pender Brook</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1334</v>
+        <v>10</v>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Sb</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2181,14 +2181,14 @@
         <v>45</v>
       </c>
       <c r="V23" t="n">
-        <v>45.79059</v>
+        <v>45.57888</v>
       </c>
       <c r="W23" t="n">
-        <v>-64.44385</v>
+        <v>-66.30664</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1334</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=10</t>
         </is>
       </c>
     </row>
@@ -2198,11 +2198,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Payne Brook</t>
+          <t>Evandale Stock *</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1036</v>
+        <v>11</v>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ag, Pb, Zn</t>
+          <t>Ag, Au, Cu</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2255,14 +2255,14 @@
         <v>45</v>
       </c>
       <c r="V24" t="n">
-        <v>47.74032</v>
+        <v>45.58501</v>
       </c>
       <c r="W24" t="n">
-        <v>-65.91246</v>
+        <v>-66.09690999999999</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1036</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=11</t>
         </is>
       </c>
     </row>
@@ -2272,11 +2272,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Hayward Pinnacle</t>
+          <t>Joliffs Brook</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1575</v>
+        <v>555</v>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>Zn</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2329,14 +2329,14 @@
         <v>43</v>
       </c>
       <c r="V25" t="n">
-        <v>45.82761</v>
+        <v>45.73919</v>
       </c>
       <c r="W25" t="n">
-        <v>-64.9164</v>
+        <v>-65.75996000000001</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1575</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=555</t>
         </is>
       </c>
     </row>
@@ -2346,11 +2346,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Crory Farm</t>
+          <t>Martins Bluff</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>605</v>
+        <v>562</v>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
@@ -2359,11 +2359,7 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Cu, Pb, Zn</t>
-        </is>
-      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -2403,14 +2399,14 @@
         <v>43</v>
       </c>
       <c r="V26" t="n">
-        <v>45.08058</v>
+        <v>46.93142</v>
       </c>
       <c r="W26" t="n">
-        <v>-66.80913</v>
+        <v>-66.64663</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=605</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=562</t>
         </is>
       </c>
     </row>
@@ -2420,11 +2416,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Tennants Cove *</t>
+          <t>Ragged Falls &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>372</v>
+        <v>570</v>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
@@ -2435,7 +2431,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Th, U</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2468,23 +2464,23 @@
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T27" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U27" t="n">
         <v>43</v>
       </c>
       <c r="V27" t="n">
-        <v>45.58694</v>
+        <v>45.2353</v>
       </c>
       <c r="W27" t="n">
-        <v>-66.01414</v>
+        <v>-66.48052</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=372</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=570</t>
         </is>
       </c>
     </row>
@@ -2494,11 +2490,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ragged Falls &amp;quot;I&amp;quot;</t>
+          <t>Crory Farm</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>570</v>
+        <v>605</v>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
@@ -2509,7 +2505,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Th, U</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2542,23 +2538,23 @@
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T28" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U28" t="n">
         <v>43</v>
       </c>
       <c r="V28" t="n">
-        <v>45.2353</v>
+        <v>45.08058</v>
       </c>
       <c r="W28" t="n">
-        <v>-66.48052</v>
+        <v>-66.80913</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=570</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=605</t>
         </is>
       </c>
     </row>
@@ -2568,11 +2564,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Martins Bluff</t>
+          <t>Dickson Brook A,B,C</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>562</v>
+        <v>639</v>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
@@ -2581,7 +2577,11 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -2621,14 +2621,14 @@
         <v>43</v>
       </c>
       <c r="V29" t="n">
-        <v>46.93142</v>
+        <v>45.58364</v>
       </c>
       <c r="W29" t="n">
-        <v>-66.64663</v>
+        <v>-64.98524</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=562</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=639</t>
         </is>
       </c>
     </row>
@@ -2638,11 +2638,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Joliffs Brook</t>
+          <t>Three Bridge Brook East *</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>555</v>
+        <v>793</v>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Zn</t>
+          <t>Ag, Au, Pb, Zn</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2686,23 +2686,23 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T30" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U30" t="n">
         <v>43</v>
       </c>
       <c r="V30" t="n">
-        <v>45.73919</v>
+        <v>45.49419</v>
       </c>
       <c r="W30" t="n">
-        <v>-65.75996000000001</v>
+        <v>-66.48581</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=555</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=793</t>
         </is>
       </c>
     </row>
@@ -2712,11 +2712,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Dickson Brook A,B,C</t>
+          <t>Eel Ground</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>639</v>
+        <v>746</v>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2769,14 +2769,14 @@
         <v>43</v>
       </c>
       <c r="V31" t="n">
-        <v>45.58364</v>
+        <v>46.96447</v>
       </c>
       <c r="W31" t="n">
-        <v>-64.98524</v>
+        <v>-65.59441</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=639</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=746</t>
         </is>
       </c>
     </row>
@@ -2786,11 +2786,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Quaco Road &amp;quot;I&amp;quot;</t>
+          <t>Halls Hill</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>678</v>
+        <v>1324</v>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Cu, Zn</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2843,14 +2843,14 @@
         <v>43</v>
       </c>
       <c r="V32" t="n">
-        <v>45.38336</v>
+        <v>45.96809</v>
       </c>
       <c r="W32" t="n">
-        <v>-65.74996</v>
+        <v>-64.16996</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=678</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1324</t>
         </is>
       </c>
     </row>
@@ -2860,11 +2860,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Gowland Mountain *</t>
+          <t>Jacquet River M</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>643</v>
+        <v>955</v>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Ba, Cu</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2917,14 +2917,14 @@
         <v>43</v>
       </c>
       <c r="V33" t="n">
-        <v>45.81975</v>
+        <v>47.82559</v>
       </c>
       <c r="W33" t="n">
-        <v>-65.0483</v>
+        <v>-66.01662</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=643</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=955</t>
         </is>
       </c>
     </row>
@@ -2934,11 +2934,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Deed Brook</t>
+          <t>Letang Harbour North</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>717</v>
+        <v>1291</v>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2982,23 +2982,23 @@
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T34" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U34" t="n">
         <v>43</v>
       </c>
       <c r="V34" t="n">
-        <v>45.78808</v>
+        <v>45.08726</v>
       </c>
       <c r="W34" t="n">
-        <v>-64.85692</v>
+        <v>-66.7833</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=717</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1291</t>
         </is>
       </c>
     </row>
@@ -3008,11 +3008,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Irving</t>
+          <t>Dennis Stream - Upper &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1238</v>
+        <v>1306</v>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
@@ -3021,11 +3021,7 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Co, Cu, Ni</t>
-        </is>
-      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -3056,23 +3052,23 @@
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T35" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="U35" t="n">
         <v>43</v>
       </c>
       <c r="V35" t="n">
-        <v>45.19116</v>
+        <v>45.22199</v>
       </c>
       <c r="W35" t="n">
-        <v>-67.25942000000001</v>
+        <v>-67.27109</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1238</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1306</t>
         </is>
       </c>
     </row>
@@ -3082,11 +3078,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>St Stephen Ni - O Zone &amp;quot;I&amp;quot;</t>
+          <t>Gowland Mountain *</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1236</v>
+        <v>643</v>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
@@ -3097,7 +3093,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Co, Cu, Ni</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3130,23 +3126,23 @@
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T36" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U36" t="n">
         <v>43</v>
       </c>
       <c r="V36" t="n">
-        <v>45.23088</v>
+        <v>45.81975</v>
       </c>
       <c r="W36" t="n">
-        <v>-67.27692</v>
+        <v>-65.0483</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1236</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=643</t>
         </is>
       </c>
     </row>
@@ -3156,11 +3152,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Memramcook Gold &amp;quot;I&amp;quot;</t>
+          <t>Quaco Road &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>723</v>
+        <v>678</v>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
@@ -3171,7 +3167,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3204,23 +3200,23 @@
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T37" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U37" t="n">
         <v>43</v>
       </c>
       <c r="V37" t="n">
-        <v>45.96531</v>
+        <v>45.38336</v>
       </c>
       <c r="W37" t="n">
-        <v>-64.53885</v>
+        <v>-65.74996</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=723</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=678</t>
         </is>
       </c>
     </row>
@@ -3230,11 +3226,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Halls Hill</t>
+          <t>St Stephen Ni - O Zone &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1324</v>
+        <v>1236</v>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
@@ -3245,7 +3241,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cu, Zn</t>
+          <t>Co, Cu, Ni</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3278,23 +3274,23 @@
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T38" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U38" t="n">
         <v>43</v>
       </c>
       <c r="V38" t="n">
-        <v>45.96809</v>
+        <v>45.23088</v>
       </c>
       <c r="W38" t="n">
-        <v>-64.16996</v>
+        <v>-67.27692</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1324</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1236</t>
         </is>
       </c>
     </row>
@@ -3304,11 +3300,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Letang Harbour North</t>
+          <t>Irving</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1291</v>
+        <v>1238</v>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
@@ -3319,7 +3315,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Co, Cu, Ni</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3352,23 +3348,23 @@
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T39" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U39" t="n">
         <v>43</v>
       </c>
       <c r="V39" t="n">
-        <v>45.08726</v>
+        <v>45.19116</v>
       </c>
       <c r="W39" t="n">
-        <v>-66.7833</v>
+        <v>-67.25942000000001</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1291</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1238</t>
         </is>
       </c>
     </row>
@@ -3378,11 +3374,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Dennis Stream - Upper &amp;quot;I&amp;quot;</t>
+          <t>Pabineau River North Manganese</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1306</v>
+        <v>1272</v>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
@@ -3391,7 +3387,11 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Mn</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -3422,23 +3422,23 @@
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T40" t="n">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="U40" t="n">
         <v>43</v>
       </c>
       <c r="V40" t="n">
-        <v>45.22199</v>
+        <v>47.49558</v>
       </c>
       <c r="W40" t="n">
-        <v>-67.27109</v>
+        <v>-65.90329</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1306</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1272</t>
         </is>
       </c>
     </row>
@@ -3448,11 +3448,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Jacquet River M</t>
+          <t>Bass River Cu-Ni</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>955</v>
+        <v>1254</v>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ba, Cu</t>
+          <t>Cu, Ni</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3505,14 +3505,14 @@
         <v>43</v>
       </c>
       <c r="V41" t="n">
-        <v>47.82559</v>
+        <v>47.46421</v>
       </c>
       <c r="W41" t="n">
-        <v>-66.01662</v>
+        <v>-65.56607</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=955</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1254</t>
         </is>
       </c>
     </row>
@@ -3522,11 +3522,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Eel Ground</t>
+          <t>Memramcook Gold &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>746</v>
+        <v>723</v>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
@@ -3537,7 +3537,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3570,23 +3570,23 @@
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T42" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U42" t="n">
         <v>43</v>
       </c>
       <c r="V42" t="n">
-        <v>46.96447</v>
+        <v>45.96531</v>
       </c>
       <c r="W42" t="n">
-        <v>-65.59441</v>
+        <v>-64.53885</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=746</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=723</t>
         </is>
       </c>
     </row>
@@ -3596,11 +3596,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Three Bridge Brook East *</t>
+          <t>Deed Brook</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>793</v>
+        <v>717</v>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ag, Au, Pb, Zn</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3644,23 +3644,23 @@
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T43" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="U43" t="n">
         <v>43</v>
       </c>
       <c r="V43" t="n">
-        <v>45.49419</v>
+        <v>45.78808</v>
       </c>
       <c r="W43" t="n">
-        <v>-66.48581</v>
+        <v>-64.85692</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=793</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=717</t>
         </is>
       </c>
     </row>
@@ -3670,11 +3670,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Pabineau River North Manganese</t>
+          <t>Hayward Pinnacle</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1272</v>
+        <v>1575</v>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>U</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3718,23 +3718,23 @@
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T44" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U44" t="n">
         <v>43</v>
       </c>
       <c r="V44" t="n">
-        <v>47.49558</v>
+        <v>45.82761</v>
       </c>
       <c r="W44" t="n">
-        <v>-65.90329</v>
+        <v>-64.9164</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1272</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1575</t>
         </is>
       </c>
     </row>
@@ -3744,11 +3744,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Bass River Cu-Ni</t>
+          <t>Tennants Cove *</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1254</v>
+        <v>372</v>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cu, Ni</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3801,14 +3801,14 @@
         <v>43</v>
       </c>
       <c r="V45" t="n">
-        <v>47.46421</v>
+        <v>45.58694</v>
       </c>
       <c r="W45" t="n">
-        <v>-65.56607</v>
+        <v>-66.01414</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1254</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=372</t>
         </is>
       </c>
     </row>
@@ -3892,11 +3892,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Lower Birch Island</t>
+          <t>Brunswick No. 12</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>172</v>
+        <v>54</v>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ba, Fe, Mn</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>88.8 Mt</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -3949,14 +3949,14 @@
         <v>38</v>
       </c>
       <c r="V47" t="n">
-        <v>46.56864</v>
+        <v>47.47889</v>
       </c>
       <c r="W47" t="n">
-        <v>-66.57080000000001</v>
+        <v>-65.89218</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=172</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=54</t>
         </is>
       </c>
     </row>
@@ -3966,11 +3966,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nigadoo River Mine</t>
+          <t>Anomaly 102 &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>128</v>
+        <v>1151</v>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ag, Cu, Pb, Zn</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>1.1 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -4023,14 +4023,14 @@
         <v>38</v>
       </c>
       <c r="V48" t="n">
-        <v>47.73307</v>
+        <v>46.47865</v>
       </c>
       <c r="W48" t="n">
-        <v>-65.80642</v>
+        <v>-66.72996999999999</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=128</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1151</t>
         </is>
       </c>
     </row>
@@ -4040,11 +4040,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Austin Brook</t>
+          <t>Nigadoo River Mine</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>69</v>
+        <v>128</v>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
@@ -4055,7 +4055,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ag, Fe, Pb, Zn</t>
+          <t>Ag, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>164 kt</t>
+          <t>1.1 Mt</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -4088,23 +4088,23 @@
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T49" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U49" t="n">
         <v>38</v>
       </c>
       <c r="V49" t="n">
-        <v>47.39779</v>
+        <v>47.73307</v>
       </c>
       <c r="W49" t="n">
-        <v>-65.82302</v>
+        <v>-65.80642</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=69</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=128</t>
         </is>
       </c>
     </row>
@@ -4114,11 +4114,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Brunswick No. 12</t>
+          <t>Lower Birch Island</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>54</v>
+        <v>172</v>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Ba, Fe, Mn</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>88.8 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
@@ -4171,14 +4171,14 @@
         <v>38</v>
       </c>
       <c r="V50" t="n">
-        <v>47.47889</v>
+        <v>46.56864</v>
       </c>
       <c r="W50" t="n">
-        <v>-65.89218</v>
+        <v>-66.57080000000001</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=54</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=172</t>
         </is>
       </c>
     </row>
@@ -4188,11 +4188,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Anomaly 102 &amp;quot;I&amp;quot;</t>
+          <t>Austin Brook</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1151</v>
+        <v>69</v>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Ag, Fe, Pb, Zn</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>164 kt</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
@@ -4236,23 +4236,23 @@
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T51" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U51" t="n">
         <v>38</v>
       </c>
       <c r="V51" t="n">
-        <v>46.47865</v>
+        <v>47.39779</v>
       </c>
       <c r="W51" t="n">
-        <v>-66.72996999999999</v>
+        <v>-65.82302</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1151</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=69</t>
         </is>
       </c>
     </row>
@@ -4262,11 +4262,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Black Point</t>
+          <t>Taylors Island</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1333</v>
+        <v>32</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pb, Zn</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4315,14 +4315,14 @@
         <v>37</v>
       </c>
       <c r="V52" t="n">
-        <v>45.79448</v>
+        <v>45.22336</v>
       </c>
       <c r="W52" t="n">
-        <v>-64.42218</v>
+        <v>-66.12747</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1333</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=32</t>
         </is>
       </c>
     </row>
@@ -4332,11 +4332,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Jeanne Mance</t>
+          <t>Henry Lake</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1249</v>
+        <v>1510</v>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
@@ -4385,14 +4385,14 @@
         <v>37</v>
       </c>
       <c r="V53" t="n">
-        <v>47.36337</v>
+        <v>45.39473</v>
       </c>
       <c r="W53" t="n">
-        <v>-65.44329999999999</v>
+        <v>-65.60417</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1249</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1510</t>
         </is>
       </c>
     </row>
@@ -4472,11 +4472,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Gaspereau River</t>
+          <t>Church Showing</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1300</v>
+        <v>726</v>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
@@ -4525,14 +4525,14 @@
         <v>37</v>
       </c>
       <c r="V55" t="n">
-        <v>46.08059</v>
+        <v>44.88974</v>
       </c>
       <c r="W55" t="n">
-        <v>-64.20996</v>
+        <v>-66.95386000000001</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1300</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=726</t>
         </is>
       </c>
     </row>
@@ -4542,11 +4542,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Church Showing</t>
+          <t>Jeanne Mance</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>726</v>
+        <v>1249</v>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
@@ -4595,14 +4595,14 @@
         <v>37</v>
       </c>
       <c r="V56" t="n">
-        <v>44.88974</v>
+        <v>47.36337</v>
       </c>
       <c r="W56" t="n">
-        <v>-66.95386000000001</v>
+        <v>-65.44329999999999</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=726</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1249</t>
         </is>
       </c>
     </row>
@@ -4612,11 +4612,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Basaltic Island West *</t>
+          <t>Black Point</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1347</v>
+        <v>1333</v>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
@@ -4665,14 +4665,14 @@
         <v>37</v>
       </c>
       <c r="V57" t="n">
-        <v>45.1392</v>
+        <v>45.79448</v>
       </c>
       <c r="W57" t="n">
-        <v>-66.92413999999999</v>
+        <v>-64.42218</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1347</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1333</t>
         </is>
       </c>
     </row>
@@ -4682,11 +4682,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Grande Anse</t>
+          <t>Quispamsis Exit</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1370</v>
+        <v>1338</v>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Ag, Au, Cu, Pb</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4735,14 +4735,14 @@
         <v>37</v>
       </c>
       <c r="V58" t="n">
-        <v>45.79615</v>
+        <v>45.42378</v>
       </c>
       <c r="W58" t="n">
-        <v>-64.50107</v>
+        <v>-65.92708</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1370</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1338</t>
         </is>
       </c>
     </row>
@@ -4752,11 +4752,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Johnson Mills</t>
+          <t>Basaltic Island West *</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1371</v>
+        <v>1347</v>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
@@ -4767,7 +4767,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Pb, Zn</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4805,14 +4805,14 @@
         <v>37</v>
       </c>
       <c r="V59" t="n">
-        <v>45.76365</v>
+        <v>45.1392</v>
       </c>
       <c r="W59" t="n">
-        <v>-64.52218000000001</v>
+        <v>-66.92413999999999</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1371</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1347</t>
         </is>
       </c>
     </row>
@@ -4822,11 +4822,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Moores Mills #2</t>
+          <t>Frye Island North</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1374</v>
+        <v>1353</v>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ag, Cu, Pb</t>
+          <t>Ag, Cu, F, Pb, Sb, Zn</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4866,23 +4866,23 @@
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T60" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U60" t="n">
         <v>37</v>
       </c>
       <c r="V60" t="n">
-        <v>45.29977</v>
+        <v>45.04753</v>
       </c>
       <c r="W60" t="n">
-        <v>-67.2533</v>
+        <v>-66.84469</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1374</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1353</t>
         </is>
       </c>
     </row>
@@ -4892,11 +4892,11 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Scoudouc River Quarry</t>
+          <t>Gaspereau River</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1367</v>
+        <v>1300</v>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pb, Zn</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4945,14 +4945,14 @@
         <v>37</v>
       </c>
       <c r="V61" t="n">
-        <v>46.19643</v>
+        <v>46.08059</v>
       </c>
       <c r="W61" t="n">
-        <v>-64.54385000000001</v>
+        <v>-64.20996</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1367</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1300</t>
         </is>
       </c>
     </row>
@@ -4962,11 +4962,11 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Black Point North</t>
+          <t>Cape Maringouin # 1</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1368</v>
+        <v>1360</v>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
@@ -4977,7 +4977,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cu, Zn</t>
+          <t>Cu, Pb</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5015,14 +5015,14 @@
         <v>37</v>
       </c>
       <c r="V62" t="n">
-        <v>45.80448</v>
+        <v>45.73532</v>
       </c>
       <c r="W62" t="n">
-        <v>-64.41634999999999</v>
+        <v>-64.54191</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1368</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1360</t>
         </is>
       </c>
     </row>
@@ -5032,11 +5032,11 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Shediac River # 2</t>
+          <t>Cape Maringouin # 2</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
@@ -5047,7 +5047,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>As</t>
+          <t>Ag, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5085,14 +5085,14 @@
         <v>37</v>
       </c>
       <c r="V63" t="n">
-        <v>46.2417</v>
+        <v>45.73782</v>
       </c>
       <c r="W63" t="n">
-        <v>-64.6858</v>
+        <v>-64.53246</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1365</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1361</t>
         </is>
       </c>
     </row>
@@ -5102,11 +5102,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Rockport Shore</t>
+          <t>Digdeguash Cu *</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1362</v>
+        <v>1344</v>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Cu, Zn</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5155,14 +5155,14 @@
         <v>37</v>
       </c>
       <c r="V64" t="n">
-        <v>45.72365</v>
+        <v>45.18698</v>
       </c>
       <c r="W64" t="n">
-        <v>-64.50663</v>
+        <v>-66.93774999999999</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1362</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1344</t>
         </is>
       </c>
     </row>
@@ -5172,11 +5172,11 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Cape Maringouin # 2</t>
+          <t>Rockport Shore</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ag, Cu, Pb, Zn</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5225,14 +5225,14 @@
         <v>37</v>
       </c>
       <c r="V65" t="n">
-        <v>45.73782</v>
+        <v>45.72365</v>
       </c>
       <c r="W65" t="n">
-        <v>-64.53246</v>
+        <v>-64.50663</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1361</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1362</t>
         </is>
       </c>
     </row>
@@ -5242,11 +5242,11 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Cape Maringouin # 1</t>
+          <t>Black Point North</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1360</v>
+        <v>1368</v>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
@@ -5257,7 +5257,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cu, Pb</t>
+          <t>Cu, Zn</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5295,14 +5295,14 @@
         <v>37</v>
       </c>
       <c r="V66" t="n">
-        <v>45.73532</v>
+        <v>45.80448</v>
       </c>
       <c r="W66" t="n">
-        <v>-64.54191</v>
+        <v>-64.41634999999999</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1360</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1368</t>
         </is>
       </c>
     </row>
@@ -5312,11 +5312,11 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Frye Island North</t>
+          <t>Grande Anse</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1353</v>
+        <v>1370</v>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
@@ -5327,7 +5327,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ag, Cu, F, Pb, Sb, Zn</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5365,14 +5365,14 @@
         <v>37</v>
       </c>
       <c r="V67" t="n">
-        <v>45.04753</v>
+        <v>45.79615</v>
       </c>
       <c r="W67" t="n">
-        <v>-66.84469</v>
+        <v>-64.50107</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1353</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1370</t>
         </is>
       </c>
     </row>
@@ -5382,11 +5382,11 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Quispamsis Exit</t>
+          <t>Sinclair Hill</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1338</v>
+        <v>9</v>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ag, Au, Cu, Pb</t>
+          <t>Ag, Au, Cu</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5435,14 +5435,14 @@
         <v>37</v>
       </c>
       <c r="V68" t="n">
-        <v>45.42378</v>
+        <v>45.63113</v>
       </c>
       <c r="W68" t="n">
-        <v>-65.92708</v>
+        <v>-64.92274999999999</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1338</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=9</t>
         </is>
       </c>
     </row>
@@ -5452,11 +5452,11 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Digdeguash Cu *</t>
+          <t>Scoudouc River Quarry</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1344</v>
+        <v>1367</v>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
@@ -5467,7 +5467,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cu, Zn</t>
+          <t>Pb, Zn</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5505,14 +5505,14 @@
         <v>37</v>
       </c>
       <c r="V69" t="n">
-        <v>45.18698</v>
+        <v>46.19643</v>
       </c>
       <c r="W69" t="n">
-        <v>-66.93774999999999</v>
+        <v>-64.54385000000001</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1344</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1367</t>
         </is>
       </c>
     </row>
@@ -5522,11 +5522,11 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Sinclair Hill</t>
+          <t>Shediac River # 2</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>9</v>
+        <v>1365</v>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
@@ -5537,7 +5537,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ag, Au, Cu</t>
+          <t>As</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5575,14 +5575,14 @@
         <v>37</v>
       </c>
       <c r="V70" t="n">
-        <v>45.63113</v>
+        <v>46.2417</v>
       </c>
       <c r="W70" t="n">
-        <v>-64.92274999999999</v>
+        <v>-64.6858</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=9</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1365</t>
         </is>
       </c>
     </row>
@@ -5592,11 +5592,11 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Taylors Island</t>
+          <t>Johnson Mills</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>32</v>
+        <v>1371</v>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5645,14 +5645,14 @@
         <v>37</v>
       </c>
       <c r="V71" t="n">
-        <v>45.22336</v>
+        <v>45.76365</v>
       </c>
       <c r="W71" t="n">
-        <v>-66.12747</v>
+        <v>-64.52218000000001</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=32</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1371</t>
         </is>
       </c>
     </row>
@@ -5662,11 +5662,11 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Henry Lake</t>
+          <t>Moores Mills #2</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1510</v>
+        <v>1374</v>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
@@ -5677,7 +5677,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Ag, Cu, Pb</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5706,23 +5706,23 @@
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T72" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U72" t="n">
         <v>37</v>
       </c>
       <c r="V72" t="n">
-        <v>45.39473</v>
+        <v>45.29977</v>
       </c>
       <c r="W72" t="n">
-        <v>-65.60417</v>
+        <v>-67.2533</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1510</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1374</t>
         </is>
       </c>
     </row>
@@ -5802,11 +5802,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Four Mile Lake B</t>
+          <t>Jacquet River Cu - A</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1175</v>
+        <v>462</v>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
@@ -5815,7 +5815,11 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
       <c r="H74" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -5851,14 +5855,14 @@
         <v>35</v>
       </c>
       <c r="V74" t="n">
-        <v>46.63643</v>
+        <v>47.85476</v>
       </c>
       <c r="W74" t="n">
-        <v>-66.58274</v>
+        <v>-66.01551000000001</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1175</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=462</t>
         </is>
       </c>
     </row>
@@ -5868,11 +5872,11 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Caledonia Mountain</t>
+          <t>Brewers Mills</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1609</v>
+        <v>904</v>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
@@ -5883,7 +5887,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ti, V</t>
+          <t>As, Au</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5912,23 +5916,23 @@
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T75" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U75" t="n">
         <v>35</v>
       </c>
       <c r="V75" t="n">
-        <v>45.8698</v>
+        <v>46.0692</v>
       </c>
       <c r="W75" t="n">
-        <v>-64.73159</v>
+        <v>-67.0283</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1609</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=904</t>
         </is>
       </c>
     </row>
@@ -5938,11 +5942,11 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Jacquet River Cu - Mitchell Rd</t>
+          <t>Jacquet River K</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>461</v>
+        <v>973</v>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr"/>
@@ -5987,14 +5991,14 @@
         <v>35</v>
       </c>
       <c r="V76" t="n">
-        <v>47.82725</v>
+        <v>47.83142</v>
       </c>
       <c r="W76" t="n">
-        <v>-66.00606999999999</v>
+        <v>-66.03246</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=461</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=973</t>
         </is>
       </c>
     </row>
@@ -6004,11 +6008,11 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Jacquet River Cu - A</t>
+          <t>Caledonia Mountain</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>462</v>
+        <v>1609</v>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
@@ -6019,7 +6023,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Ti, V</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6048,23 +6052,23 @@
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T77" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U77" t="n">
         <v>35</v>
       </c>
       <c r="V77" t="n">
-        <v>47.85476</v>
+        <v>45.8698</v>
       </c>
       <c r="W77" t="n">
-        <v>-66.01551000000001</v>
+        <v>-64.73159</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=462</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1609</t>
         </is>
       </c>
     </row>
@@ -6074,11 +6078,11 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Dumfries *</t>
+          <t>Centreville &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>535</v>
+        <v>263</v>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
@@ -6089,7 +6093,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -6127,14 +6131,14 @@
         <v>35</v>
       </c>
       <c r="V78" t="n">
-        <v>45.95029</v>
+        <v>46.44281</v>
       </c>
       <c r="W78" t="n">
-        <v>-67.12273999999999</v>
+        <v>-67.6808</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=535</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=263</t>
         </is>
       </c>
     </row>
@@ -6144,11 +6148,11 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Letete Mine</t>
+          <t>Waterville Prospect &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>311</v>
+        <v>1413</v>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
@@ -6159,12 +6163,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Au, Sb</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I79" t="b">
@@ -6175,15 +6179,11 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>1.9 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
+      <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="n">
         <v>0</v>
@@ -6192,23 +6192,23 @@
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T79" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U79" t="n">
         <v>35</v>
       </c>
       <c r="V79" t="n">
-        <v>45.06529</v>
+        <v>46.05921</v>
       </c>
       <c r="W79" t="n">
-        <v>-66.91136</v>
+        <v>-67.30663</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=311</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1413</t>
         </is>
       </c>
     </row>
@@ -6218,11 +6218,11 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Silver Island</t>
+          <t>Indian Brook</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>586</v>
+        <v>262</v>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
@@ -6231,11 +6231,7 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Ag, Pb, Zn</t>
-        </is>
-      </c>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -6271,14 +6267,14 @@
         <v>35</v>
       </c>
       <c r="V80" t="n">
-        <v>45.12114</v>
+        <v>46.73226</v>
       </c>
       <c r="W80" t="n">
-        <v>-66.8458</v>
+        <v>-67.42440999999999</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=586</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=262</t>
         </is>
       </c>
     </row>
@@ -6288,11 +6284,11 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Forty Five River &amp;quot;I&amp;quot;</t>
+          <t>Brummagen Brook Bog</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>647</v>
+        <v>188</v>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
@@ -6303,7 +6299,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -6332,23 +6328,23 @@
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T81" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U81" t="n">
         <v>35</v>
       </c>
       <c r="V81" t="n">
-        <v>45.74309</v>
+        <v>46.39003</v>
       </c>
       <c r="W81" t="n">
-        <v>-64.93053</v>
+        <v>-67.29386</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=647</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=188</t>
         </is>
       </c>
     </row>
@@ -6358,11 +6354,11 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Phyllis Creek &amp;quot;I&amp;quot;</t>
+          <t>Pecks Point South</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>655</v>
+        <v>1329</v>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
@@ -6373,7 +6369,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Ag, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -6411,14 +6407,14 @@
         <v>35</v>
       </c>
       <c r="V82" t="n">
-        <v>45.94808</v>
+        <v>45.73809</v>
       </c>
       <c r="W82" t="n">
-        <v>-66.69441</v>
+        <v>-64.48524</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=655</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1329</t>
         </is>
       </c>
     </row>
@@ -6428,11 +6424,11 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Pirate Lake</t>
+          <t>Dumfries *</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>516</v>
+        <v>535</v>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
@@ -6443,7 +6439,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -6481,14 +6477,14 @@
         <v>35</v>
       </c>
       <c r="V83" t="n">
-        <v>45.72697</v>
+        <v>45.95029</v>
       </c>
       <c r="W83" t="n">
-        <v>-67.67525000000001</v>
+        <v>-67.12273999999999</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=516</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=535</t>
         </is>
       </c>
     </row>
@@ -6498,11 +6494,11 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Pecks Point South</t>
+          <t>Pirate Lake</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1329</v>
+        <v>516</v>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
@@ -6513,7 +6509,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ag, Cu, Pb, Zn</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -6551,14 +6547,14 @@
         <v>35</v>
       </c>
       <c r="V84" t="n">
-        <v>45.73809</v>
+        <v>45.72697</v>
       </c>
       <c r="W84" t="n">
-        <v>-64.48524</v>
+        <v>-67.67525000000001</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1329</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=516</t>
         </is>
       </c>
     </row>
@@ -6568,11 +6564,11 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>East Quoddy Head</t>
+          <t>Elmtree 7B</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>737</v>
+        <v>854</v>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
@@ -6583,7 +6579,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pb</t>
+          <t>Cu, Ni</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -6612,23 +6608,23 @@
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
       <c r="S85" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T85" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U85" t="n">
         <v>35</v>
       </c>
       <c r="V85" t="n">
-        <v>44.95391</v>
+        <v>47.78253</v>
       </c>
       <c r="W85" t="n">
-        <v>-66.90831</v>
+        <v>-65.87246</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=737</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=854</t>
         </is>
       </c>
     </row>
@@ -6638,11 +6634,11 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Meadow Brook Cove</t>
+          <t>Four Mile Lake B</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>727</v>
+        <v>1175</v>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
@@ -6651,11 +6647,7 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Fe, Zn</t>
-        </is>
-      </c>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -6691,14 +6683,14 @@
         <v>35</v>
       </c>
       <c r="V86" t="n">
-        <v>44.88281</v>
+        <v>46.63643</v>
       </c>
       <c r="W86" t="n">
-        <v>-66.90774999999999</v>
+        <v>-66.58274</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=727</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1175</t>
         </is>
       </c>
     </row>
@@ -6708,11 +6700,11 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Jacquet River K</t>
+          <t>Meadow Brook Cove</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>973</v>
+        <v>727</v>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
@@ -6721,7 +6713,11 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Fe, Zn</t>
+        </is>
+      </c>
       <c r="H87" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -6757,14 +6753,14 @@
         <v>35</v>
       </c>
       <c r="V87" t="n">
-        <v>47.83142</v>
+        <v>44.88281</v>
       </c>
       <c r="W87" t="n">
-        <v>-66.03246</v>
+        <v>-66.90774999999999</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=973</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=727</t>
         </is>
       </c>
     </row>
@@ -6774,11 +6770,11 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Little Southwest Miramichi</t>
+          <t>East Quoddy Head</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>621</v>
+        <v>737</v>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
@@ -6787,7 +6783,11 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Pb</t>
+        </is>
+      </c>
       <c r="H88" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -6823,14 +6823,14 @@
         <v>35</v>
       </c>
       <c r="V88" t="n">
-        <v>46.89643</v>
+        <v>44.95391</v>
       </c>
       <c r="W88" t="n">
-        <v>-66.34998</v>
+        <v>-66.90831</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=621</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=737</t>
         </is>
       </c>
     </row>
@@ -6840,11 +6840,11 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Waterside Manganese</t>
+          <t>Silver Island</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>645</v>
+        <v>586</v>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
@@ -6855,7 +6855,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Ag, Pb, Zn</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6884,23 +6884,23 @@
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr"/>
       <c r="S89" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T89" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U89" t="n">
         <v>35</v>
       </c>
       <c r="V89" t="n">
-        <v>45.63058</v>
+        <v>45.12114</v>
       </c>
       <c r="W89" t="n">
-        <v>-64.82858</v>
+        <v>-66.8458</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=645</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=586</t>
         </is>
       </c>
     </row>
@@ -6910,11 +6910,11 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Brewers Mills</t>
+          <t>Phyllis Creek &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>904</v>
+        <v>655</v>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr"/>
@@ -6925,7 +6925,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>As, Au</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6963,14 +6963,14 @@
         <v>35</v>
       </c>
       <c r="V90" t="n">
-        <v>46.0692</v>
+        <v>45.94808</v>
       </c>
       <c r="W90" t="n">
-        <v>-67.0283</v>
+        <v>-66.69441</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=904</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=655</t>
         </is>
       </c>
     </row>
@@ -6980,11 +6980,11 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Elmtree 7B</t>
+          <t>Jacquet River Cu - Mitchell Rd</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>854</v>
+        <v>461</v>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
@@ -6993,11 +6993,7 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Cu, Ni</t>
-        </is>
-      </c>
+      <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -7024,23 +7020,23 @@
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr"/>
       <c r="S91" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T91" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U91" t="n">
         <v>35</v>
       </c>
       <c r="V91" t="n">
-        <v>47.78253</v>
+        <v>47.82725</v>
       </c>
       <c r="W91" t="n">
-        <v>-65.87246</v>
+        <v>-66.00606999999999</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=854</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=461</t>
         </is>
       </c>
     </row>
@@ -7050,11 +7046,11 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MacIntosh Brook</t>
+          <t>Maple Ridge</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>192</v>
+        <v>152</v>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr"/>
@@ -7065,7 +7061,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Mo, W</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -7094,23 +7090,23 @@
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr"/>
       <c r="S92" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T92" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U92" t="n">
         <v>35</v>
       </c>
       <c r="V92" t="n">
-        <v>46.35335</v>
+        <v>46.10003</v>
       </c>
       <c r="W92" t="n">
-        <v>-67.27636</v>
+        <v>-67.21413</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=192</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=152</t>
         </is>
       </c>
     </row>
@@ -7120,11 +7116,11 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Maple Ridge</t>
+          <t>MacIntosh Brook</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>152</v>
+        <v>192</v>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
@@ -7135,7 +7131,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Mo, W</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -7164,23 +7160,23 @@
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr"/>
       <c r="S93" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T93" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U93" t="n">
         <v>35</v>
       </c>
       <c r="V93" t="n">
-        <v>46.10003</v>
+        <v>46.35335</v>
       </c>
       <c r="W93" t="n">
-        <v>-67.21413</v>
+        <v>-67.27636</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=152</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=192</t>
         </is>
       </c>
     </row>
@@ -7190,11 +7186,11 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Indian Brook</t>
+          <t>Letete Mine</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>262</v>
+        <v>311</v>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
@@ -7203,10 +7199,14 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I94" t="b">
@@ -7217,11 +7217,15 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>1.9 Mt</t>
         </is>
       </c>
       <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="n">
         <v>0</v>
@@ -7230,23 +7234,23 @@
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr"/>
       <c r="S94" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T94" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U94" t="n">
         <v>35</v>
       </c>
       <c r="V94" t="n">
-        <v>46.73226</v>
+        <v>45.06529</v>
       </c>
       <c r="W94" t="n">
-        <v>-67.42440999999999</v>
+        <v>-66.91136</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=262</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=311</t>
         </is>
       </c>
     </row>
@@ -7256,11 +7260,11 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Centreville &amp;quot;I&amp;quot;</t>
+          <t>Forty Five River &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>263</v>
+        <v>647</v>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
@@ -7271,7 +7275,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -7300,23 +7304,23 @@
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="inlineStr"/>
       <c r="S95" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T95" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U95" t="n">
         <v>35</v>
       </c>
       <c r="V95" t="n">
-        <v>46.44281</v>
+        <v>45.74309</v>
       </c>
       <c r="W95" t="n">
-        <v>-67.6808</v>
+        <v>-64.93053</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=263</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=647</t>
         </is>
       </c>
     </row>
@@ -7326,11 +7330,11 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Brummagen Brook Bog</t>
+          <t>Waterside Manganese</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>188</v>
+        <v>645</v>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
@@ -7370,23 +7374,23 @@
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr"/>
       <c r="S96" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T96" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U96" t="n">
         <v>35</v>
       </c>
       <c r="V96" t="n">
-        <v>46.39003</v>
+        <v>45.63058</v>
       </c>
       <c r="W96" t="n">
-        <v>-67.29386</v>
+        <v>-64.82858</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=188</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=645</t>
         </is>
       </c>
     </row>
@@ -7396,11 +7400,11 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Waterville Prospect &amp;quot;I&amp;quot;</t>
+          <t>Little Southwest Miramichi</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1413</v>
+        <v>621</v>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
@@ -7409,11 +7413,7 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>Au, Sb</t>
-        </is>
-      </c>
+      <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -7449,14 +7449,14 @@
         <v>35</v>
       </c>
       <c r="V97" t="n">
-        <v>46.05921</v>
+        <v>46.89643</v>
       </c>
       <c r="W97" t="n">
-        <v>-67.30663</v>
+        <v>-66.34998</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1413</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=621</t>
         </is>
       </c>
     </row>
@@ -7466,11 +7466,11 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Meridian Brook Crossing</t>
+          <t>Shepody Mountain Manganese</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>630</v>
+        <v>721</v>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
@@ -7479,7 +7479,11 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Mn</t>
+        </is>
+      </c>
       <c r="H98" t="inlineStr">
         <is>
           <t>Past Producer</t>
@@ -7506,23 +7510,23 @@
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr"/>
       <c r="S98" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T98" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="U98" t="n">
         <v>30</v>
       </c>
       <c r="V98" t="n">
-        <v>47.26747</v>
+        <v>45.80502</v>
       </c>
       <c r="W98" t="n">
-        <v>-66.68077</v>
+        <v>-64.65774</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=630</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=721</t>
         </is>
       </c>
     </row>
@@ -7532,11 +7536,11 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Shepody Mountain Manganese</t>
+          <t>South Hamilton Road</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>721</v>
+        <v>1412</v>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr"/>
@@ -7547,7 +7551,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Ag, Au, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -7576,23 +7580,23 @@
       <c r="Q99" t="inlineStr"/>
       <c r="R99" t="inlineStr"/>
       <c r="S99" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T99" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U99" t="n">
         <v>30</v>
       </c>
       <c r="V99" t="n">
-        <v>45.80502</v>
+        <v>45.56892</v>
       </c>
       <c r="W99" t="n">
-        <v>-64.65774</v>
+        <v>-66.16552</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=721</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1412</t>
         </is>
       </c>
     </row>
@@ -7672,11 +7676,11 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>South Hamilton Road</t>
+          <t>Meridian Brook Crossing</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1412</v>
+        <v>630</v>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr"/>
@@ -7685,11 +7689,7 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>Ag, Au, Cu, Pb, Zn</t>
-        </is>
-      </c>
+      <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
           <t>Past Producer</t>
@@ -7716,23 +7716,23 @@
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr"/>
       <c r="S101" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T101" t="n">
-        <v>325</v>
+        <v>100</v>
       </c>
       <c r="U101" t="n">
         <v>30</v>
       </c>
       <c r="V101" t="n">
-        <v>45.56892</v>
+        <v>47.26747</v>
       </c>
       <c r="W101" t="n">
-        <v>-66.16552</v>
+        <v>-66.68077</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1412</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=630</t>
         </is>
       </c>
     </row>

--- a/site/nb_leads.xlsx
+++ b/site/nb_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X103"/>
+  <dimension ref="A1:X105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4472,11 +4472,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Church Showing</t>
+          <t>Bulls Creek 2</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>726</v>
+        <v>1072</v>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
@@ -4487,7 +4487,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Ag, Au, Co, Cu</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4516,23 +4516,23 @@
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T55" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U55" t="n">
         <v>37</v>
       </c>
       <c r="V55" t="n">
-        <v>44.88974</v>
+        <v>46.08809</v>
       </c>
       <c r="W55" t="n">
-        <v>-66.95386000000001</v>
+        <v>-67.56498000000001</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=726</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1072</t>
         </is>
       </c>
     </row>
@@ -4542,11 +4542,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Jeanne Mance</t>
+          <t>Bulls Creek 1</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1249</v>
+        <v>1071</v>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
@@ -4595,14 +4595,14 @@
         <v>37</v>
       </c>
       <c r="V56" t="n">
-        <v>47.36337</v>
+        <v>46.08421</v>
       </c>
       <c r="W56" t="n">
-        <v>-65.44329999999999</v>
+        <v>-67.57774999999999</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1249</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1071</t>
         </is>
       </c>
     </row>
@@ -4612,11 +4612,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Black Point</t>
+          <t>Church Showing</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1333</v>
+        <v>726</v>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pb, Zn</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4665,14 +4665,14 @@
         <v>37</v>
       </c>
       <c r="V57" t="n">
-        <v>45.79448</v>
+        <v>44.88974</v>
       </c>
       <c r="W57" t="n">
-        <v>-64.42218</v>
+        <v>-66.95386000000001</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1333</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=726</t>
         </is>
       </c>
     </row>
@@ -4682,11 +4682,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Quispamsis Exit</t>
+          <t>Jeanne Mance</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1338</v>
+        <v>1249</v>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ag, Au, Cu, Pb</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4735,14 +4735,14 @@
         <v>37</v>
       </c>
       <c r="V58" t="n">
-        <v>45.42378</v>
+        <v>47.36337</v>
       </c>
       <c r="W58" t="n">
-        <v>-65.92708</v>
+        <v>-65.44329999999999</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1338</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1249</t>
         </is>
       </c>
     </row>
@@ -4752,11 +4752,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Basaltic Island West *</t>
+          <t>Black Point</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1347</v>
+        <v>1333</v>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
@@ -4805,14 +4805,14 @@
         <v>37</v>
       </c>
       <c r="V59" t="n">
-        <v>45.1392</v>
+        <v>45.79448</v>
       </c>
       <c r="W59" t="n">
-        <v>-66.92413999999999</v>
+        <v>-64.42218</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1347</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1333</t>
         </is>
       </c>
     </row>
@@ -4822,11 +4822,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Frye Island North</t>
+          <t>Quispamsis Exit</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1353</v>
+        <v>1338</v>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ag, Cu, F, Pb, Sb, Zn</t>
+          <t>Ag, Au, Cu, Pb</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4875,14 +4875,14 @@
         <v>37</v>
       </c>
       <c r="V60" t="n">
-        <v>45.04753</v>
+        <v>45.42378</v>
       </c>
       <c r="W60" t="n">
-        <v>-66.84469</v>
+        <v>-65.92708</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1353</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1338</t>
         </is>
       </c>
     </row>
@@ -4892,11 +4892,11 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Gaspereau River</t>
+          <t>Basaltic Island West *</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1300</v>
+        <v>1347</v>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Pb, Zn</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4945,14 +4945,14 @@
         <v>37</v>
       </c>
       <c r="V61" t="n">
-        <v>46.08059</v>
+        <v>45.1392</v>
       </c>
       <c r="W61" t="n">
-        <v>-64.20996</v>
+        <v>-66.92413999999999</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1300</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1347</t>
         </is>
       </c>
     </row>
@@ -4962,11 +4962,11 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Cape Maringouin # 1</t>
+          <t>Frye Island North</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1360</v>
+        <v>1353</v>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
@@ -4977,7 +4977,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cu, Pb</t>
+          <t>Ag, Cu, F, Pb, Sb, Zn</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5015,14 +5015,14 @@
         <v>37</v>
       </c>
       <c r="V62" t="n">
-        <v>45.73532</v>
+        <v>45.04753</v>
       </c>
       <c r="W62" t="n">
-        <v>-64.54191</v>
+        <v>-66.84469</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1360</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1353</t>
         </is>
       </c>
     </row>
@@ -5032,11 +5032,11 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Cape Maringouin # 2</t>
+          <t>Gaspereau River</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1361</v>
+        <v>1300</v>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
@@ -5047,7 +5047,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ag, Cu, Pb, Zn</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5085,14 +5085,14 @@
         <v>37</v>
       </c>
       <c r="V63" t="n">
-        <v>45.73782</v>
+        <v>46.08059</v>
       </c>
       <c r="W63" t="n">
-        <v>-64.53246</v>
+        <v>-64.20996</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1361</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1300</t>
         </is>
       </c>
     </row>
@@ -5102,11 +5102,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Digdeguash Cu *</t>
+          <t>Cape Maringouin # 1</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1344</v>
+        <v>1360</v>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cu, Zn</t>
+          <t>Cu, Pb</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5155,14 +5155,14 @@
         <v>37</v>
       </c>
       <c r="V64" t="n">
-        <v>45.18698</v>
+        <v>45.73532</v>
       </c>
       <c r="W64" t="n">
-        <v>-66.93774999999999</v>
+        <v>-64.54191</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1344</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1360</t>
         </is>
       </c>
     </row>
@@ -5172,11 +5172,11 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Rockport Shore</t>
+          <t>Cape Maringouin # 2</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Ag, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5225,14 +5225,14 @@
         <v>37</v>
       </c>
       <c r="V65" t="n">
-        <v>45.72365</v>
+        <v>45.73782</v>
       </c>
       <c r="W65" t="n">
-        <v>-64.50663</v>
+        <v>-64.53246</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1362</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1361</t>
         </is>
       </c>
     </row>
@@ -5242,11 +5242,11 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Black Point North</t>
+          <t>Digdeguash Cu *</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1368</v>
+        <v>1344</v>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
@@ -5295,14 +5295,14 @@
         <v>37</v>
       </c>
       <c r="V66" t="n">
-        <v>45.80448</v>
+        <v>45.18698</v>
       </c>
       <c r="W66" t="n">
-        <v>-64.41634999999999</v>
+        <v>-66.93774999999999</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1368</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1344</t>
         </is>
       </c>
     </row>
@@ -5312,11 +5312,11 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Grande Anse</t>
+          <t>Rockport Shore</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1370</v>
+        <v>1362</v>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
@@ -5365,14 +5365,14 @@
         <v>37</v>
       </c>
       <c r="V67" t="n">
-        <v>45.79615</v>
+        <v>45.72365</v>
       </c>
       <c r="W67" t="n">
-        <v>-64.50107</v>
+        <v>-64.50663</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1370</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1362</t>
         </is>
       </c>
     </row>
@@ -5382,11 +5382,11 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Sinclair Hill</t>
+          <t>Black Point North</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>9</v>
+        <v>1368</v>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ag, Au, Cu</t>
+          <t>Cu, Zn</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5435,14 +5435,14 @@
         <v>37</v>
       </c>
       <c r="V68" t="n">
-        <v>45.63113</v>
+        <v>45.80448</v>
       </c>
       <c r="W68" t="n">
-        <v>-64.92274999999999</v>
+        <v>-64.41634999999999</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=9</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1368</t>
         </is>
       </c>
     </row>
@@ -5452,11 +5452,11 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Scoudouc River Quarry</t>
+          <t>Grande Anse</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1367</v>
+        <v>1370</v>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
@@ -5467,7 +5467,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pb, Zn</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5505,14 +5505,14 @@
         <v>37</v>
       </c>
       <c r="V69" t="n">
-        <v>46.19643</v>
+        <v>45.79615</v>
       </c>
       <c r="W69" t="n">
-        <v>-64.54385000000001</v>
+        <v>-64.50107</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1367</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1370</t>
         </is>
       </c>
     </row>
@@ -5522,11 +5522,11 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Shediac River # 2</t>
+          <t>Sinclair Hill</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1365</v>
+        <v>9</v>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
@@ -5537,7 +5537,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>As</t>
+          <t>Ag, Au, Cu</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5575,14 +5575,14 @@
         <v>37</v>
       </c>
       <c r="V70" t="n">
-        <v>46.2417</v>
+        <v>45.63113</v>
       </c>
       <c r="W70" t="n">
-        <v>-64.6858</v>
+        <v>-64.92274999999999</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1365</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=9</t>
         </is>
       </c>
     </row>
@@ -5592,11 +5592,11 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Johnson Mills</t>
+          <t>Scoudouc River Quarry</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Pb, Zn</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5645,14 +5645,14 @@
         <v>37</v>
       </c>
       <c r="V71" t="n">
-        <v>45.76365</v>
+        <v>46.19643</v>
       </c>
       <c r="W71" t="n">
-        <v>-64.52218000000001</v>
+        <v>-64.54385000000001</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1371</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1367</t>
         </is>
       </c>
     </row>
@@ -5662,11 +5662,11 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Moores Mills #2</t>
+          <t>Shediac River # 2</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1374</v>
+        <v>1365</v>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
@@ -5677,7 +5677,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ag, Cu, Pb</t>
+          <t>As</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5706,23 +5706,23 @@
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T72" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U72" t="n">
         <v>37</v>
       </c>
       <c r="V72" t="n">
-        <v>45.29977</v>
+        <v>46.2417</v>
       </c>
       <c r="W72" t="n">
-        <v>-67.2533</v>
+        <v>-64.6858</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1374</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1365</t>
         </is>
       </c>
     </row>
@@ -5732,11 +5732,11 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Little John Lake</t>
+          <t>Johnson Mills</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1396</v>
+        <v>1371</v>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
@@ -5747,7 +5747,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Au, Cu, Pb</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5776,23 +5776,23 @@
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T73" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U73" t="n">
         <v>37</v>
       </c>
       <c r="V73" t="n">
-        <v>45.34976</v>
+        <v>45.76365</v>
       </c>
       <c r="W73" t="n">
-        <v>-66.31052</v>
+        <v>-64.52218000000001</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1396</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1371</t>
         </is>
       </c>
     </row>
@@ -5802,11 +5802,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Jacquet River Cu - A</t>
+          <t>Moores Mills #2</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>462</v>
+        <v>1374</v>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
@@ -5817,12 +5817,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Ag, Cu, Pb</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Developed Prospect</t>
         </is>
       </c>
       <c r="I74" t="b">
@@ -5846,23 +5846,23 @@
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T74" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U74" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="V74" t="n">
-        <v>47.85476</v>
+        <v>45.29977</v>
       </c>
       <c r="W74" t="n">
-        <v>-66.01551000000001</v>
+        <v>-67.2533</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=462</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1374</t>
         </is>
       </c>
     </row>
@@ -5872,11 +5872,11 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Brewers Mills</t>
+          <t>Little John Lake</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>904</v>
+        <v>1396</v>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
@@ -5887,12 +5887,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>As, Au</t>
+          <t>Au, Cu, Pb</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Developed Prospect</t>
         </is>
       </c>
       <c r="I75" t="b">
@@ -5916,23 +5916,23 @@
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T75" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U75" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="V75" t="n">
-        <v>46.0692</v>
+        <v>45.34976</v>
       </c>
       <c r="W75" t="n">
-        <v>-67.0283</v>
+        <v>-66.31052</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=904</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1396</t>
         </is>
       </c>
     </row>
@@ -5942,11 +5942,11 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Jacquet River K</t>
+          <t>Jacquet River Cu - A</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>973</v>
+        <v>462</v>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr"/>
@@ -5955,7 +5955,11 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
       <c r="H76" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -5991,14 +5995,14 @@
         <v>35</v>
       </c>
       <c r="V76" t="n">
-        <v>47.83142</v>
+        <v>47.85476</v>
       </c>
       <c r="W76" t="n">
-        <v>-66.03246</v>
+        <v>-66.01551000000001</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=973</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=462</t>
         </is>
       </c>
     </row>
@@ -6008,11 +6012,11 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Caledonia Mountain</t>
+          <t>Brewers Mills</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1609</v>
+        <v>904</v>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
@@ -6023,7 +6027,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ti, V</t>
+          <t>As, Au</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6052,23 +6056,23 @@
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T77" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U77" t="n">
         <v>35</v>
       </c>
       <c r="V77" t="n">
-        <v>45.8698</v>
+        <v>46.0692</v>
       </c>
       <c r="W77" t="n">
-        <v>-64.73159</v>
+        <v>-67.0283</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1609</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=904</t>
         </is>
       </c>
     </row>
@@ -6078,11 +6082,11 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Centreville &amp;quot;I&amp;quot;</t>
+          <t>Jacquet River K</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>263</v>
+        <v>973</v>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
@@ -6091,11 +6095,7 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Au</t>
-        </is>
-      </c>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -6131,14 +6131,14 @@
         <v>35</v>
       </c>
       <c r="V78" t="n">
-        <v>46.44281</v>
+        <v>47.83142</v>
       </c>
       <c r="W78" t="n">
-        <v>-67.6808</v>
+        <v>-66.03246</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=263</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=973</t>
         </is>
       </c>
     </row>
@@ -6148,11 +6148,11 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Waterville Prospect &amp;quot;I&amp;quot;</t>
+          <t>Caledonia Mountain</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1413</v>
+        <v>1609</v>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
@@ -6163,7 +6163,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Au, Sb</t>
+          <t>Ti, V</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6192,23 +6192,23 @@
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T79" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U79" t="n">
         <v>35</v>
       </c>
       <c r="V79" t="n">
-        <v>46.05921</v>
+        <v>45.8698</v>
       </c>
       <c r="W79" t="n">
-        <v>-67.30663</v>
+        <v>-64.73159</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1413</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1609</t>
         </is>
       </c>
     </row>
@@ -6218,11 +6218,11 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Indian Brook</t>
+          <t>Centreville &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
@@ -6231,7 +6231,11 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Au</t>
+        </is>
+      </c>
       <c r="H80" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -6267,14 +6271,14 @@
         <v>35</v>
       </c>
       <c r="V80" t="n">
-        <v>46.73226</v>
+        <v>46.44281</v>
       </c>
       <c r="W80" t="n">
-        <v>-67.42440999999999</v>
+        <v>-67.6808</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=262</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=263</t>
         </is>
       </c>
     </row>
@@ -6284,11 +6288,11 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Brummagen Brook Bog</t>
+          <t>Waterville Prospect &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>188</v>
+        <v>1413</v>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
@@ -6299,7 +6303,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Au, Sb</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -6337,14 +6341,14 @@
         <v>35</v>
       </c>
       <c r="V81" t="n">
-        <v>46.39003</v>
+        <v>46.05921</v>
       </c>
       <c r="W81" t="n">
-        <v>-67.29386</v>
+        <v>-67.30663</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=188</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1413</t>
         </is>
       </c>
     </row>
@@ -6354,11 +6358,11 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Pecks Point South</t>
+          <t>Indian Brook</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1329</v>
+        <v>262</v>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
@@ -6367,11 +6371,7 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Ag, Cu, Pb, Zn</t>
-        </is>
-      </c>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -6407,14 +6407,14 @@
         <v>35</v>
       </c>
       <c r="V82" t="n">
-        <v>45.73809</v>
+        <v>46.73226</v>
       </c>
       <c r="W82" t="n">
-        <v>-64.48524</v>
+        <v>-67.42440999999999</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1329</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=262</t>
         </is>
       </c>
     </row>
@@ -6424,11 +6424,11 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Dumfries *</t>
+          <t>Brummagen Brook Bog</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>535</v>
+        <v>188</v>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
@@ -6439,7 +6439,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -6477,14 +6477,14 @@
         <v>35</v>
       </c>
       <c r="V83" t="n">
-        <v>45.95029</v>
+        <v>46.39003</v>
       </c>
       <c r="W83" t="n">
-        <v>-67.12273999999999</v>
+        <v>-67.29386</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=535</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=188</t>
         </is>
       </c>
     </row>
@@ -6494,11 +6494,11 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Pirate Lake</t>
+          <t>Pecks Point South</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>516</v>
+        <v>1329</v>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
@@ -6509,7 +6509,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Ag, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -6547,14 +6547,14 @@
         <v>35</v>
       </c>
       <c r="V84" t="n">
-        <v>45.72697</v>
+        <v>45.73809</v>
       </c>
       <c r="W84" t="n">
-        <v>-67.67525000000001</v>
+        <v>-64.48524</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=516</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1329</t>
         </is>
       </c>
     </row>
@@ -6564,11 +6564,11 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Elmtree 7B</t>
+          <t>Dumfries *</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>854</v>
+        <v>535</v>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cu, Ni</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -6608,23 +6608,23 @@
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
       <c r="S85" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T85" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U85" t="n">
         <v>35</v>
       </c>
       <c r="V85" t="n">
-        <v>47.78253</v>
+        <v>45.95029</v>
       </c>
       <c r="W85" t="n">
-        <v>-65.87246</v>
+        <v>-67.12273999999999</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=854</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=535</t>
         </is>
       </c>
     </row>
@@ -6634,11 +6634,11 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Four Mile Lake B</t>
+          <t>Pirate Lake</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1175</v>
+        <v>516</v>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
@@ -6647,7 +6647,11 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
       <c r="H86" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -6683,14 +6687,14 @@
         <v>35</v>
       </c>
       <c r="V86" t="n">
-        <v>46.63643</v>
+        <v>45.72697</v>
       </c>
       <c r="W86" t="n">
-        <v>-66.58274</v>
+        <v>-67.67525000000001</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1175</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=516</t>
         </is>
       </c>
     </row>
@@ -6700,11 +6704,11 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Meadow Brook Cove</t>
+          <t>Elmtree 7B</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>727</v>
+        <v>854</v>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
@@ -6715,7 +6719,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Fe, Zn</t>
+          <t>Cu, Ni</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -6744,23 +6748,23 @@
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr"/>
       <c r="S87" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T87" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U87" t="n">
         <v>35</v>
       </c>
       <c r="V87" t="n">
-        <v>44.88281</v>
+        <v>47.78253</v>
       </c>
       <c r="W87" t="n">
-        <v>-66.90774999999999</v>
+        <v>-65.87246</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=727</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=854</t>
         </is>
       </c>
     </row>
@@ -6770,11 +6774,11 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>East Quoddy Head</t>
+          <t>Four Mile Lake B</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>737</v>
+        <v>1175</v>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
@@ -6783,11 +6787,7 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Pb</t>
-        </is>
-      </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -6823,14 +6823,14 @@
         <v>35</v>
       </c>
       <c r="V88" t="n">
-        <v>44.95391</v>
+        <v>46.63643</v>
       </c>
       <c r="W88" t="n">
-        <v>-66.90831</v>
+        <v>-66.58274</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=737</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1175</t>
         </is>
       </c>
     </row>
@@ -6840,11 +6840,11 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Silver Island</t>
+          <t>Meadow Brook Cove</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>586</v>
+        <v>727</v>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
@@ -6855,7 +6855,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ag, Pb, Zn</t>
+          <t>Fe, Zn</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6893,14 +6893,14 @@
         <v>35</v>
       </c>
       <c r="V89" t="n">
-        <v>45.12114</v>
+        <v>44.88281</v>
       </c>
       <c r="W89" t="n">
-        <v>-66.8458</v>
+        <v>-66.90774999999999</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=586</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=727</t>
         </is>
       </c>
     </row>
@@ -6910,11 +6910,11 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Phyllis Creek &amp;quot;I&amp;quot;</t>
+          <t>East Quoddy Head</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>655</v>
+        <v>737</v>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr"/>
@@ -6925,7 +6925,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Pb</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6963,14 +6963,14 @@
         <v>35</v>
       </c>
       <c r="V90" t="n">
-        <v>45.94808</v>
+        <v>44.95391</v>
       </c>
       <c r="W90" t="n">
-        <v>-66.69441</v>
+        <v>-66.90831</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=655</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=737</t>
         </is>
       </c>
     </row>
@@ -6980,11 +6980,11 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Jacquet River Cu - Mitchell Rd</t>
+          <t>Silver Island</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>461</v>
+        <v>586</v>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
@@ -6993,7 +6993,11 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Ag, Pb, Zn</t>
+        </is>
+      </c>
       <c r="H91" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -7029,14 +7033,14 @@
         <v>35</v>
       </c>
       <c r="V91" t="n">
-        <v>47.82725</v>
+        <v>45.12114</v>
       </c>
       <c r="W91" t="n">
-        <v>-66.00606999999999</v>
+        <v>-66.8458</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=461</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=586</t>
         </is>
       </c>
     </row>
@@ -7046,11 +7050,11 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Maple Ridge</t>
+          <t>Phyllis Creek &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>152</v>
+        <v>655</v>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr"/>
@@ -7061,7 +7065,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Mo, W</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -7099,14 +7103,14 @@
         <v>35</v>
       </c>
       <c r="V92" t="n">
-        <v>46.10003</v>
+        <v>45.94808</v>
       </c>
       <c r="W92" t="n">
-        <v>-67.21413</v>
+        <v>-66.69441</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=152</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=655</t>
         </is>
       </c>
     </row>
@@ -7116,11 +7120,11 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>MacIntosh Brook</t>
+          <t>Jacquet River Cu - Mitchell Rd</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>192</v>
+        <v>461</v>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
@@ -7129,11 +7133,7 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>Cu</t>
-        </is>
-      </c>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -7160,23 +7160,23 @@
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr"/>
       <c r="S93" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T93" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U93" t="n">
         <v>35</v>
       </c>
       <c r="V93" t="n">
-        <v>46.35335</v>
+        <v>47.82725</v>
       </c>
       <c r="W93" t="n">
-        <v>-67.27636</v>
+        <v>-66.00606999999999</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=192</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=461</t>
         </is>
       </c>
     </row>
@@ -7186,11 +7186,11 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Letete Mine</t>
+          <t>Maple Ridge</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>311</v>
+        <v>152</v>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
@@ -7201,12 +7201,12 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Mo, W</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I94" t="b">
@@ -7217,15 +7217,11 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>1.9 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
+      <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="n">
         <v>0</v>
@@ -7234,23 +7230,23 @@
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr"/>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T94" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U94" t="n">
         <v>35</v>
       </c>
       <c r="V94" t="n">
-        <v>45.06529</v>
+        <v>46.10003</v>
       </c>
       <c r="W94" t="n">
-        <v>-66.91136</v>
+        <v>-67.21413</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=311</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=152</t>
         </is>
       </c>
     </row>
@@ -7260,11 +7256,11 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Forty Five River &amp;quot;I&amp;quot;</t>
+          <t>MacIntosh Brook</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>647</v>
+        <v>192</v>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
@@ -7275,7 +7271,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -7304,23 +7300,23 @@
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="inlineStr"/>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T95" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="U95" t="n">
         <v>35</v>
       </c>
       <c r="V95" t="n">
-        <v>45.74309</v>
+        <v>46.35335</v>
       </c>
       <c r="W95" t="n">
-        <v>-64.93053</v>
+        <v>-67.27636</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=647</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=192</t>
         </is>
       </c>
     </row>
@@ -7330,11 +7326,11 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Waterside Manganese</t>
+          <t>Letete Mine</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>645</v>
+        <v>311</v>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
@@ -7345,12 +7341,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I96" t="b">
@@ -7361,11 +7357,15 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>1.9 Mt</t>
         </is>
       </c>
       <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="n">
         <v>0</v>
@@ -7374,23 +7374,23 @@
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr"/>
       <c r="S96" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T96" t="n">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="U96" t="n">
         <v>35</v>
       </c>
       <c r="V96" t="n">
-        <v>45.63058</v>
+        <v>45.06529</v>
       </c>
       <c r="W96" t="n">
-        <v>-64.82858</v>
+        <v>-66.91136</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=645</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=311</t>
         </is>
       </c>
     </row>
@@ -7400,11 +7400,11 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Little Southwest Miramichi</t>
+          <t>Forty Five River &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>621</v>
+        <v>647</v>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
@@ -7413,7 +7413,11 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
       <c r="H97" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -7440,23 +7444,23 @@
       <c r="Q97" t="inlineStr"/>
       <c r="R97" t="inlineStr"/>
       <c r="S97" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T97" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U97" t="n">
         <v>35</v>
       </c>
       <c r="V97" t="n">
-        <v>46.89643</v>
+        <v>45.74309</v>
       </c>
       <c r="W97" t="n">
-        <v>-66.34998</v>
+        <v>-64.93053</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=621</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=647</t>
         </is>
       </c>
     </row>
@@ -7466,11 +7470,11 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Shepody Mountain Manganese</t>
+          <t>Waterside Manganese</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>721</v>
+        <v>645</v>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
@@ -7486,7 +7490,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I98" t="b">
@@ -7510,23 +7514,23 @@
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr"/>
       <c r="S98" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T98" t="n">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="U98" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="V98" t="n">
-        <v>45.80502</v>
+        <v>45.63058</v>
       </c>
       <c r="W98" t="n">
-        <v>-64.65774</v>
+        <v>-64.82858</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=721</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=645</t>
         </is>
       </c>
     </row>
@@ -7536,11 +7540,11 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>South Hamilton Road</t>
+          <t>Little Southwest Miramichi</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1412</v>
+        <v>621</v>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr"/>
@@ -7549,14 +7553,10 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>Ag, Au, Cu, Pb, Zn</t>
-        </is>
-      </c>
+      <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I99" t="b">
@@ -7586,17 +7586,17 @@
         <v>325</v>
       </c>
       <c r="U99" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="V99" t="n">
-        <v>45.56892</v>
+        <v>46.89643</v>
       </c>
       <c r="W99" t="n">
-        <v>-66.16552</v>
+        <v>-66.34998</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1412</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=621</t>
         </is>
       </c>
     </row>
@@ -7606,11 +7606,11 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Memramcook East</t>
+          <t>Shepody Mountain Manganese</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>320</v>
+        <v>721</v>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr"/>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ba</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -7650,23 +7650,23 @@
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr"/>
       <c r="S100" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T100" t="n">
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="U100" t="n">
         <v>30</v>
       </c>
       <c r="V100" t="n">
-        <v>46.01558</v>
+        <v>45.80502</v>
       </c>
       <c r="W100" t="n">
-        <v>-64.52218999999999</v>
+        <v>-64.65774</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=320</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=721</t>
         </is>
       </c>
     </row>
@@ -7676,11 +7676,11 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Meridian Brook Crossing</t>
+          <t>South Hamilton Road</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>630</v>
+        <v>1412</v>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr"/>
@@ -7689,7 +7689,11 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Ag, Au, Cu, Pb, Zn</t>
+        </is>
+      </c>
       <c r="H101" t="inlineStr">
         <is>
           <t>Past Producer</t>
@@ -7716,23 +7720,23 @@
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr"/>
       <c r="S101" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T101" t="n">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="U101" t="n">
         <v>30</v>
       </c>
       <c r="V101" t="n">
-        <v>47.26747</v>
+        <v>45.56892</v>
       </c>
       <c r="W101" t="n">
-        <v>-66.68077</v>
+        <v>-66.16552</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=630</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1412</t>
         </is>
       </c>
     </row>
@@ -7742,11 +7746,11 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Gaspereau Station</t>
+          <t>Memramcook East</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
@@ -7757,7 +7761,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Mo, Pb, Zn</t>
+          <t>Ba</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -7786,23 +7790,23 @@
       <c r="Q102" t="inlineStr"/>
       <c r="R102" t="inlineStr"/>
       <c r="S102" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T102" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U102" t="n">
         <v>30</v>
       </c>
       <c r="V102" t="n">
-        <v>45.48947</v>
+        <v>46.01558</v>
       </c>
       <c r="W102" t="n">
-        <v>-66.47469</v>
+        <v>-64.52218999999999</v>
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=328</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=320</t>
         </is>
       </c>
     </row>
@@ -7812,11 +7816,11 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Collins Lake</t>
+          <t>Meridian Brook Crossing</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1299</v>
+        <v>630</v>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
@@ -7825,14 +7829,10 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>Pb, Zn</t>
-        </is>
-      </c>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I103" t="b">
@@ -7843,15 +7843,11 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>1.9 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
+      <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
       <c r="O103" t="n">
         <v>0</v>
@@ -7860,21 +7856,165 @@
       <c r="Q103" t="inlineStr"/>
       <c r="R103" t="inlineStr"/>
       <c r="S103" t="n">
+        <v>4</v>
+      </c>
+      <c r="T103" t="n">
+        <v>100</v>
+      </c>
+      <c r="U103" t="n">
+        <v>30</v>
+      </c>
+      <c r="V103" t="n">
+        <v>47.26747</v>
+      </c>
+      <c r="W103" t="n">
+        <v>-66.68077</v>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=630</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Gaspereau Station</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>328</v>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Mo, Pb, Zn</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Past Producer</t>
+        </is>
+      </c>
+      <c r="I104" t="b">
+        <v>1</v>
+      </c>
+      <c r="J104" t="b">
+        <v>0</v>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr"/>
+      <c r="R104" t="inlineStr"/>
+      <c r="S104" t="n">
         <v>13</v>
       </c>
-      <c r="T103" t="n">
+      <c r="T104" t="n">
         <v>325</v>
       </c>
-      <c r="U103" t="n">
+      <c r="U104" t="n">
+        <v>30</v>
+      </c>
+      <c r="V104" t="n">
+        <v>45.48947</v>
+      </c>
+      <c r="W104" t="n">
+        <v>-66.47469</v>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=328</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Collins Lake</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>1299</v>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Pb, Zn</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Occurrence</t>
+        </is>
+      </c>
+      <c r="I105" t="b">
+        <v>1</v>
+      </c>
+      <c r="J105" t="b">
+        <v>0</v>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>1.9 Mt</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr"/>
+      <c r="R105" t="inlineStr"/>
+      <c r="S105" t="n">
+        <v>13</v>
+      </c>
+      <c r="T105" t="n">
+        <v>325</v>
+      </c>
+      <c r="U105" t="n">
         <v>27</v>
       </c>
-      <c r="V103" t="n">
+      <c r="V105" t="n">
         <v>46.10254</v>
       </c>
-      <c r="W103" t="n">
+      <c r="W105" t="n">
         <v>-64.11969000000001</v>
       </c>
-      <c r="X103" t="inlineStr">
+      <c r="X105" t="inlineStr">
         <is>
           <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1299</t>
         </is>

--- a/site/nb_leads.xlsx
+++ b/site/nb_leads.xlsx
@@ -570,11 +570,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sloop Cove</t>
+          <t>Shin Creek</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
@@ -585,7 +585,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Ag, Mo, W</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -627,14 +627,14 @@
         <v>45</v>
       </c>
       <c r="V2" t="n">
-        <v>44.68722</v>
+        <v>45.55224</v>
       </c>
       <c r="W2" t="n">
-        <v>-66.87302</v>
+        <v>-66.63357999999999</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=31</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=8</t>
         </is>
       </c>
     </row>
@@ -644,11 +644,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Quispamsis</t>
+          <t>Evandale Stock *</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -659,7 +659,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ag, Au, Cu, Pb, Zn</t>
+          <t>Ag, Au, Cu</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -701,14 +701,14 @@
         <v>45</v>
       </c>
       <c r="V3" t="n">
-        <v>45.42362</v>
+        <v>45.58501</v>
       </c>
       <c r="W3" t="n">
-        <v>-65.95802</v>
+        <v>-66.09690999999999</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=4</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=11</t>
         </is>
       </c>
     </row>
@@ -718,11 +718,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Melanson Brook E</t>
+          <t>Quispamsis</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1026</v>
+        <v>4</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -733,7 +733,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ag, Pb, Zn</t>
+          <t>Ag, Au, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -775,14 +775,14 @@
         <v>45</v>
       </c>
       <c r="V4" t="n">
-        <v>47.73447</v>
+        <v>45.42362</v>
       </c>
       <c r="W4" t="n">
-        <v>-65.98719</v>
+        <v>-65.95802</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1026</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=4</t>
         </is>
       </c>
     </row>
@@ -792,11 +792,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nigadoo 8</t>
+          <t>Pender Brook</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1028</v>
+        <v>10</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -807,7 +807,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ag, Au, Pb, Zn</t>
+          <t>Sb</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -840,23 +840,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T5" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U5" t="n">
         <v>45</v>
       </c>
       <c r="V5" t="n">
-        <v>47.74616</v>
+        <v>45.57888</v>
       </c>
       <c r="W5" t="n">
-        <v>-65.88711000000001</v>
+        <v>-66.30664</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1028</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=10</t>
         </is>
       </c>
     </row>
@@ -866,11 +866,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Antinouri Lake West B</t>
+          <t>Taylor Village</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1021</v>
+        <v>57</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -881,7 +881,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pb, Zn</t>
+          <t>Ti</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -923,14 +923,14 @@
         <v>45</v>
       </c>
       <c r="V6" t="n">
-        <v>47.78921</v>
+        <v>45.93834</v>
       </c>
       <c r="W6" t="n">
-        <v>-65.99773</v>
+        <v>-64.55385</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1021</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=57</t>
         </is>
       </c>
     </row>
@@ -940,11 +940,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Payne Brook</t>
+          <t>Quisibis Mountain</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1036</v>
+        <v>58</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -955,7 +955,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ag, Pb, Zn</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -997,14 +997,14 @@
         <v>45</v>
       </c>
       <c r="V7" t="n">
-        <v>47.74032</v>
+        <v>47.42337</v>
       </c>
       <c r="W7" t="n">
-        <v>-65.91246</v>
+        <v>-67.96913000000001</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1036</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=58</t>
         </is>
       </c>
     </row>
@@ -1014,11 +1014,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Belledune Pond</t>
+          <t>Levesque Gulch</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>72</v>
+        <v>1115</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ag, Cu, Pb, Zn</t>
+          <t>Au, Cu, Sb</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1062,23 +1062,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T8" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U8" t="n">
         <v>45</v>
       </c>
       <c r="V8" t="n">
-        <v>47.82638</v>
+        <v>47.6649</v>
       </c>
       <c r="W8" t="n">
-        <v>-65.97922</v>
+        <v>-66.69267000000001</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=72</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1115</t>
         </is>
       </c>
     </row>
@@ -1088,11 +1088,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>St. Leonard Iron-Manganese</t>
+          <t>Antinouri Lake West A</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Ag, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1145,14 +1145,14 @@
         <v>45</v>
       </c>
       <c r="V9" t="n">
-        <v>47.2053</v>
+        <v>47.78952</v>
       </c>
       <c r="W9" t="n">
-        <v>-67.88663</v>
+        <v>-65.98515</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=101</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=85</t>
         </is>
       </c>
     </row>
@@ -1236,11 +1236,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Antinouri Lake West A</t>
+          <t>St. Leonard Iron-Manganese</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ag, Cu, Pb, Zn</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1293,14 +1293,14 @@
         <v>45</v>
       </c>
       <c r="V11" t="n">
-        <v>47.78952</v>
+        <v>47.2053</v>
       </c>
       <c r="W11" t="n">
-        <v>-65.98515</v>
+        <v>-67.88663</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=85</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=101</t>
         </is>
       </c>
     </row>
@@ -1310,11 +1310,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Levesque Gulch</t>
+          <t>Belledune Pond</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1115</v>
+        <v>72</v>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Au, Cu, Sb</t>
+          <t>Ag, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1358,23 +1358,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T12" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U12" t="n">
         <v>45</v>
       </c>
       <c r="V12" t="n">
-        <v>47.6649</v>
+        <v>47.82638</v>
       </c>
       <c r="W12" t="n">
-        <v>-66.69267000000001</v>
+        <v>-65.97922</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1115</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=72</t>
         </is>
       </c>
     </row>
@@ -1384,11 +1384,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Gordon Meadow Brook East</t>
+          <t>Red Pine Brook</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1252</v>
+        <v>1408</v>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ag, Pb, Zn</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1441,14 +1441,14 @@
         <v>45</v>
       </c>
       <c r="V13" t="n">
-        <v>47.39279</v>
+        <v>47.4492</v>
       </c>
       <c r="W13" t="n">
-        <v>-65.68568999999999</v>
+        <v>-65.62412999999999</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1252</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1408</t>
         </is>
       </c>
     </row>
@@ -1458,11 +1458,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kenny Lake</t>
+          <t>Little Sevogle River 1</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1278</v>
+        <v>60</v>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pb, Zn</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1506,23 +1506,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T14" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U14" t="n">
         <v>45</v>
       </c>
       <c r="V14" t="n">
-        <v>47.23226</v>
+        <v>47.0005</v>
       </c>
       <c r="W14" t="n">
-        <v>-66.2908</v>
+        <v>-65.98999999999999</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1278</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=60</t>
         </is>
       </c>
     </row>
@@ -1532,11 +1532,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Green Creek North</t>
+          <t>Peekaboo Corner *</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1334</v>
+        <v>27</v>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
@@ -1589,14 +1589,14 @@
         <v>45</v>
       </c>
       <c r="V15" t="n">
-        <v>45.79059</v>
+        <v>45.65473</v>
       </c>
       <c r="W15" t="n">
-        <v>-64.44385</v>
+        <v>-65.71941</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1334</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=27</t>
         </is>
       </c>
     </row>
@@ -1606,11 +1606,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Peekaboo Corner *</t>
+          <t>Gordon Meadow Brook East</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>27</v>
+        <v>1252</v>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Ag, Pb, Zn</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1663,14 +1663,14 @@
         <v>45</v>
       </c>
       <c r="V16" t="n">
-        <v>45.65473</v>
+        <v>47.39279</v>
       </c>
       <c r="W16" t="n">
-        <v>-65.71941</v>
+        <v>-65.68568999999999</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=27</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1252</t>
         </is>
       </c>
     </row>
@@ -1680,11 +1680,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Shin Creek</t>
+          <t>Nigadoo 8</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>1028</v>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ag, Mo, W</t>
+          <t>Ag, Au, Pb, Zn</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1728,23 +1728,23 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T17" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U17" t="n">
         <v>45</v>
       </c>
       <c r="V17" t="n">
-        <v>45.55224</v>
+        <v>47.74616</v>
       </c>
       <c r="W17" t="n">
-        <v>-66.63357999999999</v>
+        <v>-65.88711000000001</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=8</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1028</t>
         </is>
       </c>
     </row>
@@ -1754,11 +1754,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Quisibis Mountain</t>
+          <t>Melanson Brook E</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>58</v>
+        <v>1026</v>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Ag, Pb, Zn</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1811,14 +1811,14 @@
         <v>45</v>
       </c>
       <c r="V18" t="n">
-        <v>47.42337</v>
+        <v>47.73447</v>
       </c>
       <c r="W18" t="n">
-        <v>-67.96913000000001</v>
+        <v>-65.98719</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=58</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1026</t>
         </is>
       </c>
     </row>
@@ -1828,11 +1828,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Little Sevogle River 1</t>
+          <t>Antinouri Lake West B</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>1021</v>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Pb, Zn</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1885,14 +1885,14 @@
         <v>45</v>
       </c>
       <c r="V19" t="n">
-        <v>47.0005</v>
+        <v>47.78921</v>
       </c>
       <c r="W19" t="n">
-        <v>-65.98999999999999</v>
+        <v>-65.99773</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=60</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1021</t>
         </is>
       </c>
     </row>
@@ -1902,11 +1902,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Taylor Village</t>
+          <t>Kenny Lake</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>57</v>
+        <v>1278</v>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ti</t>
+          <t>Pb, Zn</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1950,23 +1950,23 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T20" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U20" t="n">
         <v>45</v>
       </c>
       <c r="V20" t="n">
-        <v>45.93834</v>
+        <v>47.23226</v>
       </c>
       <c r="W20" t="n">
-        <v>-64.55385</v>
+        <v>-66.2908</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=57</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1278</t>
         </is>
       </c>
     </row>
@@ -1976,11 +1976,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>South Glassville</t>
+          <t>Sloop Cove</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1504</v>
+        <v>31</v>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2033,14 +2033,14 @@
         <v>45</v>
       </c>
       <c r="V21" t="n">
-        <v>46.48057</v>
+        <v>44.68722</v>
       </c>
       <c r="W21" t="n">
-        <v>-67.42028000000001</v>
+        <v>-66.87302</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1504</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=31</t>
         </is>
       </c>
     </row>
@@ -2050,11 +2050,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Red Pine Brook</t>
+          <t>South Glassville</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1408</v>
+        <v>1504</v>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2107,14 +2107,14 @@
         <v>45</v>
       </c>
       <c r="V22" t="n">
-        <v>47.4492</v>
+        <v>46.48057</v>
       </c>
       <c r="W22" t="n">
-        <v>-65.62412999999999</v>
+        <v>-67.42028000000001</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1408</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1504</t>
         </is>
       </c>
     </row>
@@ -2124,11 +2124,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pender Brook</t>
+          <t>Green Creek North</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>10</v>
+        <v>1334</v>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sb</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2181,14 +2181,14 @@
         <v>45</v>
       </c>
       <c r="V23" t="n">
-        <v>45.57888</v>
+        <v>45.79059</v>
       </c>
       <c r="W23" t="n">
-        <v>-66.30664</v>
+        <v>-64.44385</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=10</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1334</t>
         </is>
       </c>
     </row>
@@ -2198,11 +2198,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Evandale Stock *</t>
+          <t>Payne Brook</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>11</v>
+        <v>1036</v>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ag, Au, Cu</t>
+          <t>Ag, Pb, Zn</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2255,14 +2255,14 @@
         <v>45</v>
       </c>
       <c r="V24" t="n">
-        <v>45.58501</v>
+        <v>47.74032</v>
       </c>
       <c r="W24" t="n">
-        <v>-66.09690999999999</v>
+        <v>-65.91246</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=11</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1036</t>
         </is>
       </c>
     </row>
@@ -2272,11 +2272,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Joliffs Brook</t>
+          <t>Hayward Pinnacle</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>555</v>
+        <v>1575</v>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Zn</t>
+          <t>U</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2329,14 +2329,14 @@
         <v>43</v>
       </c>
       <c r="V25" t="n">
-        <v>45.73919</v>
+        <v>45.82761</v>
       </c>
       <c r="W25" t="n">
-        <v>-65.75996000000001</v>
+        <v>-64.9164</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=555</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1575</t>
         </is>
       </c>
     </row>
@@ -2346,11 +2346,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Martins Bluff</t>
+          <t>Crory Farm</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>562</v>
+        <v>605</v>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
@@ -2359,7 +2359,11 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Cu, Pb, Zn</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -2399,14 +2403,14 @@
         <v>43</v>
       </c>
       <c r="V26" t="n">
-        <v>46.93142</v>
+        <v>45.08058</v>
       </c>
       <c r="W26" t="n">
-        <v>-66.64663</v>
+        <v>-66.80913</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=562</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=605</t>
         </is>
       </c>
     </row>
@@ -2416,11 +2420,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ragged Falls &amp;quot;I&amp;quot;</t>
+          <t>Tennants Cove *</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>570</v>
+        <v>372</v>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
@@ -2431,7 +2435,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Th, U</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2464,23 +2468,23 @@
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T27" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U27" t="n">
         <v>43</v>
       </c>
       <c r="V27" t="n">
-        <v>45.2353</v>
+        <v>45.58694</v>
       </c>
       <c r="W27" t="n">
-        <v>-66.48052</v>
+        <v>-66.01414</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=570</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=372</t>
         </is>
       </c>
     </row>
@@ -2490,11 +2494,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Crory Farm</t>
+          <t>Ragged Falls &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>605</v>
+        <v>570</v>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
@@ -2505,7 +2509,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Th, U</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2538,23 +2542,23 @@
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T28" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U28" t="n">
         <v>43</v>
       </c>
       <c r="V28" t="n">
-        <v>45.08058</v>
+        <v>45.2353</v>
       </c>
       <c r="W28" t="n">
-        <v>-66.80913</v>
+        <v>-66.48052</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=605</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=570</t>
         </is>
       </c>
     </row>
@@ -2564,11 +2568,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Dickson Brook A,B,C</t>
+          <t>Martins Bluff</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>639</v>
+        <v>562</v>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
@@ -2577,11 +2581,7 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Cu</t>
-        </is>
-      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -2621,14 +2621,14 @@
         <v>43</v>
       </c>
       <c r="V29" t="n">
-        <v>45.58364</v>
+        <v>46.93142</v>
       </c>
       <c r="W29" t="n">
-        <v>-64.98524</v>
+        <v>-66.64663</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=639</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=562</t>
         </is>
       </c>
     </row>
@@ -2638,11 +2638,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Three Bridge Brook East *</t>
+          <t>Joliffs Brook</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>793</v>
+        <v>555</v>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ag, Au, Pb, Zn</t>
+          <t>Zn</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2686,23 +2686,23 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T30" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U30" t="n">
         <v>43</v>
       </c>
       <c r="V30" t="n">
-        <v>45.49419</v>
+        <v>45.73919</v>
       </c>
       <c r="W30" t="n">
-        <v>-66.48581</v>
+        <v>-65.75996000000001</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=793</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=555</t>
         </is>
       </c>
     </row>
@@ -2712,11 +2712,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Eel Ground</t>
+          <t>Dickson Brook A,B,C</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>746</v>
+        <v>639</v>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2769,14 +2769,14 @@
         <v>43</v>
       </c>
       <c r="V31" t="n">
-        <v>46.96447</v>
+        <v>45.58364</v>
       </c>
       <c r="W31" t="n">
-        <v>-65.59441</v>
+        <v>-64.98524</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=746</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=639</t>
         </is>
       </c>
     </row>
@@ -2786,11 +2786,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Halls Hill</t>
+          <t>Quaco Road &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1324</v>
+        <v>678</v>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cu, Zn</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2843,14 +2843,14 @@
         <v>43</v>
       </c>
       <c r="V32" t="n">
-        <v>45.96809</v>
+        <v>45.38336</v>
       </c>
       <c r="W32" t="n">
-        <v>-64.16996</v>
+        <v>-65.74996</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1324</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=678</t>
         </is>
       </c>
     </row>
@@ -2860,11 +2860,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Jacquet River M</t>
+          <t>Gowland Mountain *</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>955</v>
+        <v>643</v>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ba, Cu</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2917,14 +2917,14 @@
         <v>43</v>
       </c>
       <c r="V33" t="n">
-        <v>47.82559</v>
+        <v>45.81975</v>
       </c>
       <c r="W33" t="n">
-        <v>-66.01662</v>
+        <v>-65.0483</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=955</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=643</t>
         </is>
       </c>
     </row>
@@ -2934,11 +2934,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Letang Harbour North</t>
+          <t>Deed Brook</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1291</v>
+        <v>717</v>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2982,23 +2982,23 @@
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T34" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U34" t="n">
         <v>43</v>
       </c>
       <c r="V34" t="n">
-        <v>45.08726</v>
+        <v>45.78808</v>
       </c>
       <c r="W34" t="n">
-        <v>-66.7833</v>
+        <v>-64.85692</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1291</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=717</t>
         </is>
       </c>
     </row>
@@ -3008,11 +3008,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Dennis Stream - Upper &amp;quot;I&amp;quot;</t>
+          <t>Irving</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1306</v>
+        <v>1238</v>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
@@ -3021,7 +3021,11 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Co, Cu, Ni</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -3052,23 +3056,23 @@
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T35" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="U35" t="n">
         <v>43</v>
       </c>
       <c r="V35" t="n">
-        <v>45.22199</v>
+        <v>45.19116</v>
       </c>
       <c r="W35" t="n">
-        <v>-67.27109</v>
+        <v>-67.25942000000001</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1306</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1238</t>
         </is>
       </c>
     </row>
@@ -3078,11 +3082,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Gowland Mountain *</t>
+          <t>St Stephen Ni - O Zone &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>643</v>
+        <v>1236</v>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
@@ -3093,7 +3097,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Co, Cu, Ni</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3126,23 +3130,23 @@
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T36" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U36" t="n">
         <v>43</v>
       </c>
       <c r="V36" t="n">
-        <v>45.81975</v>
+        <v>45.23088</v>
       </c>
       <c r="W36" t="n">
-        <v>-65.0483</v>
+        <v>-67.27692</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=643</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1236</t>
         </is>
       </c>
     </row>
@@ -3152,11 +3156,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Quaco Road &amp;quot;I&amp;quot;</t>
+          <t>Memramcook Gold &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>678</v>
+        <v>723</v>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
@@ -3167,7 +3171,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3200,23 +3204,23 @@
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T37" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U37" t="n">
         <v>43</v>
       </c>
       <c r="V37" t="n">
-        <v>45.38336</v>
+        <v>45.96531</v>
       </c>
       <c r="W37" t="n">
-        <v>-65.74996</v>
+        <v>-64.53885</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=678</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=723</t>
         </is>
       </c>
     </row>
@@ -3226,11 +3230,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>St Stephen Ni - O Zone &amp;quot;I&amp;quot;</t>
+          <t>Halls Hill</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1236</v>
+        <v>1324</v>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
@@ -3241,7 +3245,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Co, Cu, Ni</t>
+          <t>Cu, Zn</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3274,23 +3278,23 @@
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T38" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U38" t="n">
         <v>43</v>
       </c>
       <c r="V38" t="n">
-        <v>45.23088</v>
+        <v>45.96809</v>
       </c>
       <c r="W38" t="n">
-        <v>-67.27692</v>
+        <v>-64.16996</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1236</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1324</t>
         </is>
       </c>
     </row>
@@ -3300,11 +3304,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Irving</t>
+          <t>Letang Harbour North</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1238</v>
+        <v>1291</v>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
@@ -3315,7 +3319,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Co, Cu, Ni</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3348,23 +3352,23 @@
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T39" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U39" t="n">
         <v>43</v>
       </c>
       <c r="V39" t="n">
-        <v>45.19116</v>
+        <v>45.08726</v>
       </c>
       <c r="W39" t="n">
-        <v>-67.25942000000001</v>
+        <v>-66.7833</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1238</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1291</t>
         </is>
       </c>
     </row>
@@ -3374,11 +3378,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Pabineau River North Manganese</t>
+          <t>Dennis Stream - Upper &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
@@ -3387,11 +3391,7 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Mn</t>
-        </is>
-      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -3422,23 +3422,23 @@
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T40" t="n">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="U40" t="n">
         <v>43</v>
       </c>
       <c r="V40" t="n">
-        <v>47.49558</v>
+        <v>45.22199</v>
       </c>
       <c r="W40" t="n">
-        <v>-65.90329</v>
+        <v>-67.27109</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1272</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1306</t>
         </is>
       </c>
     </row>
@@ -3448,11 +3448,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Bass River Cu-Ni</t>
+          <t>Jacquet River M</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1254</v>
+        <v>955</v>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cu, Ni</t>
+          <t>Ba, Cu</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3505,14 +3505,14 @@
         <v>43</v>
       </c>
       <c r="V41" t="n">
-        <v>47.46421</v>
+        <v>47.82559</v>
       </c>
       <c r="W41" t="n">
-        <v>-65.56607</v>
+        <v>-66.01662</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1254</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=955</t>
         </is>
       </c>
     </row>
@@ -3522,11 +3522,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Memramcook Gold &amp;quot;I&amp;quot;</t>
+          <t>Eel Ground</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>723</v>
+        <v>746</v>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
@@ -3537,7 +3537,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3570,23 +3570,23 @@
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T42" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U42" t="n">
         <v>43</v>
       </c>
       <c r="V42" t="n">
-        <v>45.96531</v>
+        <v>46.96447</v>
       </c>
       <c r="W42" t="n">
-        <v>-64.53885</v>
+        <v>-65.59441</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=723</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=746</t>
         </is>
       </c>
     </row>
@@ -3596,11 +3596,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Deed Brook</t>
+          <t>Three Bridge Brook East *</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>717</v>
+        <v>793</v>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Ag, Au, Pb, Zn</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3644,23 +3644,23 @@
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T43" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="U43" t="n">
         <v>43</v>
       </c>
       <c r="V43" t="n">
-        <v>45.78808</v>
+        <v>45.49419</v>
       </c>
       <c r="W43" t="n">
-        <v>-64.85692</v>
+        <v>-66.48581</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=717</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=793</t>
         </is>
       </c>
     </row>
@@ -3670,11 +3670,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Hayward Pinnacle</t>
+          <t>Pabineau River North Manganese</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1575</v>
+        <v>1272</v>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3718,23 +3718,23 @@
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T44" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U44" t="n">
         <v>43</v>
       </c>
       <c r="V44" t="n">
-        <v>45.82761</v>
+        <v>47.49558</v>
       </c>
       <c r="W44" t="n">
-        <v>-64.9164</v>
+        <v>-65.90329</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1575</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1272</t>
         </is>
       </c>
     </row>
@@ -3744,11 +3744,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Tennants Cove *</t>
+          <t>Bass River Cu-Ni</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>372</v>
+        <v>1254</v>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Cu, Ni</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3801,14 +3801,14 @@
         <v>43</v>
       </c>
       <c r="V45" t="n">
-        <v>45.58694</v>
+        <v>47.46421</v>
       </c>
       <c r="W45" t="n">
-        <v>-66.01414</v>
+        <v>-65.56607</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=372</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1254</t>
         </is>
       </c>
     </row>
@@ -3892,11 +3892,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Brunswick No. 12</t>
+          <t>Lower Birch Island</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>54</v>
+        <v>172</v>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Ba, Fe, Mn</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>88.8 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -3949,14 +3949,14 @@
         <v>38</v>
       </c>
       <c r="V47" t="n">
-        <v>47.47889</v>
+        <v>46.56864</v>
       </c>
       <c r="W47" t="n">
-        <v>-65.89218</v>
+        <v>-66.57080000000001</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=54</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=172</t>
         </is>
       </c>
     </row>
@@ -3966,11 +3966,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Anomaly 102 &amp;quot;I&amp;quot;</t>
+          <t>Nigadoo River Mine</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1151</v>
+        <v>128</v>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Ag, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>1.1 Mt</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -4023,14 +4023,14 @@
         <v>38</v>
       </c>
       <c r="V48" t="n">
-        <v>46.47865</v>
+        <v>47.73307</v>
       </c>
       <c r="W48" t="n">
-        <v>-66.72996999999999</v>
+        <v>-65.80642</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1151</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=128</t>
         </is>
       </c>
     </row>
@@ -4040,11 +4040,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nigadoo River Mine</t>
+          <t>Austin Brook</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>128</v>
+        <v>69</v>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
@@ -4055,7 +4055,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ag, Cu, Pb, Zn</t>
+          <t>Ag, Fe, Pb, Zn</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>1.1 Mt</t>
+          <t>164 kt</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -4088,23 +4088,23 @@
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T49" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U49" t="n">
         <v>38</v>
       </c>
       <c r="V49" t="n">
-        <v>47.73307</v>
+        <v>47.39779</v>
       </c>
       <c r="W49" t="n">
-        <v>-65.80642</v>
+        <v>-65.82302</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=128</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=69</t>
         </is>
       </c>
     </row>
@@ -4114,11 +4114,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Lower Birch Island</t>
+          <t>Brunswick No. 12</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>172</v>
+        <v>54</v>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ba, Fe, Mn</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>88.8 Mt</t>
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
@@ -4171,14 +4171,14 @@
         <v>38</v>
       </c>
       <c r="V50" t="n">
-        <v>46.56864</v>
+        <v>47.47889</v>
       </c>
       <c r="W50" t="n">
-        <v>-66.57080000000001</v>
+        <v>-65.89218</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=172</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=54</t>
         </is>
       </c>
     </row>
@@ -4188,11 +4188,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Austin Brook</t>
+          <t>Anomaly 102 &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>69</v>
+        <v>1151</v>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ag, Fe, Pb, Zn</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>164 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
@@ -4236,23 +4236,23 @@
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T51" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U51" t="n">
         <v>38</v>
       </c>
       <c r="V51" t="n">
-        <v>47.39779</v>
+        <v>46.47865</v>
       </c>
       <c r="W51" t="n">
-        <v>-65.82302</v>
+        <v>-66.72996999999999</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=69</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1151</t>
         </is>
       </c>
     </row>
@@ -4262,11 +4262,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Taylors Island</t>
+          <t>Black Point</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>32</v>
+        <v>1333</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Pb, Zn</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4315,14 +4315,14 @@
         <v>37</v>
       </c>
       <c r="V52" t="n">
-        <v>45.22336</v>
+        <v>45.79448</v>
       </c>
       <c r="W52" t="n">
-        <v>-66.12747</v>
+        <v>-64.42218</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=32</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1333</t>
         </is>
       </c>
     </row>
@@ -4332,11 +4332,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Henry Lake</t>
+          <t>Jeanne Mance</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1510</v>
+        <v>1249</v>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
@@ -4385,14 +4385,14 @@
         <v>37</v>
       </c>
       <c r="V53" t="n">
-        <v>45.39473</v>
+        <v>47.36337</v>
       </c>
       <c r="W53" t="n">
-        <v>-65.60417</v>
+        <v>-65.44329999999999</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1510</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1249</t>
         </is>
       </c>
     </row>
@@ -4402,11 +4402,11 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Little Nictor Lake</t>
+          <t>Bulls Creek 2</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>94</v>
+        <v>1072</v>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
@@ -4417,7 +4417,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Zn</t>
+          <t>Ag, Au, Co, Cu</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4446,23 +4446,23 @@
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T54" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U54" t="n">
         <v>37</v>
       </c>
       <c r="V54" t="n">
-        <v>47.40642</v>
+        <v>46.08809</v>
       </c>
       <c r="W54" t="n">
-        <v>-66.84441</v>
+        <v>-67.56498000000001</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=94</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1072</t>
         </is>
       </c>
     </row>
@@ -4472,11 +4472,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Bulls Creek 2</t>
+          <t>Bulls Creek 1</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
@@ -4487,7 +4487,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ag, Au, Co, Cu</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4516,23 +4516,23 @@
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T55" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U55" t="n">
         <v>37</v>
       </c>
       <c r="V55" t="n">
-        <v>46.08809</v>
+        <v>46.08421</v>
       </c>
       <c r="W55" t="n">
-        <v>-67.56498000000001</v>
+        <v>-67.57774999999999</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1072</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1071</t>
         </is>
       </c>
     </row>
@@ -4542,11 +4542,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Bulls Creek 1</t>
+          <t>Little Nictor Lake</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1071</v>
+        <v>94</v>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
@@ -4557,7 +4557,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Zn</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4595,14 +4595,14 @@
         <v>37</v>
       </c>
       <c r="V56" t="n">
-        <v>46.08421</v>
+        <v>47.40642</v>
       </c>
       <c r="W56" t="n">
-        <v>-67.57774999999999</v>
+        <v>-66.84441</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1071</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=94</t>
         </is>
       </c>
     </row>
@@ -4612,11 +4612,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Church Showing</t>
+          <t>Gaspereau River</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>726</v>
+        <v>1300</v>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
@@ -4665,14 +4665,14 @@
         <v>37</v>
       </c>
       <c r="V57" t="n">
-        <v>44.88974</v>
+        <v>46.08059</v>
       </c>
       <c r="W57" t="n">
-        <v>-66.95386000000001</v>
+        <v>-64.20996</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=726</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1300</t>
         </is>
       </c>
     </row>
@@ -4682,11 +4682,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Jeanne Mance</t>
+          <t>Church Showing</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1249</v>
+        <v>726</v>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
@@ -4735,14 +4735,14 @@
         <v>37</v>
       </c>
       <c r="V58" t="n">
-        <v>47.36337</v>
+        <v>44.88974</v>
       </c>
       <c r="W58" t="n">
-        <v>-65.44329999999999</v>
+        <v>-66.95386000000001</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1249</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=726</t>
         </is>
       </c>
     </row>
@@ -4752,11 +4752,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Black Point</t>
+          <t>Basaltic Island West *</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1333</v>
+        <v>1347</v>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
@@ -4805,14 +4805,14 @@
         <v>37</v>
       </c>
       <c r="V59" t="n">
-        <v>45.79448</v>
+        <v>45.1392</v>
       </c>
       <c r="W59" t="n">
-        <v>-64.42218</v>
+        <v>-66.92413999999999</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1333</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1347</t>
         </is>
       </c>
     </row>
@@ -4822,11 +4822,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Quispamsis Exit</t>
+          <t>Grande Anse</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1338</v>
+        <v>1370</v>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ag, Au, Cu, Pb</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4875,14 +4875,14 @@
         <v>37</v>
       </c>
       <c r="V60" t="n">
-        <v>45.42378</v>
+        <v>45.79615</v>
       </c>
       <c r="W60" t="n">
-        <v>-65.92708</v>
+        <v>-64.50107</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1338</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1370</t>
         </is>
       </c>
     </row>
@@ -4892,11 +4892,11 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Basaltic Island West *</t>
+          <t>Johnson Mills</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1347</v>
+        <v>1371</v>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pb, Zn</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4945,14 +4945,14 @@
         <v>37</v>
       </c>
       <c r="V61" t="n">
-        <v>45.1392</v>
+        <v>45.76365</v>
       </c>
       <c r="W61" t="n">
-        <v>-66.92413999999999</v>
+        <v>-64.52218000000001</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1347</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1371</t>
         </is>
       </c>
     </row>
@@ -4962,11 +4962,11 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Frye Island North</t>
+          <t>Moores Mills #2</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1353</v>
+        <v>1374</v>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
@@ -4977,7 +4977,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ag, Cu, F, Pb, Sb, Zn</t>
+          <t>Ag, Cu, Pb</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5006,23 +5006,23 @@
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T62" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U62" t="n">
         <v>37</v>
       </c>
       <c r="V62" t="n">
-        <v>45.04753</v>
+        <v>45.29977</v>
       </c>
       <c r="W62" t="n">
-        <v>-66.84469</v>
+        <v>-67.2533</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1353</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1374</t>
         </is>
       </c>
     </row>
@@ -5032,11 +5032,11 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Gaspereau River</t>
+          <t>Scoudouc River Quarry</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1300</v>
+        <v>1367</v>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
@@ -5047,7 +5047,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Pb, Zn</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5085,14 +5085,14 @@
         <v>37</v>
       </c>
       <c r="V63" t="n">
-        <v>46.08059</v>
+        <v>46.19643</v>
       </c>
       <c r="W63" t="n">
-        <v>-64.20996</v>
+        <v>-64.54385000000001</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1300</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1367</t>
         </is>
       </c>
     </row>
@@ -5102,11 +5102,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Cape Maringouin # 1</t>
+          <t>Black Point North</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1360</v>
+        <v>1368</v>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cu, Pb</t>
+          <t>Cu, Zn</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5155,14 +5155,14 @@
         <v>37</v>
       </c>
       <c r="V64" t="n">
-        <v>45.73532</v>
+        <v>45.80448</v>
       </c>
       <c r="W64" t="n">
-        <v>-64.54191</v>
+        <v>-64.41634999999999</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1360</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1368</t>
         </is>
       </c>
     </row>
@@ -5172,11 +5172,11 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Cape Maringouin # 2</t>
+          <t>Shediac River # 2</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ag, Cu, Pb, Zn</t>
+          <t>As</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5225,14 +5225,14 @@
         <v>37</v>
       </c>
       <c r="V65" t="n">
-        <v>45.73782</v>
+        <v>46.2417</v>
       </c>
       <c r="W65" t="n">
-        <v>-64.53246</v>
+        <v>-64.6858</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1361</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1365</t>
         </is>
       </c>
     </row>
@@ -5242,11 +5242,11 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Digdeguash Cu *</t>
+          <t>Rockport Shore</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1344</v>
+        <v>1362</v>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
@@ -5257,7 +5257,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cu, Zn</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5295,14 +5295,14 @@
         <v>37</v>
       </c>
       <c r="V66" t="n">
-        <v>45.18698</v>
+        <v>45.72365</v>
       </c>
       <c r="W66" t="n">
-        <v>-66.93774999999999</v>
+        <v>-64.50663</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1344</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1362</t>
         </is>
       </c>
     </row>
@@ -5312,11 +5312,11 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Rockport Shore</t>
+          <t>Cape Maringouin # 2</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
@@ -5327,7 +5327,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Ag, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5365,14 +5365,14 @@
         <v>37</v>
       </c>
       <c r="V67" t="n">
-        <v>45.72365</v>
+        <v>45.73782</v>
       </c>
       <c r="W67" t="n">
-        <v>-64.50663</v>
+        <v>-64.53246</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1362</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1361</t>
         </is>
       </c>
     </row>
@@ -5382,11 +5382,11 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Black Point North</t>
+          <t>Cape Maringouin # 1</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1368</v>
+        <v>1360</v>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cu, Zn</t>
+          <t>Cu, Pb</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5435,14 +5435,14 @@
         <v>37</v>
       </c>
       <c r="V68" t="n">
-        <v>45.80448</v>
+        <v>45.73532</v>
       </c>
       <c r="W68" t="n">
-        <v>-64.41634999999999</v>
+        <v>-64.54191</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1368</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1360</t>
         </is>
       </c>
     </row>
@@ -5452,11 +5452,11 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Grande Anse</t>
+          <t>Frye Island North</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1370</v>
+        <v>1353</v>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
@@ -5467,7 +5467,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Ag, Cu, F, Pb, Sb, Zn</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5505,14 +5505,14 @@
         <v>37</v>
       </c>
       <c r="V69" t="n">
-        <v>45.79615</v>
+        <v>45.04753</v>
       </c>
       <c r="W69" t="n">
-        <v>-64.50107</v>
+        <v>-66.84469</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1370</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1353</t>
         </is>
       </c>
     </row>
@@ -5522,11 +5522,11 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Sinclair Hill</t>
+          <t>Quispamsis Exit</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>9</v>
+        <v>1338</v>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
@@ -5537,7 +5537,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ag, Au, Cu</t>
+          <t>Ag, Au, Cu, Pb</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5575,14 +5575,14 @@
         <v>37</v>
       </c>
       <c r="V70" t="n">
-        <v>45.63113</v>
+        <v>45.42378</v>
       </c>
       <c r="W70" t="n">
-        <v>-64.92274999999999</v>
+        <v>-65.92708</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=9</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1338</t>
         </is>
       </c>
     </row>
@@ -5592,11 +5592,11 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Scoudouc River Quarry</t>
+          <t>Digdeguash Cu *</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1367</v>
+        <v>1344</v>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pb, Zn</t>
+          <t>Cu, Zn</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5645,14 +5645,14 @@
         <v>37</v>
       </c>
       <c r="V71" t="n">
-        <v>46.19643</v>
+        <v>45.18698</v>
       </c>
       <c r="W71" t="n">
-        <v>-64.54385000000001</v>
+        <v>-66.93774999999999</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1367</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1344</t>
         </is>
       </c>
     </row>
@@ -5662,11 +5662,11 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Shediac River # 2</t>
+          <t>Sinclair Hill</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1365</v>
+        <v>9</v>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
@@ -5677,7 +5677,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>As</t>
+          <t>Ag, Au, Cu</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5715,14 +5715,14 @@
         <v>37</v>
       </c>
       <c r="V72" t="n">
-        <v>46.2417</v>
+        <v>45.63113</v>
       </c>
       <c r="W72" t="n">
-        <v>-64.6858</v>
+        <v>-64.92274999999999</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1365</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=9</t>
         </is>
       </c>
     </row>
@@ -5732,11 +5732,11 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Johnson Mills</t>
+          <t>Taylors Island</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1371</v>
+        <v>32</v>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
@@ -5747,7 +5747,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5785,14 +5785,14 @@
         <v>37</v>
       </c>
       <c r="V73" t="n">
-        <v>45.76365</v>
+        <v>45.22336</v>
       </c>
       <c r="W73" t="n">
-        <v>-64.52218000000001</v>
+        <v>-66.12747</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1371</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=32</t>
         </is>
       </c>
     </row>
@@ -5802,11 +5802,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Moores Mills #2</t>
+          <t>Henry Lake</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1374</v>
+        <v>1510</v>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
@@ -5817,7 +5817,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ag, Cu, Pb</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5846,23 +5846,23 @@
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T74" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U74" t="n">
         <v>37</v>
       </c>
       <c r="V74" t="n">
-        <v>45.29977</v>
+        <v>45.39473</v>
       </c>
       <c r="W74" t="n">
-        <v>-67.2533</v>
+        <v>-65.60417</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1374</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1510</t>
         </is>
       </c>
     </row>
@@ -5942,11 +5942,11 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Jacquet River Cu - A</t>
+          <t>Four Mile Lake B</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>462</v>
+        <v>1175</v>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr"/>
@@ -5955,11 +5955,7 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Cu</t>
-        </is>
-      </c>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -5995,14 +5991,14 @@
         <v>35</v>
       </c>
       <c r="V76" t="n">
-        <v>47.85476</v>
+        <v>46.63643</v>
       </c>
       <c r="W76" t="n">
-        <v>-66.01551000000001</v>
+        <v>-66.58274</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=462</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1175</t>
         </is>
       </c>
     </row>
@@ -6012,11 +6008,11 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Brewers Mills</t>
+          <t>Caledonia Mountain</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>904</v>
+        <v>1609</v>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
@@ -6027,7 +6023,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>As, Au</t>
+          <t>Ti, V</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6056,23 +6052,23 @@
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T77" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U77" t="n">
         <v>35</v>
       </c>
       <c r="V77" t="n">
-        <v>46.0692</v>
+        <v>45.8698</v>
       </c>
       <c r="W77" t="n">
-        <v>-67.0283</v>
+        <v>-64.73159</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=904</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1609</t>
         </is>
       </c>
     </row>
@@ -6082,11 +6078,11 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Jacquet River K</t>
+          <t>Jacquet River Cu - Mitchell Rd</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>973</v>
+        <v>461</v>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
@@ -6131,14 +6127,14 @@
         <v>35</v>
       </c>
       <c r="V78" t="n">
-        <v>47.83142</v>
+        <v>47.82725</v>
       </c>
       <c r="W78" t="n">
-        <v>-66.03246</v>
+        <v>-66.00606999999999</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=973</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=461</t>
         </is>
       </c>
     </row>
@@ -6148,11 +6144,11 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Caledonia Mountain</t>
+          <t>Jacquet River Cu - A</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1609</v>
+        <v>462</v>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
@@ -6163,7 +6159,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ti, V</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6192,23 +6188,23 @@
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T79" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U79" t="n">
         <v>35</v>
       </c>
       <c r="V79" t="n">
-        <v>45.8698</v>
+        <v>47.85476</v>
       </c>
       <c r="W79" t="n">
-        <v>-64.73159</v>
+        <v>-66.01551000000001</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1609</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=462</t>
         </is>
       </c>
     </row>
@@ -6218,11 +6214,11 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Centreville &amp;quot;I&amp;quot;</t>
+          <t>Dumfries *</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>263</v>
+        <v>535</v>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
@@ -6233,7 +6229,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -6271,14 +6267,14 @@
         <v>35</v>
       </c>
       <c r="V80" t="n">
-        <v>46.44281</v>
+        <v>45.95029</v>
       </c>
       <c r="W80" t="n">
-        <v>-67.6808</v>
+        <v>-67.12273999999999</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=263</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=535</t>
         </is>
       </c>
     </row>
@@ -6288,11 +6284,11 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Waterville Prospect &amp;quot;I&amp;quot;</t>
+          <t>Letete Mine</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1413</v>
+        <v>311</v>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
@@ -6303,12 +6299,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Au, Sb</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I81" t="b">
@@ -6319,11 +6315,15 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>1.9 Mt</t>
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="n">
         <v>0</v>
@@ -6332,23 +6332,23 @@
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T81" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U81" t="n">
         <v>35</v>
       </c>
       <c r="V81" t="n">
-        <v>46.05921</v>
+        <v>45.06529</v>
       </c>
       <c r="W81" t="n">
-        <v>-67.30663</v>
+        <v>-66.91136</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1413</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=311</t>
         </is>
       </c>
     </row>
@@ -6358,11 +6358,11 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Indian Brook</t>
+          <t>Silver Island</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>262</v>
+        <v>586</v>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
@@ -6371,7 +6371,11 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Ag, Pb, Zn</t>
+        </is>
+      </c>
       <c r="H82" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -6407,14 +6411,14 @@
         <v>35</v>
       </c>
       <c r="V82" t="n">
-        <v>46.73226</v>
+        <v>45.12114</v>
       </c>
       <c r="W82" t="n">
-        <v>-67.42440999999999</v>
+        <v>-66.8458</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=262</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=586</t>
         </is>
       </c>
     </row>
@@ -6424,11 +6428,11 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Brummagen Brook Bog</t>
+          <t>Forty Five River &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>188</v>
+        <v>647</v>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
@@ -6439,7 +6443,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -6468,23 +6472,23 @@
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T83" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U83" t="n">
         <v>35</v>
       </c>
       <c r="V83" t="n">
-        <v>46.39003</v>
+        <v>45.74309</v>
       </c>
       <c r="W83" t="n">
-        <v>-67.29386</v>
+        <v>-64.93053</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=188</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=647</t>
         </is>
       </c>
     </row>
@@ -6494,11 +6498,11 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Pecks Point South</t>
+          <t>Phyllis Creek &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1329</v>
+        <v>655</v>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
@@ -6509,7 +6513,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ag, Cu, Pb, Zn</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -6547,14 +6551,14 @@
         <v>35</v>
       </c>
       <c r="V84" t="n">
-        <v>45.73809</v>
+        <v>45.94808</v>
       </c>
       <c r="W84" t="n">
-        <v>-64.48524</v>
+        <v>-66.69441</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1329</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=655</t>
         </is>
       </c>
     </row>
@@ -6564,11 +6568,11 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Dumfries *</t>
+          <t>Pirate Lake</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>535</v>
+        <v>516</v>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
@@ -6579,7 +6583,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -6617,14 +6621,14 @@
         <v>35</v>
       </c>
       <c r="V85" t="n">
-        <v>45.95029</v>
+        <v>45.72697</v>
       </c>
       <c r="W85" t="n">
-        <v>-67.12273999999999</v>
+        <v>-67.67525000000001</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=535</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=516</t>
         </is>
       </c>
     </row>
@@ -6634,11 +6638,11 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Pirate Lake</t>
+          <t>Pecks Point South</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>516</v>
+        <v>1329</v>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
@@ -6649,7 +6653,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Ag, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6687,14 +6691,14 @@
         <v>35</v>
       </c>
       <c r="V86" t="n">
-        <v>45.72697</v>
+        <v>45.73809</v>
       </c>
       <c r="W86" t="n">
-        <v>-67.67525000000001</v>
+        <v>-64.48524</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=516</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1329</t>
         </is>
       </c>
     </row>
@@ -6704,11 +6708,11 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Elmtree 7B</t>
+          <t>East Quoddy Head</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>854</v>
+        <v>737</v>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
@@ -6719,7 +6723,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cu, Ni</t>
+          <t>Pb</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -6748,23 +6752,23 @@
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr"/>
       <c r="S87" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T87" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U87" t="n">
         <v>35</v>
       </c>
       <c r="V87" t="n">
-        <v>47.78253</v>
+        <v>44.95391</v>
       </c>
       <c r="W87" t="n">
-        <v>-65.87246</v>
+        <v>-66.90831</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=854</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=737</t>
         </is>
       </c>
     </row>
@@ -6774,11 +6778,11 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Four Mile Lake B</t>
+          <t>Meadow Brook Cove</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1175</v>
+        <v>727</v>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
@@ -6787,7 +6791,11 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Fe, Zn</t>
+        </is>
+      </c>
       <c r="H88" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -6823,14 +6831,14 @@
         <v>35</v>
       </c>
       <c r="V88" t="n">
-        <v>46.63643</v>
+        <v>44.88281</v>
       </c>
       <c r="W88" t="n">
-        <v>-66.58274</v>
+        <v>-66.90774999999999</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1175</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=727</t>
         </is>
       </c>
     </row>
@@ -6840,11 +6848,11 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Meadow Brook Cove</t>
+          <t>Jacquet River K</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>727</v>
+        <v>973</v>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
@@ -6853,11 +6861,7 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Fe, Zn</t>
-        </is>
-      </c>
+      <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -6893,14 +6897,14 @@
         <v>35</v>
       </c>
       <c r="V89" t="n">
-        <v>44.88281</v>
+        <v>47.83142</v>
       </c>
       <c r="W89" t="n">
-        <v>-66.90774999999999</v>
+        <v>-66.03246</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=727</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=973</t>
         </is>
       </c>
     </row>
@@ -6910,11 +6914,11 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>East Quoddy Head</t>
+          <t>Little Southwest Miramichi</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>737</v>
+        <v>621</v>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr"/>
@@ -6923,11 +6927,7 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Pb</t>
-        </is>
-      </c>
+      <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -6963,14 +6963,14 @@
         <v>35</v>
       </c>
       <c r="V90" t="n">
-        <v>44.95391</v>
+        <v>46.89643</v>
       </c>
       <c r="W90" t="n">
-        <v>-66.90831</v>
+        <v>-66.34998</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=737</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=621</t>
         </is>
       </c>
     </row>
@@ -6980,11 +6980,11 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Silver Island</t>
+          <t>Waterside Manganese</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>586</v>
+        <v>645</v>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
@@ -6995,7 +6995,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ag, Pb, Zn</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -7024,23 +7024,23 @@
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr"/>
       <c r="S91" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T91" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U91" t="n">
         <v>35</v>
       </c>
       <c r="V91" t="n">
-        <v>45.12114</v>
+        <v>45.63058</v>
       </c>
       <c r="W91" t="n">
-        <v>-66.8458</v>
+        <v>-64.82858</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=586</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=645</t>
         </is>
       </c>
     </row>
@@ -7050,11 +7050,11 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Phyllis Creek &amp;quot;I&amp;quot;</t>
+          <t>Brewers Mills</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>655</v>
+        <v>904</v>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr"/>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>As, Au</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -7103,14 +7103,14 @@
         <v>35</v>
       </c>
       <c r="V92" t="n">
-        <v>45.94808</v>
+        <v>46.0692</v>
       </c>
       <c r="W92" t="n">
-        <v>-66.69441</v>
+        <v>-67.0283</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=655</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=904</t>
         </is>
       </c>
     </row>
@@ -7120,11 +7120,11 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Jacquet River Cu - Mitchell Rd</t>
+          <t>Elmtree 7B</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>461</v>
+        <v>854</v>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
@@ -7133,7 +7133,11 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Cu, Ni</t>
+        </is>
+      </c>
       <c r="H93" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -7160,23 +7164,23 @@
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr"/>
       <c r="S93" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T93" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U93" t="n">
         <v>35</v>
       </c>
       <c r="V93" t="n">
-        <v>47.82725</v>
+        <v>47.78253</v>
       </c>
       <c r="W93" t="n">
-        <v>-66.00606999999999</v>
+        <v>-65.87246</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=461</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=854</t>
         </is>
       </c>
     </row>
@@ -7186,11 +7190,11 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Maple Ridge</t>
+          <t>MacIntosh Brook</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>152</v>
+        <v>192</v>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
@@ -7201,7 +7205,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Mo, W</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -7230,23 +7234,23 @@
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr"/>
       <c r="S94" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T94" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U94" t="n">
         <v>35</v>
       </c>
       <c r="V94" t="n">
-        <v>46.10003</v>
+        <v>46.35335</v>
       </c>
       <c r="W94" t="n">
-        <v>-67.21413</v>
+        <v>-67.27636</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=152</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=192</t>
         </is>
       </c>
     </row>
@@ -7256,11 +7260,11 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>MacIntosh Brook</t>
+          <t>Maple Ridge</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>192</v>
+        <v>152</v>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
@@ -7271,7 +7275,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Mo, W</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -7300,23 +7304,23 @@
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="inlineStr"/>
       <c r="S95" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T95" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U95" t="n">
         <v>35</v>
       </c>
       <c r="V95" t="n">
-        <v>46.35335</v>
+        <v>46.10003</v>
       </c>
       <c r="W95" t="n">
-        <v>-67.27636</v>
+        <v>-67.21413</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=192</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=152</t>
         </is>
       </c>
     </row>
@@ -7326,11 +7330,11 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Letete Mine</t>
+          <t>Indian Brook</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>311</v>
+        <v>262</v>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
@@ -7339,14 +7343,10 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Cu</t>
-        </is>
-      </c>
+      <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I96" t="b">
@@ -7357,15 +7357,11 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>1.9 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
+      <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="n">
         <v>0</v>
@@ -7374,23 +7370,23 @@
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr"/>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T96" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U96" t="n">
         <v>35</v>
       </c>
       <c r="V96" t="n">
-        <v>45.06529</v>
+        <v>46.73226</v>
       </c>
       <c r="W96" t="n">
-        <v>-66.91136</v>
+        <v>-67.42440999999999</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=311</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=262</t>
         </is>
       </c>
     </row>
@@ -7400,11 +7396,11 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Forty Five River &amp;quot;I&amp;quot;</t>
+          <t>Centreville &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>647</v>
+        <v>263</v>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
@@ -7415,7 +7411,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -7444,23 +7440,23 @@
       <c r="Q97" t="inlineStr"/>
       <c r="R97" t="inlineStr"/>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T97" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U97" t="n">
         <v>35</v>
       </c>
       <c r="V97" t="n">
-        <v>45.74309</v>
+        <v>46.44281</v>
       </c>
       <c r="W97" t="n">
-        <v>-64.93053</v>
+        <v>-67.6808</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=647</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=263</t>
         </is>
       </c>
     </row>
@@ -7470,11 +7466,11 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Waterside Manganese</t>
+          <t>Brummagen Brook Bog</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>645</v>
+        <v>188</v>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
@@ -7514,23 +7510,23 @@
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr"/>
       <c r="S98" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T98" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U98" t="n">
         <v>35</v>
       </c>
       <c r="V98" t="n">
-        <v>45.63058</v>
+        <v>46.39003</v>
       </c>
       <c r="W98" t="n">
-        <v>-64.82858</v>
+        <v>-67.29386</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=645</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=188</t>
         </is>
       </c>
     </row>
@@ -7540,11 +7536,11 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Little Southwest Miramichi</t>
+          <t>Waterville Prospect &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>621</v>
+        <v>1413</v>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr"/>
@@ -7553,7 +7549,11 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Au, Sb</t>
+        </is>
+      </c>
       <c r="H99" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -7589,14 +7589,14 @@
         <v>35</v>
       </c>
       <c r="V99" t="n">
-        <v>46.89643</v>
+        <v>46.05921</v>
       </c>
       <c r="W99" t="n">
-        <v>-66.34998</v>
+        <v>-67.30663</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=621</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1413</t>
         </is>
       </c>
     </row>
@@ -7606,11 +7606,11 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Shepody Mountain Manganese</t>
+          <t>Meridian Brook Crossing</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>721</v>
+        <v>630</v>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr"/>
@@ -7619,11 +7619,7 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>Mn</t>
-        </is>
-      </c>
+      <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr">
         <is>
           <t>Past Producer</t>
@@ -7650,23 +7646,23 @@
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr"/>
       <c r="S100" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="T100" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="U100" t="n">
         <v>30</v>
       </c>
       <c r="V100" t="n">
-        <v>45.80502</v>
+        <v>47.26747</v>
       </c>
       <c r="W100" t="n">
-        <v>-64.65774</v>
+        <v>-66.68077</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=721</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=630</t>
         </is>
       </c>
     </row>
@@ -7676,11 +7672,11 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>South Hamilton Road</t>
+          <t>Shepody Mountain Manganese</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1412</v>
+        <v>721</v>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr"/>
@@ -7691,7 +7687,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ag, Au, Cu, Pb, Zn</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -7720,23 +7716,23 @@
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr"/>
       <c r="S101" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T101" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U101" t="n">
         <v>30</v>
       </c>
       <c r="V101" t="n">
-        <v>45.56892</v>
+        <v>45.80502</v>
       </c>
       <c r="W101" t="n">
-        <v>-66.16552</v>
+        <v>-64.65774</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1412</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=721</t>
         </is>
       </c>
     </row>
@@ -7816,11 +7812,11 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Meridian Brook Crossing</t>
+          <t>South Hamilton Road</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>630</v>
+        <v>1412</v>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
@@ -7829,7 +7825,11 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Ag, Au, Cu, Pb, Zn</t>
+        </is>
+      </c>
       <c r="H103" t="inlineStr">
         <is>
           <t>Past Producer</t>
@@ -7856,23 +7856,23 @@
       <c r="Q103" t="inlineStr"/>
       <c r="R103" t="inlineStr"/>
       <c r="S103" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T103" t="n">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="U103" t="n">
         <v>30</v>
       </c>
       <c r="V103" t="n">
-        <v>47.26747</v>
+        <v>45.56892</v>
       </c>
       <c r="W103" t="n">
-        <v>-66.68077</v>
+        <v>-66.16552</v>
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=630</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1412</t>
         </is>
       </c>
     </row>

--- a/site/nb_leads.xlsx
+++ b/site/nb_leads.xlsx
@@ -570,11 +570,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Shin Creek</t>
+          <t>Sloop Cove</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
@@ -585,7 +585,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ag, Mo, W</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -627,14 +627,14 @@
         <v>45</v>
       </c>
       <c r="V2" t="n">
-        <v>45.55224</v>
+        <v>44.68722</v>
       </c>
       <c r="W2" t="n">
-        <v>-66.63357999999999</v>
+        <v>-66.87302</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=8</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=31</t>
         </is>
       </c>
     </row>
@@ -644,11 +644,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Evandale Stock *</t>
+          <t>Quispamsis</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -659,7 +659,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ag, Au, Cu</t>
+          <t>Ag, Au, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -701,14 +701,14 @@
         <v>45</v>
       </c>
       <c r="V3" t="n">
-        <v>45.58501</v>
+        <v>45.42362</v>
       </c>
       <c r="W3" t="n">
-        <v>-66.09690999999999</v>
+        <v>-65.95802</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=11</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=4</t>
         </is>
       </c>
     </row>
@@ -718,11 +718,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Quispamsis</t>
+          <t>Melanson Brook E</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>1026</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -733,7 +733,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ag, Au, Cu, Pb, Zn</t>
+          <t>Ag, Pb, Zn</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -775,14 +775,14 @@
         <v>45</v>
       </c>
       <c r="V4" t="n">
-        <v>45.42362</v>
+        <v>47.73447</v>
       </c>
       <c r="W4" t="n">
-        <v>-65.95802</v>
+        <v>-65.98719</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=4</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1026</t>
         </is>
       </c>
     </row>
@@ -792,11 +792,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pender Brook</t>
+          <t>Nigadoo 8</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>1028</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -807,7 +807,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sb</t>
+          <t>Ag, Au, Pb, Zn</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -840,23 +840,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T5" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U5" t="n">
         <v>45</v>
       </c>
       <c r="V5" t="n">
-        <v>45.57888</v>
+        <v>47.74616</v>
       </c>
       <c r="W5" t="n">
-        <v>-66.30664</v>
+        <v>-65.88711000000001</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=10</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1028</t>
         </is>
       </c>
     </row>
@@ -866,11 +866,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Taylor Village</t>
+          <t>Antinouri Lake West B</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>57</v>
+        <v>1021</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -881,7 +881,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ti</t>
+          <t>Pb, Zn</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -923,14 +923,14 @@
         <v>45</v>
       </c>
       <c r="V6" t="n">
-        <v>45.93834</v>
+        <v>47.78921</v>
       </c>
       <c r="W6" t="n">
-        <v>-64.55385</v>
+        <v>-65.99773</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=57</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1021</t>
         </is>
       </c>
     </row>
@@ -940,11 +940,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Quisibis Mountain</t>
+          <t>Payne Brook</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>58</v>
+        <v>1036</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -955,7 +955,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Ag, Pb, Zn</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -997,14 +997,14 @@
         <v>45</v>
       </c>
       <c r="V7" t="n">
-        <v>47.42337</v>
+        <v>47.74032</v>
       </c>
       <c r="W7" t="n">
-        <v>-67.96913000000001</v>
+        <v>-65.91246</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=58</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1036</t>
         </is>
       </c>
     </row>
@@ -1014,11 +1014,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Levesque Gulch</t>
+          <t>Belledune Pond</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1115</v>
+        <v>72</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Au, Cu, Sb</t>
+          <t>Ag, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1062,23 +1062,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T8" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U8" t="n">
         <v>45</v>
       </c>
       <c r="V8" t="n">
-        <v>47.6649</v>
+        <v>47.82638</v>
       </c>
       <c r="W8" t="n">
-        <v>-66.69267000000001</v>
+        <v>-65.97922</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1115</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=72</t>
         </is>
       </c>
     </row>
@@ -1088,11 +1088,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Antinouri Lake West A</t>
+          <t>St. Leonard Iron-Manganese</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ag, Cu, Pb, Zn</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1145,14 +1145,14 @@
         <v>45</v>
       </c>
       <c r="V9" t="n">
-        <v>47.78952</v>
+        <v>47.2053</v>
       </c>
       <c r="W9" t="n">
-        <v>-65.98515</v>
+        <v>-67.88663</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=85</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=101</t>
         </is>
       </c>
     </row>
@@ -1236,11 +1236,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>St. Leonard Iron-Manganese</t>
+          <t>Antinouri Lake West A</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Ag, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1293,14 +1293,14 @@
         <v>45</v>
       </c>
       <c r="V11" t="n">
-        <v>47.2053</v>
+        <v>47.78952</v>
       </c>
       <c r="W11" t="n">
-        <v>-67.88663</v>
+        <v>-65.98515</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=101</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=85</t>
         </is>
       </c>
     </row>
@@ -1310,11 +1310,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Belledune Pond</t>
+          <t>Levesque Gulch</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>72</v>
+        <v>1115</v>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ag, Cu, Pb, Zn</t>
+          <t>Au, Cu, Sb</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1358,23 +1358,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T12" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U12" t="n">
         <v>45</v>
       </c>
       <c r="V12" t="n">
-        <v>47.82638</v>
+        <v>47.6649</v>
       </c>
       <c r="W12" t="n">
-        <v>-65.97922</v>
+        <v>-66.69267000000001</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=72</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1115</t>
         </is>
       </c>
     </row>
@@ -1384,11 +1384,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Red Pine Brook</t>
+          <t>Gordon Meadow Brook East</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1408</v>
+        <v>1252</v>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Ag, Pb, Zn</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1441,14 +1441,14 @@
         <v>45</v>
       </c>
       <c r="V13" t="n">
-        <v>47.4492</v>
+        <v>47.39279</v>
       </c>
       <c r="W13" t="n">
-        <v>-65.62412999999999</v>
+        <v>-65.68568999999999</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1408</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1252</t>
         </is>
       </c>
     </row>
@@ -1458,11 +1458,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Little Sevogle River 1</t>
+          <t>Kenny Lake</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>60</v>
+        <v>1278</v>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Pb, Zn</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1506,23 +1506,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T14" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U14" t="n">
         <v>45</v>
       </c>
       <c r="V14" t="n">
-        <v>47.0005</v>
+        <v>47.23226</v>
       </c>
       <c r="W14" t="n">
-        <v>-65.98999999999999</v>
+        <v>-66.2908</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=60</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1278</t>
         </is>
       </c>
     </row>
@@ -1532,11 +1532,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Peekaboo Corner *</t>
+          <t>Green Creek North</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>27</v>
+        <v>1334</v>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
@@ -1589,14 +1589,14 @@
         <v>45</v>
       </c>
       <c r="V15" t="n">
-        <v>45.65473</v>
+        <v>45.79059</v>
       </c>
       <c r="W15" t="n">
-        <v>-65.71941</v>
+        <v>-64.44385</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=27</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1334</t>
         </is>
       </c>
     </row>
@@ -1606,11 +1606,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Gordon Meadow Brook East</t>
+          <t>Peekaboo Corner *</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1252</v>
+        <v>27</v>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ag, Pb, Zn</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1663,14 +1663,14 @@
         <v>45</v>
       </c>
       <c r="V16" t="n">
-        <v>47.39279</v>
+        <v>45.65473</v>
       </c>
       <c r="W16" t="n">
-        <v>-65.68568999999999</v>
+        <v>-65.71941</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1252</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=27</t>
         </is>
       </c>
     </row>
@@ -1680,11 +1680,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nigadoo 8</t>
+          <t>Shin Creek</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1028</v>
+        <v>8</v>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ag, Au, Pb, Zn</t>
+          <t>Ag, Mo, W</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1728,23 +1728,23 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T17" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U17" t="n">
         <v>45</v>
       </c>
       <c r="V17" t="n">
-        <v>47.74616</v>
+        <v>45.55224</v>
       </c>
       <c r="W17" t="n">
-        <v>-65.88711000000001</v>
+        <v>-66.63357999999999</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1028</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=8</t>
         </is>
       </c>
     </row>
@@ -1754,11 +1754,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Melanson Brook E</t>
+          <t>Quisibis Mountain</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1026</v>
+        <v>58</v>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ag, Pb, Zn</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1811,14 +1811,14 @@
         <v>45</v>
       </c>
       <c r="V18" t="n">
-        <v>47.73447</v>
+        <v>47.42337</v>
       </c>
       <c r="W18" t="n">
-        <v>-65.98719</v>
+        <v>-67.96913000000001</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1026</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=58</t>
         </is>
       </c>
     </row>
@@ -1828,11 +1828,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Antinouri Lake West B</t>
+          <t>Little Sevogle River 1</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1021</v>
+        <v>60</v>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pb, Zn</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1885,14 +1885,14 @@
         <v>45</v>
       </c>
       <c r="V19" t="n">
-        <v>47.78921</v>
+        <v>47.0005</v>
       </c>
       <c r="W19" t="n">
-        <v>-65.99773</v>
+        <v>-65.98999999999999</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1021</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=60</t>
         </is>
       </c>
     </row>
@@ -1902,11 +1902,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Kenny Lake</t>
+          <t>Taylor Village</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1278</v>
+        <v>57</v>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pb, Zn</t>
+          <t>Ti</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1950,23 +1950,23 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T20" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U20" t="n">
         <v>45</v>
       </c>
       <c r="V20" t="n">
-        <v>47.23226</v>
+        <v>45.93834</v>
       </c>
       <c r="W20" t="n">
-        <v>-66.2908</v>
+        <v>-64.55385</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1278</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=57</t>
         </is>
       </c>
     </row>
@@ -1976,11 +1976,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sloop Cove</t>
+          <t>South Glassville</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>31</v>
+        <v>1504</v>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2033,14 +2033,14 @@
         <v>45</v>
       </c>
       <c r="V21" t="n">
-        <v>44.68722</v>
+        <v>46.48057</v>
       </c>
       <c r="W21" t="n">
-        <v>-66.87302</v>
+        <v>-67.42028000000001</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=31</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1504</t>
         </is>
       </c>
     </row>
@@ -2050,11 +2050,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>South Glassville</t>
+          <t>Red Pine Brook</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1504</v>
+        <v>1408</v>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2107,14 +2107,14 @@
         <v>45</v>
       </c>
       <c r="V22" t="n">
-        <v>46.48057</v>
+        <v>47.4492</v>
       </c>
       <c r="W22" t="n">
-        <v>-67.42028000000001</v>
+        <v>-65.62412999999999</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1504</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1408</t>
         </is>
       </c>
     </row>
@@ -2124,11 +2124,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Green Creek North</t>
+          <t>Pender Brook</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1334</v>
+        <v>10</v>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Sb</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2181,14 +2181,14 @@
         <v>45</v>
       </c>
       <c r="V23" t="n">
-        <v>45.79059</v>
+        <v>45.57888</v>
       </c>
       <c r="W23" t="n">
-        <v>-64.44385</v>
+        <v>-66.30664</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1334</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=10</t>
         </is>
       </c>
     </row>
@@ -2198,11 +2198,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Payne Brook</t>
+          <t>Evandale Stock *</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1036</v>
+        <v>11</v>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ag, Pb, Zn</t>
+          <t>Ag, Au, Cu</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2255,14 +2255,14 @@
         <v>45</v>
       </c>
       <c r="V24" t="n">
-        <v>47.74032</v>
+        <v>45.58501</v>
       </c>
       <c r="W24" t="n">
-        <v>-65.91246</v>
+        <v>-66.09690999999999</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1036</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=11</t>
         </is>
       </c>
     </row>
@@ -2272,11 +2272,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Hayward Pinnacle</t>
+          <t>Joliffs Brook</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1575</v>
+        <v>555</v>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>Zn</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2329,14 +2329,14 @@
         <v>43</v>
       </c>
       <c r="V25" t="n">
-        <v>45.82761</v>
+        <v>45.73919</v>
       </c>
       <c r="W25" t="n">
-        <v>-64.9164</v>
+        <v>-65.75996000000001</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1575</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=555</t>
         </is>
       </c>
     </row>
@@ -2346,11 +2346,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Crory Farm</t>
+          <t>Martins Bluff</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>605</v>
+        <v>562</v>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
@@ -2359,11 +2359,7 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Cu, Pb, Zn</t>
-        </is>
-      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -2403,14 +2399,14 @@
         <v>43</v>
       </c>
       <c r="V26" t="n">
-        <v>45.08058</v>
+        <v>46.93142</v>
       </c>
       <c r="W26" t="n">
-        <v>-66.80913</v>
+        <v>-66.64663</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=605</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=562</t>
         </is>
       </c>
     </row>
@@ -2420,11 +2416,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Tennants Cove *</t>
+          <t>Ragged Falls &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>372</v>
+        <v>570</v>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
@@ -2435,7 +2431,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Th, U</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2468,23 +2464,23 @@
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T27" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U27" t="n">
         <v>43</v>
       </c>
       <c r="V27" t="n">
-        <v>45.58694</v>
+        <v>45.2353</v>
       </c>
       <c r="W27" t="n">
-        <v>-66.01414</v>
+        <v>-66.48052</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=372</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=570</t>
         </is>
       </c>
     </row>
@@ -2494,11 +2490,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ragged Falls &amp;quot;I&amp;quot;</t>
+          <t>Crory Farm</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>570</v>
+        <v>605</v>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
@@ -2509,7 +2505,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Th, U</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2542,23 +2538,23 @@
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T28" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U28" t="n">
         <v>43</v>
       </c>
       <c r="V28" t="n">
-        <v>45.2353</v>
+        <v>45.08058</v>
       </c>
       <c r="W28" t="n">
-        <v>-66.48052</v>
+        <v>-66.80913</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=570</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=605</t>
         </is>
       </c>
     </row>
@@ -2568,11 +2564,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Martins Bluff</t>
+          <t>Dickson Brook A,B,C</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>562</v>
+        <v>639</v>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
@@ -2581,7 +2577,11 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -2621,14 +2621,14 @@
         <v>43</v>
       </c>
       <c r="V29" t="n">
-        <v>46.93142</v>
+        <v>45.58364</v>
       </c>
       <c r="W29" t="n">
-        <v>-66.64663</v>
+        <v>-64.98524</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=562</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=639</t>
         </is>
       </c>
     </row>
@@ -2638,11 +2638,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Joliffs Brook</t>
+          <t>Three Bridge Brook East *</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>555</v>
+        <v>793</v>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Zn</t>
+          <t>Ag, Au, Pb, Zn</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2686,23 +2686,23 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T30" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U30" t="n">
         <v>43</v>
       </c>
       <c r="V30" t="n">
-        <v>45.73919</v>
+        <v>45.49419</v>
       </c>
       <c r="W30" t="n">
-        <v>-65.75996000000001</v>
+        <v>-66.48581</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=555</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=793</t>
         </is>
       </c>
     </row>
@@ -2712,11 +2712,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Dickson Brook A,B,C</t>
+          <t>Eel Ground</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>639</v>
+        <v>746</v>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2769,14 +2769,14 @@
         <v>43</v>
       </c>
       <c r="V31" t="n">
-        <v>45.58364</v>
+        <v>46.96447</v>
       </c>
       <c r="W31" t="n">
-        <v>-64.98524</v>
+        <v>-65.59441</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=639</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=746</t>
         </is>
       </c>
     </row>
@@ -2786,11 +2786,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Quaco Road &amp;quot;I&amp;quot;</t>
+          <t>Halls Hill</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>678</v>
+        <v>1324</v>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Cu, Zn</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2843,14 +2843,14 @@
         <v>43</v>
       </c>
       <c r="V32" t="n">
-        <v>45.38336</v>
+        <v>45.96809</v>
       </c>
       <c r="W32" t="n">
-        <v>-65.74996</v>
+        <v>-64.16996</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=678</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1324</t>
         </is>
       </c>
     </row>
@@ -2860,11 +2860,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Gowland Mountain *</t>
+          <t>Jacquet River M</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>643</v>
+        <v>955</v>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Ba, Cu</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2917,14 +2917,14 @@
         <v>43</v>
       </c>
       <c r="V33" t="n">
-        <v>45.81975</v>
+        <v>47.82559</v>
       </c>
       <c r="W33" t="n">
-        <v>-65.0483</v>
+        <v>-66.01662</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=643</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=955</t>
         </is>
       </c>
     </row>
@@ -2934,11 +2934,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Deed Brook</t>
+          <t>Letang Harbour North</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>717</v>
+        <v>1291</v>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2982,23 +2982,23 @@
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T34" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U34" t="n">
         <v>43</v>
       </c>
       <c r="V34" t="n">
-        <v>45.78808</v>
+        <v>45.08726</v>
       </c>
       <c r="W34" t="n">
-        <v>-64.85692</v>
+        <v>-66.7833</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=717</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1291</t>
         </is>
       </c>
     </row>
@@ -3008,11 +3008,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Irving</t>
+          <t>Dennis Stream - Upper &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1238</v>
+        <v>1306</v>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
@@ -3021,11 +3021,7 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Co, Cu, Ni</t>
-        </is>
-      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -3056,23 +3052,23 @@
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T35" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="U35" t="n">
         <v>43</v>
       </c>
       <c r="V35" t="n">
-        <v>45.19116</v>
+        <v>45.22199</v>
       </c>
       <c r="W35" t="n">
-        <v>-67.25942000000001</v>
+        <v>-67.27109</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1238</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1306</t>
         </is>
       </c>
     </row>
@@ -3082,11 +3078,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>St Stephen Ni - O Zone &amp;quot;I&amp;quot;</t>
+          <t>Gowland Mountain *</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1236</v>
+        <v>643</v>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
@@ -3097,7 +3093,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Co, Cu, Ni</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3130,23 +3126,23 @@
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T36" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U36" t="n">
         <v>43</v>
       </c>
       <c r="V36" t="n">
-        <v>45.23088</v>
+        <v>45.81975</v>
       </c>
       <c r="W36" t="n">
-        <v>-67.27692</v>
+        <v>-65.0483</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1236</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=643</t>
         </is>
       </c>
     </row>
@@ -3156,11 +3152,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Memramcook Gold &amp;quot;I&amp;quot;</t>
+          <t>Quaco Road &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>723</v>
+        <v>678</v>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
@@ -3171,7 +3167,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3204,23 +3200,23 @@
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T37" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U37" t="n">
         <v>43</v>
       </c>
       <c r="V37" t="n">
-        <v>45.96531</v>
+        <v>45.38336</v>
       </c>
       <c r="W37" t="n">
-        <v>-64.53885</v>
+        <v>-65.74996</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=723</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=678</t>
         </is>
       </c>
     </row>
@@ -3230,11 +3226,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Halls Hill</t>
+          <t>St Stephen Ni - O Zone &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1324</v>
+        <v>1236</v>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
@@ -3245,7 +3241,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cu, Zn</t>
+          <t>Co, Cu, Ni</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3278,23 +3274,23 @@
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T38" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U38" t="n">
         <v>43</v>
       </c>
       <c r="V38" t="n">
-        <v>45.96809</v>
+        <v>45.23088</v>
       </c>
       <c r="W38" t="n">
-        <v>-64.16996</v>
+        <v>-67.27692</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1324</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1236</t>
         </is>
       </c>
     </row>
@@ -3304,11 +3300,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Letang Harbour North</t>
+          <t>Irving</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1291</v>
+        <v>1238</v>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
@@ -3319,7 +3315,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Co, Cu, Ni</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3352,23 +3348,23 @@
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T39" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U39" t="n">
         <v>43</v>
       </c>
       <c r="V39" t="n">
-        <v>45.08726</v>
+        <v>45.19116</v>
       </c>
       <c r="W39" t="n">
-        <v>-66.7833</v>
+        <v>-67.25942000000001</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1291</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1238</t>
         </is>
       </c>
     </row>
@@ -3378,11 +3374,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Dennis Stream - Upper &amp;quot;I&amp;quot;</t>
+          <t>Pabineau River North Manganese</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1306</v>
+        <v>1272</v>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
@@ -3391,7 +3387,11 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Mn</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -3422,23 +3422,23 @@
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T40" t="n">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="U40" t="n">
         <v>43</v>
       </c>
       <c r="V40" t="n">
-        <v>45.22199</v>
+        <v>47.49558</v>
       </c>
       <c r="W40" t="n">
-        <v>-67.27109</v>
+        <v>-65.90329</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1306</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1272</t>
         </is>
       </c>
     </row>
@@ -3448,11 +3448,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Jacquet River M</t>
+          <t>Bass River Cu-Ni</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>955</v>
+        <v>1254</v>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ba, Cu</t>
+          <t>Cu, Ni</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3505,14 +3505,14 @@
         <v>43</v>
       </c>
       <c r="V41" t="n">
-        <v>47.82559</v>
+        <v>47.46421</v>
       </c>
       <c r="W41" t="n">
-        <v>-66.01662</v>
+        <v>-65.56607</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=955</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1254</t>
         </is>
       </c>
     </row>
@@ -3522,11 +3522,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Eel Ground</t>
+          <t>Memramcook Gold &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>746</v>
+        <v>723</v>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
@@ -3537,7 +3537,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3570,23 +3570,23 @@
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T42" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U42" t="n">
         <v>43</v>
       </c>
       <c r="V42" t="n">
-        <v>46.96447</v>
+        <v>45.96531</v>
       </c>
       <c r="W42" t="n">
-        <v>-65.59441</v>
+        <v>-64.53885</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=746</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=723</t>
         </is>
       </c>
     </row>
@@ -3596,11 +3596,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Three Bridge Brook East *</t>
+          <t>Deed Brook</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>793</v>
+        <v>717</v>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ag, Au, Pb, Zn</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3644,23 +3644,23 @@
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T43" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="U43" t="n">
         <v>43</v>
       </c>
       <c r="V43" t="n">
-        <v>45.49419</v>
+        <v>45.78808</v>
       </c>
       <c r="W43" t="n">
-        <v>-66.48581</v>
+        <v>-64.85692</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=793</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=717</t>
         </is>
       </c>
     </row>
@@ -3670,11 +3670,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Pabineau River North Manganese</t>
+          <t>Hayward Pinnacle</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1272</v>
+        <v>1575</v>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>U</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3718,23 +3718,23 @@
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T44" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U44" t="n">
         <v>43</v>
       </c>
       <c r="V44" t="n">
-        <v>47.49558</v>
+        <v>45.82761</v>
       </c>
       <c r="W44" t="n">
-        <v>-65.90329</v>
+        <v>-64.9164</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1272</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1575</t>
         </is>
       </c>
     </row>
@@ -3744,11 +3744,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Bass River Cu-Ni</t>
+          <t>Tennants Cove *</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1254</v>
+        <v>372</v>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cu, Ni</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3801,14 +3801,14 @@
         <v>43</v>
       </c>
       <c r="V45" t="n">
-        <v>47.46421</v>
+        <v>45.58694</v>
       </c>
       <c r="W45" t="n">
-        <v>-65.56607</v>
+        <v>-66.01414</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1254</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=372</t>
         </is>
       </c>
     </row>
@@ -3892,11 +3892,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Lower Birch Island</t>
+          <t>Brunswick No. 12</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>172</v>
+        <v>54</v>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ba, Fe, Mn</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>88.8 Mt</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -3949,14 +3949,14 @@
         <v>38</v>
       </c>
       <c r="V47" t="n">
-        <v>46.56864</v>
+        <v>47.47889</v>
       </c>
       <c r="W47" t="n">
-        <v>-66.57080000000001</v>
+        <v>-65.89218</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=172</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=54</t>
         </is>
       </c>
     </row>
@@ -3966,11 +3966,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nigadoo River Mine</t>
+          <t>Anomaly 102 &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>128</v>
+        <v>1151</v>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ag, Cu, Pb, Zn</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>1.1 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -4023,14 +4023,14 @@
         <v>38</v>
       </c>
       <c r="V48" t="n">
-        <v>47.73307</v>
+        <v>46.47865</v>
       </c>
       <c r="W48" t="n">
-        <v>-65.80642</v>
+        <v>-66.72996999999999</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=128</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1151</t>
         </is>
       </c>
     </row>
@@ -4040,11 +4040,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Austin Brook</t>
+          <t>Nigadoo River Mine</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>69</v>
+        <v>128</v>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
@@ -4055,7 +4055,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ag, Fe, Pb, Zn</t>
+          <t>Ag, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>164 kt</t>
+          <t>1.1 Mt</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -4088,23 +4088,23 @@
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T49" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U49" t="n">
         <v>38</v>
       </c>
       <c r="V49" t="n">
-        <v>47.39779</v>
+        <v>47.73307</v>
       </c>
       <c r="W49" t="n">
-        <v>-65.82302</v>
+        <v>-65.80642</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=69</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=128</t>
         </is>
       </c>
     </row>
@@ -4114,11 +4114,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Brunswick No. 12</t>
+          <t>Lower Birch Island</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>54</v>
+        <v>172</v>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Ba, Fe, Mn</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>88.8 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
@@ -4171,14 +4171,14 @@
         <v>38</v>
       </c>
       <c r="V50" t="n">
-        <v>47.47889</v>
+        <v>46.56864</v>
       </c>
       <c r="W50" t="n">
-        <v>-65.89218</v>
+        <v>-66.57080000000001</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=54</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=172</t>
         </is>
       </c>
     </row>
@@ -4188,11 +4188,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Anomaly 102 &amp;quot;I&amp;quot;</t>
+          <t>Austin Brook</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1151</v>
+        <v>69</v>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Ag, Fe, Pb, Zn</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>164 kt</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
@@ -4236,23 +4236,23 @@
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T51" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U51" t="n">
         <v>38</v>
       </c>
       <c r="V51" t="n">
-        <v>46.47865</v>
+        <v>47.39779</v>
       </c>
       <c r="W51" t="n">
-        <v>-66.72996999999999</v>
+        <v>-65.82302</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1151</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=69</t>
         </is>
       </c>
     </row>
@@ -4262,11 +4262,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Black Point</t>
+          <t>Taylors Island</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1333</v>
+        <v>32</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pb, Zn</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4315,14 +4315,14 @@
         <v>37</v>
       </c>
       <c r="V52" t="n">
-        <v>45.79448</v>
+        <v>45.22336</v>
       </c>
       <c r="W52" t="n">
-        <v>-64.42218</v>
+        <v>-66.12747</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1333</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=32</t>
         </is>
       </c>
     </row>
@@ -4332,11 +4332,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Jeanne Mance</t>
+          <t>Henry Lake</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1249</v>
+        <v>1510</v>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
@@ -4385,14 +4385,14 @@
         <v>37</v>
       </c>
       <c r="V53" t="n">
-        <v>47.36337</v>
+        <v>45.39473</v>
       </c>
       <c r="W53" t="n">
-        <v>-65.44329999999999</v>
+        <v>-65.60417</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1249</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1510</t>
         </is>
       </c>
     </row>
@@ -4402,11 +4402,11 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Bulls Creek 2</t>
+          <t>Little Nictor Lake</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1072</v>
+        <v>94</v>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
@@ -4417,7 +4417,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ag, Au, Co, Cu</t>
+          <t>Zn</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4446,23 +4446,23 @@
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T54" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U54" t="n">
         <v>37</v>
       </c>
       <c r="V54" t="n">
-        <v>46.08809</v>
+        <v>47.40642</v>
       </c>
       <c r="W54" t="n">
-        <v>-67.56498000000001</v>
+        <v>-66.84441</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1072</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=94</t>
         </is>
       </c>
     </row>
@@ -4472,11 +4472,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Bulls Creek 1</t>
+          <t>Bulls Creek 2</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
@@ -4487,7 +4487,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Ag, Au, Co, Cu</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4516,23 +4516,23 @@
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T55" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U55" t="n">
         <v>37</v>
       </c>
       <c r="V55" t="n">
-        <v>46.08421</v>
+        <v>46.08809</v>
       </c>
       <c r="W55" t="n">
-        <v>-67.57774999999999</v>
+        <v>-67.56498000000001</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1071</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1072</t>
         </is>
       </c>
     </row>
@@ -4542,11 +4542,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Little Nictor Lake</t>
+          <t>Bulls Creek 1</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>94</v>
+        <v>1071</v>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
@@ -4557,7 +4557,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Zn</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4595,14 +4595,14 @@
         <v>37</v>
       </c>
       <c r="V56" t="n">
-        <v>47.40642</v>
+        <v>46.08421</v>
       </c>
       <c r="W56" t="n">
-        <v>-66.84441</v>
+        <v>-67.57774999999999</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=94</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1071</t>
         </is>
       </c>
     </row>
@@ -4612,11 +4612,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Gaspereau River</t>
+          <t>Church Showing</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1300</v>
+        <v>726</v>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
@@ -4665,14 +4665,14 @@
         <v>37</v>
       </c>
       <c r="V57" t="n">
-        <v>46.08059</v>
+        <v>44.88974</v>
       </c>
       <c r="W57" t="n">
-        <v>-64.20996</v>
+        <v>-66.95386000000001</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1300</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=726</t>
         </is>
       </c>
     </row>
@@ -4682,11 +4682,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Church Showing</t>
+          <t>Jeanne Mance</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>726</v>
+        <v>1249</v>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
@@ -4735,14 +4735,14 @@
         <v>37</v>
       </c>
       <c r="V58" t="n">
-        <v>44.88974</v>
+        <v>47.36337</v>
       </c>
       <c r="W58" t="n">
-        <v>-66.95386000000001</v>
+        <v>-65.44329999999999</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=726</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1249</t>
         </is>
       </c>
     </row>
@@ -4752,11 +4752,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Basaltic Island West *</t>
+          <t>Black Point</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1347</v>
+        <v>1333</v>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
@@ -4805,14 +4805,14 @@
         <v>37</v>
       </c>
       <c r="V59" t="n">
-        <v>45.1392</v>
+        <v>45.79448</v>
       </c>
       <c r="W59" t="n">
-        <v>-66.92413999999999</v>
+        <v>-64.42218</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1347</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1333</t>
         </is>
       </c>
     </row>
@@ -4822,11 +4822,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Grande Anse</t>
+          <t>Quispamsis Exit</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1370</v>
+        <v>1338</v>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Ag, Au, Cu, Pb</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4875,14 +4875,14 @@
         <v>37</v>
       </c>
       <c r="V60" t="n">
-        <v>45.79615</v>
+        <v>45.42378</v>
       </c>
       <c r="W60" t="n">
-        <v>-64.50107</v>
+        <v>-65.92708</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1370</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1338</t>
         </is>
       </c>
     </row>
@@ -4892,11 +4892,11 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Johnson Mills</t>
+          <t>Basaltic Island West *</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1371</v>
+        <v>1347</v>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Pb, Zn</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4945,14 +4945,14 @@
         <v>37</v>
       </c>
       <c r="V61" t="n">
-        <v>45.76365</v>
+        <v>45.1392</v>
       </c>
       <c r="W61" t="n">
-        <v>-64.52218000000001</v>
+        <v>-66.92413999999999</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1371</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1347</t>
         </is>
       </c>
     </row>
@@ -4962,11 +4962,11 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Moores Mills #2</t>
+          <t>Frye Island North</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1374</v>
+        <v>1353</v>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
@@ -4977,7 +4977,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ag, Cu, Pb</t>
+          <t>Ag, Cu, F, Pb, Sb, Zn</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5006,23 +5006,23 @@
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T62" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U62" t="n">
         <v>37</v>
       </c>
       <c r="V62" t="n">
-        <v>45.29977</v>
+        <v>45.04753</v>
       </c>
       <c r="W62" t="n">
-        <v>-67.2533</v>
+        <v>-66.84469</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1374</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1353</t>
         </is>
       </c>
     </row>
@@ -5032,11 +5032,11 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Scoudouc River Quarry</t>
+          <t>Gaspereau River</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1367</v>
+        <v>1300</v>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
@@ -5047,7 +5047,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pb, Zn</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5085,14 +5085,14 @@
         <v>37</v>
       </c>
       <c r="V63" t="n">
-        <v>46.19643</v>
+        <v>46.08059</v>
       </c>
       <c r="W63" t="n">
-        <v>-64.54385000000001</v>
+        <v>-64.20996</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1367</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1300</t>
         </is>
       </c>
     </row>
@@ -5102,11 +5102,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Black Point North</t>
+          <t>Cape Maringouin # 1</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1368</v>
+        <v>1360</v>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cu, Zn</t>
+          <t>Cu, Pb</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5155,14 +5155,14 @@
         <v>37</v>
       </c>
       <c r="V64" t="n">
-        <v>45.80448</v>
+        <v>45.73532</v>
       </c>
       <c r="W64" t="n">
-        <v>-64.41634999999999</v>
+        <v>-64.54191</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1368</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1360</t>
         </is>
       </c>
     </row>
@@ -5172,11 +5172,11 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Shediac River # 2</t>
+          <t>Cape Maringouin # 2</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>As</t>
+          <t>Ag, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5225,14 +5225,14 @@
         <v>37</v>
       </c>
       <c r="V65" t="n">
-        <v>46.2417</v>
+        <v>45.73782</v>
       </c>
       <c r="W65" t="n">
-        <v>-64.6858</v>
+        <v>-64.53246</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1365</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1361</t>
         </is>
       </c>
     </row>
@@ -5242,11 +5242,11 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Rockport Shore</t>
+          <t>Digdeguash Cu *</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1362</v>
+        <v>1344</v>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
@@ -5257,7 +5257,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Cu, Zn</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5295,14 +5295,14 @@
         <v>37</v>
       </c>
       <c r="V66" t="n">
-        <v>45.72365</v>
+        <v>45.18698</v>
       </c>
       <c r="W66" t="n">
-        <v>-64.50663</v>
+        <v>-66.93774999999999</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1362</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1344</t>
         </is>
       </c>
     </row>
@@ -5312,11 +5312,11 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Cape Maringouin # 2</t>
+          <t>Rockport Shore</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
@@ -5327,7 +5327,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ag, Cu, Pb, Zn</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5365,14 +5365,14 @@
         <v>37</v>
       </c>
       <c r="V67" t="n">
-        <v>45.73782</v>
+        <v>45.72365</v>
       </c>
       <c r="W67" t="n">
-        <v>-64.53246</v>
+        <v>-64.50663</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1361</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1362</t>
         </is>
       </c>
     </row>
@@ -5382,11 +5382,11 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Cape Maringouin # 1</t>
+          <t>Black Point North</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1360</v>
+        <v>1368</v>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cu, Pb</t>
+          <t>Cu, Zn</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5435,14 +5435,14 @@
         <v>37</v>
       </c>
       <c r="V68" t="n">
-        <v>45.73532</v>
+        <v>45.80448</v>
       </c>
       <c r="W68" t="n">
-        <v>-64.54191</v>
+        <v>-64.41634999999999</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1360</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1368</t>
         </is>
       </c>
     </row>
@@ -5452,11 +5452,11 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Frye Island North</t>
+          <t>Grande Anse</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1353</v>
+        <v>1370</v>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
@@ -5467,7 +5467,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ag, Cu, F, Pb, Sb, Zn</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5505,14 +5505,14 @@
         <v>37</v>
       </c>
       <c r="V69" t="n">
-        <v>45.04753</v>
+        <v>45.79615</v>
       </c>
       <c r="W69" t="n">
-        <v>-66.84469</v>
+        <v>-64.50107</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1353</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1370</t>
         </is>
       </c>
     </row>
@@ -5522,11 +5522,11 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Quispamsis Exit</t>
+          <t>Sinclair Hill</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1338</v>
+        <v>9</v>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
@@ -5537,7 +5537,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ag, Au, Cu, Pb</t>
+          <t>Ag, Au, Cu</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5575,14 +5575,14 @@
         <v>37</v>
       </c>
       <c r="V70" t="n">
-        <v>45.42378</v>
+        <v>45.63113</v>
       </c>
       <c r="W70" t="n">
-        <v>-65.92708</v>
+        <v>-64.92274999999999</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1338</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=9</t>
         </is>
       </c>
     </row>
@@ -5592,11 +5592,11 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Digdeguash Cu *</t>
+          <t>Scoudouc River Quarry</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1344</v>
+        <v>1367</v>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cu, Zn</t>
+          <t>Pb, Zn</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5645,14 +5645,14 @@
         <v>37</v>
       </c>
       <c r="V71" t="n">
-        <v>45.18698</v>
+        <v>46.19643</v>
       </c>
       <c r="W71" t="n">
-        <v>-66.93774999999999</v>
+        <v>-64.54385000000001</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1344</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1367</t>
         </is>
       </c>
     </row>
@@ -5662,11 +5662,11 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Sinclair Hill</t>
+          <t>Shediac River # 2</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>9</v>
+        <v>1365</v>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
@@ -5677,7 +5677,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ag, Au, Cu</t>
+          <t>As</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5715,14 +5715,14 @@
         <v>37</v>
       </c>
       <c r="V72" t="n">
-        <v>45.63113</v>
+        <v>46.2417</v>
       </c>
       <c r="W72" t="n">
-        <v>-64.92274999999999</v>
+        <v>-64.6858</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=9</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1365</t>
         </is>
       </c>
     </row>
@@ -5732,11 +5732,11 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Taylors Island</t>
+          <t>Johnson Mills</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>32</v>
+        <v>1371</v>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
@@ -5747,7 +5747,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5785,14 +5785,14 @@
         <v>37</v>
       </c>
       <c r="V73" t="n">
-        <v>45.22336</v>
+        <v>45.76365</v>
       </c>
       <c r="W73" t="n">
-        <v>-66.12747</v>
+        <v>-64.52218000000001</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=32</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1371</t>
         </is>
       </c>
     </row>
@@ -5802,11 +5802,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Henry Lake</t>
+          <t>Moores Mills #2</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1510</v>
+        <v>1374</v>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
@@ -5817,7 +5817,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Ag, Cu, Pb</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5846,23 +5846,23 @@
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T74" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U74" t="n">
         <v>37</v>
       </c>
       <c r="V74" t="n">
-        <v>45.39473</v>
+        <v>45.29977</v>
       </c>
       <c r="W74" t="n">
-        <v>-65.60417</v>
+        <v>-67.2533</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1510</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1374</t>
         </is>
       </c>
     </row>
@@ -5942,11 +5942,11 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Four Mile Lake B</t>
+          <t>Jacquet River Cu - A</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1175</v>
+        <v>462</v>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr"/>
@@ -5955,7 +5955,11 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
       <c r="H76" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -5991,14 +5995,14 @@
         <v>35</v>
       </c>
       <c r="V76" t="n">
-        <v>46.63643</v>
+        <v>47.85476</v>
       </c>
       <c r="W76" t="n">
-        <v>-66.58274</v>
+        <v>-66.01551000000001</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1175</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=462</t>
         </is>
       </c>
     </row>
@@ -6008,11 +6012,11 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Caledonia Mountain</t>
+          <t>Brewers Mills</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1609</v>
+        <v>904</v>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
@@ -6023,7 +6027,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ti, V</t>
+          <t>As, Au</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6052,23 +6056,23 @@
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T77" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U77" t="n">
         <v>35</v>
       </c>
       <c r="V77" t="n">
-        <v>45.8698</v>
+        <v>46.0692</v>
       </c>
       <c r="W77" t="n">
-        <v>-64.73159</v>
+        <v>-67.0283</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1609</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=904</t>
         </is>
       </c>
     </row>
@@ -6078,11 +6082,11 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Jacquet River Cu - Mitchell Rd</t>
+          <t>Jacquet River K</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>461</v>
+        <v>973</v>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
@@ -6127,14 +6131,14 @@
         <v>35</v>
       </c>
       <c r="V78" t="n">
-        <v>47.82725</v>
+        <v>47.83142</v>
       </c>
       <c r="W78" t="n">
-        <v>-66.00606999999999</v>
+        <v>-66.03246</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=461</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=973</t>
         </is>
       </c>
     </row>
@@ -6144,11 +6148,11 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Jacquet River Cu - A</t>
+          <t>Caledonia Mountain</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>462</v>
+        <v>1609</v>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
@@ -6159,7 +6163,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Ti, V</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6188,23 +6192,23 @@
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T79" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U79" t="n">
         <v>35</v>
       </c>
       <c r="V79" t="n">
-        <v>47.85476</v>
+        <v>45.8698</v>
       </c>
       <c r="W79" t="n">
-        <v>-66.01551000000001</v>
+        <v>-64.73159</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=462</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1609</t>
         </is>
       </c>
     </row>
@@ -6214,11 +6218,11 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Dumfries *</t>
+          <t>Centreville &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>535</v>
+        <v>263</v>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
@@ -6229,7 +6233,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -6267,14 +6271,14 @@
         <v>35</v>
       </c>
       <c r="V80" t="n">
-        <v>45.95029</v>
+        <v>46.44281</v>
       </c>
       <c r="W80" t="n">
-        <v>-67.12273999999999</v>
+        <v>-67.6808</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=535</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=263</t>
         </is>
       </c>
     </row>
@@ -6284,11 +6288,11 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Letete Mine</t>
+          <t>Waterville Prospect &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>311</v>
+        <v>1413</v>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
@@ -6299,12 +6303,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Au, Sb</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I81" t="b">
@@ -6315,15 +6319,11 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>1.9 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
+      <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="n">
         <v>0</v>
@@ -6332,23 +6332,23 @@
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T81" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U81" t="n">
         <v>35</v>
       </c>
       <c r="V81" t="n">
-        <v>45.06529</v>
+        <v>46.05921</v>
       </c>
       <c r="W81" t="n">
-        <v>-66.91136</v>
+        <v>-67.30663</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=311</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1413</t>
         </is>
       </c>
     </row>
@@ -6358,11 +6358,11 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Silver Island</t>
+          <t>Indian Brook</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>586</v>
+        <v>262</v>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
@@ -6371,11 +6371,7 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Ag, Pb, Zn</t>
-        </is>
-      </c>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -6411,14 +6407,14 @@
         <v>35</v>
       </c>
       <c r="V82" t="n">
-        <v>45.12114</v>
+        <v>46.73226</v>
       </c>
       <c r="W82" t="n">
-        <v>-66.8458</v>
+        <v>-67.42440999999999</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=586</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=262</t>
         </is>
       </c>
     </row>
@@ -6428,11 +6424,11 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Forty Five River &amp;quot;I&amp;quot;</t>
+          <t>Brummagen Brook Bog</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>647</v>
+        <v>188</v>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
@@ -6443,7 +6439,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -6472,23 +6468,23 @@
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T83" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U83" t="n">
         <v>35</v>
       </c>
       <c r="V83" t="n">
-        <v>45.74309</v>
+        <v>46.39003</v>
       </c>
       <c r="W83" t="n">
-        <v>-64.93053</v>
+        <v>-67.29386</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=647</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=188</t>
         </is>
       </c>
     </row>
@@ -6498,11 +6494,11 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Phyllis Creek &amp;quot;I&amp;quot;</t>
+          <t>Pecks Point South</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>655</v>
+        <v>1329</v>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
@@ -6513,7 +6509,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Ag, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -6551,14 +6547,14 @@
         <v>35</v>
       </c>
       <c r="V84" t="n">
-        <v>45.94808</v>
+        <v>45.73809</v>
       </c>
       <c r="W84" t="n">
-        <v>-66.69441</v>
+        <v>-64.48524</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=655</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1329</t>
         </is>
       </c>
     </row>
@@ -6568,11 +6564,11 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Pirate Lake</t>
+          <t>Dumfries *</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>516</v>
+        <v>535</v>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
@@ -6583,7 +6579,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -6621,14 +6617,14 @@
         <v>35</v>
       </c>
       <c r="V85" t="n">
-        <v>45.72697</v>
+        <v>45.95029</v>
       </c>
       <c r="W85" t="n">
-        <v>-67.67525000000001</v>
+        <v>-67.12273999999999</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=516</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=535</t>
         </is>
       </c>
     </row>
@@ -6638,11 +6634,11 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Pecks Point South</t>
+          <t>Pirate Lake</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1329</v>
+        <v>516</v>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
@@ -6653,7 +6649,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Ag, Cu, Pb, Zn</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6691,14 +6687,14 @@
         <v>35</v>
       </c>
       <c r="V86" t="n">
-        <v>45.73809</v>
+        <v>45.72697</v>
       </c>
       <c r="W86" t="n">
-        <v>-64.48524</v>
+        <v>-67.67525000000001</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1329</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=516</t>
         </is>
       </c>
     </row>
@@ -6708,11 +6704,11 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>East Quoddy Head</t>
+          <t>Elmtree 7B</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>737</v>
+        <v>854</v>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
@@ -6723,7 +6719,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pb</t>
+          <t>Cu, Ni</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -6752,23 +6748,23 @@
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr"/>
       <c r="S87" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T87" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U87" t="n">
         <v>35</v>
       </c>
       <c r="V87" t="n">
-        <v>44.95391</v>
+        <v>47.78253</v>
       </c>
       <c r="W87" t="n">
-        <v>-66.90831</v>
+        <v>-65.87246</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=737</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=854</t>
         </is>
       </c>
     </row>
@@ -6778,11 +6774,11 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Meadow Brook Cove</t>
+          <t>Four Mile Lake B</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>727</v>
+        <v>1175</v>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
@@ -6791,11 +6787,7 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Fe, Zn</t>
-        </is>
-      </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -6831,14 +6823,14 @@
         <v>35</v>
       </c>
       <c r="V88" t="n">
-        <v>44.88281</v>
+        <v>46.63643</v>
       </c>
       <c r="W88" t="n">
-        <v>-66.90774999999999</v>
+        <v>-66.58274</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=727</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1175</t>
         </is>
       </c>
     </row>
@@ -6848,11 +6840,11 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Jacquet River K</t>
+          <t>Meadow Brook Cove</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>973</v>
+        <v>727</v>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
@@ -6861,7 +6853,11 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Fe, Zn</t>
+        </is>
+      </c>
       <c r="H89" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -6897,14 +6893,14 @@
         <v>35</v>
       </c>
       <c r="V89" t="n">
-        <v>47.83142</v>
+        <v>44.88281</v>
       </c>
       <c r="W89" t="n">
-        <v>-66.03246</v>
+        <v>-66.90774999999999</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=973</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=727</t>
         </is>
       </c>
     </row>
@@ -6914,11 +6910,11 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Little Southwest Miramichi</t>
+          <t>East Quoddy Head</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>621</v>
+        <v>737</v>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr"/>
@@ -6927,7 +6923,11 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Pb</t>
+        </is>
+      </c>
       <c r="H90" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -6963,14 +6963,14 @@
         <v>35</v>
       </c>
       <c r="V90" t="n">
-        <v>46.89643</v>
+        <v>44.95391</v>
       </c>
       <c r="W90" t="n">
-        <v>-66.34998</v>
+        <v>-66.90831</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=621</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=737</t>
         </is>
       </c>
     </row>
@@ -6980,11 +6980,11 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Waterside Manganese</t>
+          <t>Silver Island</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>645</v>
+        <v>586</v>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
@@ -6995,7 +6995,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Ag, Pb, Zn</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -7024,23 +7024,23 @@
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr"/>
       <c r="S91" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T91" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U91" t="n">
         <v>35</v>
       </c>
       <c r="V91" t="n">
-        <v>45.63058</v>
+        <v>45.12114</v>
       </c>
       <c r="W91" t="n">
-        <v>-64.82858</v>
+        <v>-66.8458</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=645</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=586</t>
         </is>
       </c>
     </row>
@@ -7050,11 +7050,11 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Brewers Mills</t>
+          <t>Phyllis Creek &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>904</v>
+        <v>655</v>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr"/>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>As, Au</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -7103,14 +7103,14 @@
         <v>35</v>
       </c>
       <c r="V92" t="n">
-        <v>46.0692</v>
+        <v>45.94808</v>
       </c>
       <c r="W92" t="n">
-        <v>-67.0283</v>
+        <v>-66.69441</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=904</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=655</t>
         </is>
       </c>
     </row>
@@ -7120,11 +7120,11 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Elmtree 7B</t>
+          <t>Jacquet River Cu - Mitchell Rd</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>854</v>
+        <v>461</v>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
@@ -7133,11 +7133,7 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>Cu, Ni</t>
-        </is>
-      </c>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -7164,23 +7160,23 @@
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr"/>
       <c r="S93" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T93" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U93" t="n">
         <v>35</v>
       </c>
       <c r="V93" t="n">
-        <v>47.78253</v>
+        <v>47.82725</v>
       </c>
       <c r="W93" t="n">
-        <v>-65.87246</v>
+        <v>-66.00606999999999</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=854</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=461</t>
         </is>
       </c>
     </row>
@@ -7190,11 +7186,11 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>MacIntosh Brook</t>
+          <t>Maple Ridge</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>192</v>
+        <v>152</v>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
@@ -7205,7 +7201,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Mo, W</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -7234,23 +7230,23 @@
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr"/>
       <c r="S94" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T94" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U94" t="n">
         <v>35</v>
       </c>
       <c r="V94" t="n">
-        <v>46.35335</v>
+        <v>46.10003</v>
       </c>
       <c r="W94" t="n">
-        <v>-67.27636</v>
+        <v>-67.21413</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=192</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=152</t>
         </is>
       </c>
     </row>
@@ -7260,11 +7256,11 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Maple Ridge</t>
+          <t>MacIntosh Brook</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>152</v>
+        <v>192</v>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
@@ -7275,7 +7271,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Mo, W</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -7304,23 +7300,23 @@
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="inlineStr"/>
       <c r="S95" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T95" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U95" t="n">
         <v>35</v>
       </c>
       <c r="V95" t="n">
-        <v>46.10003</v>
+        <v>46.35335</v>
       </c>
       <c r="W95" t="n">
-        <v>-67.21413</v>
+        <v>-67.27636</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=152</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=192</t>
         </is>
       </c>
     </row>
@@ -7330,11 +7326,11 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Indian Brook</t>
+          <t>Letete Mine</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>262</v>
+        <v>311</v>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
@@ -7343,10 +7339,14 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I96" t="b">
@@ -7357,11 +7357,15 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>1.9 Mt</t>
         </is>
       </c>
       <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="n">
         <v>0</v>
@@ -7370,23 +7374,23 @@
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr"/>
       <c r="S96" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T96" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U96" t="n">
         <v>35</v>
       </c>
       <c r="V96" t="n">
-        <v>46.73226</v>
+        <v>45.06529</v>
       </c>
       <c r="W96" t="n">
-        <v>-67.42440999999999</v>
+        <v>-66.91136</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=262</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=311</t>
         </is>
       </c>
     </row>
@@ -7396,11 +7400,11 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Centreville &amp;quot;I&amp;quot;</t>
+          <t>Forty Five River &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>263</v>
+        <v>647</v>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
@@ -7411,7 +7415,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -7440,23 +7444,23 @@
       <c r="Q97" t="inlineStr"/>
       <c r="R97" t="inlineStr"/>
       <c r="S97" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T97" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U97" t="n">
         <v>35</v>
       </c>
       <c r="V97" t="n">
-        <v>46.44281</v>
+        <v>45.74309</v>
       </c>
       <c r="W97" t="n">
-        <v>-67.6808</v>
+        <v>-64.93053</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=263</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=647</t>
         </is>
       </c>
     </row>
@@ -7466,11 +7470,11 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Brummagen Brook Bog</t>
+          <t>Waterside Manganese</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>188</v>
+        <v>645</v>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
@@ -7510,23 +7514,23 @@
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr"/>
       <c r="S98" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T98" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U98" t="n">
         <v>35</v>
       </c>
       <c r="V98" t="n">
-        <v>46.39003</v>
+        <v>45.63058</v>
       </c>
       <c r="W98" t="n">
-        <v>-67.29386</v>
+        <v>-64.82858</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=188</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=645</t>
         </is>
       </c>
     </row>
@@ -7536,11 +7540,11 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Waterville Prospect &amp;quot;I&amp;quot;</t>
+          <t>Little Southwest Miramichi</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1413</v>
+        <v>621</v>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr"/>
@@ -7549,11 +7553,7 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>Au, Sb</t>
-        </is>
-      </c>
+      <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -7589,14 +7589,14 @@
         <v>35</v>
       </c>
       <c r="V99" t="n">
-        <v>46.05921</v>
+        <v>46.89643</v>
       </c>
       <c r="W99" t="n">
-        <v>-67.30663</v>
+        <v>-66.34998</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1413</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=621</t>
         </is>
       </c>
     </row>
@@ -7606,11 +7606,11 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Meridian Brook Crossing</t>
+          <t>Shepody Mountain Manganese</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>630</v>
+        <v>721</v>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr"/>
@@ -7619,7 +7619,11 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Mn</t>
+        </is>
+      </c>
       <c r="H100" t="inlineStr">
         <is>
           <t>Past Producer</t>
@@ -7646,23 +7650,23 @@
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr"/>
       <c r="S100" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T100" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="U100" t="n">
         <v>30</v>
       </c>
       <c r="V100" t="n">
-        <v>47.26747</v>
+        <v>45.80502</v>
       </c>
       <c r="W100" t="n">
-        <v>-66.68077</v>
+        <v>-64.65774</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=630</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=721</t>
         </is>
       </c>
     </row>
@@ -7672,11 +7676,11 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Shepody Mountain Manganese</t>
+          <t>South Hamilton Road</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>721</v>
+        <v>1412</v>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr"/>
@@ -7687,7 +7691,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Ag, Au, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -7716,23 +7720,23 @@
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr"/>
       <c r="S101" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T101" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U101" t="n">
         <v>30</v>
       </c>
       <c r="V101" t="n">
-        <v>45.80502</v>
+        <v>45.56892</v>
       </c>
       <c r="W101" t="n">
-        <v>-64.65774</v>
+        <v>-66.16552</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=721</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1412</t>
         </is>
       </c>
     </row>
@@ -7812,11 +7816,11 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>South Hamilton Road</t>
+          <t>Meridian Brook Crossing</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1412</v>
+        <v>630</v>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
@@ -7825,11 +7829,7 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>Ag, Au, Cu, Pb, Zn</t>
-        </is>
-      </c>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
           <t>Past Producer</t>
@@ -7856,23 +7856,23 @@
       <c r="Q103" t="inlineStr"/>
       <c r="R103" t="inlineStr"/>
       <c r="S103" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T103" t="n">
-        <v>325</v>
+        <v>100</v>
       </c>
       <c r="U103" t="n">
         <v>30</v>
       </c>
       <c r="V103" t="n">
-        <v>45.56892</v>
+        <v>47.26747</v>
       </c>
       <c r="W103" t="n">
-        <v>-66.16552</v>
+        <v>-66.68077</v>
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1412</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=630</t>
         </is>
       </c>
     </row>

--- a/site/nb_leads.xlsx
+++ b/site/nb_leads.xlsx
@@ -4446,10 +4446,10 @@
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T54" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U54" t="n">
         <v>37</v>

--- a/site/nb_leads.xlsx
+++ b/site/nb_leads.xlsx
@@ -570,11 +570,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Shin Creek</t>
+          <t>Sloop Cove</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
@@ -585,7 +585,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ag, Mo, W</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -627,14 +627,14 @@
         <v>45</v>
       </c>
       <c r="V2" t="n">
-        <v>45.55224</v>
+        <v>44.68722</v>
       </c>
       <c r="W2" t="n">
-        <v>-66.63357999999999</v>
+        <v>-66.87302</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=8</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=31</t>
         </is>
       </c>
     </row>
@@ -644,11 +644,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Evandale Stock *</t>
+          <t>Quispamsis</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -659,7 +659,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ag, Au, Cu</t>
+          <t>Ag, Au, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -701,14 +701,14 @@
         <v>45</v>
       </c>
       <c r="V3" t="n">
-        <v>45.58501</v>
+        <v>45.42362</v>
       </c>
       <c r="W3" t="n">
-        <v>-66.09690999999999</v>
+        <v>-65.95802</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=11</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=4</t>
         </is>
       </c>
     </row>
@@ -718,11 +718,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Quispamsis</t>
+          <t>Melanson Brook E</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>1026</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -733,7 +733,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ag, Au, Cu, Pb, Zn</t>
+          <t>Ag, Pb, Zn</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -775,14 +775,14 @@
         <v>45</v>
       </c>
       <c r="V4" t="n">
-        <v>45.42362</v>
+        <v>47.73447</v>
       </c>
       <c r="W4" t="n">
-        <v>-65.95802</v>
+        <v>-65.98719</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=4</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1026</t>
         </is>
       </c>
     </row>
@@ -792,11 +792,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pender Brook</t>
+          <t>Nigadoo 8</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>1028</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -807,7 +807,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sb</t>
+          <t>Ag, Au, Pb, Zn</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -840,23 +840,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T5" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U5" t="n">
         <v>45</v>
       </c>
       <c r="V5" t="n">
-        <v>45.57888</v>
+        <v>47.74616</v>
       </c>
       <c r="W5" t="n">
-        <v>-66.30664</v>
+        <v>-65.88711000000001</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=10</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1028</t>
         </is>
       </c>
     </row>
@@ -866,11 +866,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Taylor Village</t>
+          <t>Antinouri Lake West B</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>57</v>
+        <v>1021</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -881,7 +881,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ti</t>
+          <t>Pb, Zn</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -923,14 +923,14 @@
         <v>45</v>
       </c>
       <c r="V6" t="n">
-        <v>45.93834</v>
+        <v>47.78921</v>
       </c>
       <c r="W6" t="n">
-        <v>-64.55385</v>
+        <v>-65.99773</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=57</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1021</t>
         </is>
       </c>
     </row>
@@ -940,11 +940,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Quisibis Mountain</t>
+          <t>Payne Brook</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>58</v>
+        <v>1036</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -955,7 +955,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Ag, Pb, Zn</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -997,14 +997,14 @@
         <v>45</v>
       </c>
       <c r="V7" t="n">
-        <v>47.42337</v>
+        <v>47.74032</v>
       </c>
       <c r="W7" t="n">
-        <v>-67.96913000000001</v>
+        <v>-65.91246</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=58</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1036</t>
         </is>
       </c>
     </row>
@@ -1014,11 +1014,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Levesque Gulch</t>
+          <t>Belledune Pond</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1115</v>
+        <v>72</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Au, Cu, Sb</t>
+          <t>Ag, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1062,23 +1062,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T8" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U8" t="n">
         <v>45</v>
       </c>
       <c r="V8" t="n">
-        <v>47.6649</v>
+        <v>47.82638</v>
       </c>
       <c r="W8" t="n">
-        <v>-66.69267000000001</v>
+        <v>-65.97922</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1115</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=72</t>
         </is>
       </c>
     </row>
@@ -1088,11 +1088,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Antinouri Lake West A</t>
+          <t>St. Leonard Iron-Manganese</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ag, Cu, Pb, Zn</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1145,14 +1145,14 @@
         <v>45</v>
       </c>
       <c r="V9" t="n">
-        <v>47.78952</v>
+        <v>47.2053</v>
       </c>
       <c r="W9" t="n">
-        <v>-65.98515</v>
+        <v>-67.88663</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=85</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=101</t>
         </is>
       </c>
     </row>
@@ -1236,11 +1236,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>St. Leonard Iron-Manganese</t>
+          <t>Antinouri Lake West A</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Ag, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1293,14 +1293,14 @@
         <v>45</v>
       </c>
       <c r="V11" t="n">
-        <v>47.2053</v>
+        <v>47.78952</v>
       </c>
       <c r="W11" t="n">
-        <v>-67.88663</v>
+        <v>-65.98515</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=101</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=85</t>
         </is>
       </c>
     </row>
@@ -1310,11 +1310,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Belledune Pond</t>
+          <t>Levesque Gulch</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>72</v>
+        <v>1115</v>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ag, Cu, Pb, Zn</t>
+          <t>Au, Cu, Sb</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1358,23 +1358,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T12" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U12" t="n">
         <v>45</v>
       </c>
       <c r="V12" t="n">
-        <v>47.82638</v>
+        <v>47.6649</v>
       </c>
       <c r="W12" t="n">
-        <v>-65.97922</v>
+        <v>-66.69267000000001</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=72</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1115</t>
         </is>
       </c>
     </row>
@@ -1384,11 +1384,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Red Pine Brook</t>
+          <t>Gordon Meadow Brook East</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1408</v>
+        <v>1252</v>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Ag, Pb, Zn</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1441,14 +1441,14 @@
         <v>45</v>
       </c>
       <c r="V13" t="n">
-        <v>47.4492</v>
+        <v>47.39279</v>
       </c>
       <c r="W13" t="n">
-        <v>-65.62412999999999</v>
+        <v>-65.68568999999999</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1408</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1252</t>
         </is>
       </c>
     </row>
@@ -1458,11 +1458,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Little Sevogle River 1</t>
+          <t>Kenny Lake</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>60</v>
+        <v>1278</v>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Pb, Zn</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1506,23 +1506,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T14" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U14" t="n">
         <v>45</v>
       </c>
       <c r="V14" t="n">
-        <v>47.0005</v>
+        <v>47.23226</v>
       </c>
       <c r="W14" t="n">
-        <v>-65.98999999999999</v>
+        <v>-66.2908</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=60</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1278</t>
         </is>
       </c>
     </row>
@@ -1532,11 +1532,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Peekaboo Corner *</t>
+          <t>Green Creek North</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>27</v>
+        <v>1334</v>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
@@ -1589,14 +1589,14 @@
         <v>45</v>
       </c>
       <c r="V15" t="n">
-        <v>45.65473</v>
+        <v>45.79059</v>
       </c>
       <c r="W15" t="n">
-        <v>-65.71941</v>
+        <v>-64.44385</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=27</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1334</t>
         </is>
       </c>
     </row>
@@ -1606,11 +1606,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Gordon Meadow Brook East</t>
+          <t>Peekaboo Corner *</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1252</v>
+        <v>27</v>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ag, Pb, Zn</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1663,14 +1663,14 @@
         <v>45</v>
       </c>
       <c r="V16" t="n">
-        <v>47.39279</v>
+        <v>45.65473</v>
       </c>
       <c r="W16" t="n">
-        <v>-65.68568999999999</v>
+        <v>-65.71941</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1252</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=27</t>
         </is>
       </c>
     </row>
@@ -1680,11 +1680,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nigadoo 8</t>
+          <t>Shin Creek</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1028</v>
+        <v>8</v>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ag, Au, Pb, Zn</t>
+          <t>Ag, Mo, W</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1728,23 +1728,23 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T17" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U17" t="n">
         <v>45</v>
       </c>
       <c r="V17" t="n">
-        <v>47.74616</v>
+        <v>45.55224</v>
       </c>
       <c r="W17" t="n">
-        <v>-65.88711000000001</v>
+        <v>-66.63357999999999</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1028</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=8</t>
         </is>
       </c>
     </row>
@@ -1754,11 +1754,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Melanson Brook E</t>
+          <t>Quisibis Mountain</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1026</v>
+        <v>58</v>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ag, Pb, Zn</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1811,14 +1811,14 @@
         <v>45</v>
       </c>
       <c r="V18" t="n">
-        <v>47.73447</v>
+        <v>47.42337</v>
       </c>
       <c r="W18" t="n">
-        <v>-65.98719</v>
+        <v>-67.96913000000001</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1026</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=58</t>
         </is>
       </c>
     </row>
@@ -1828,11 +1828,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Antinouri Lake West B</t>
+          <t>Little Sevogle River 1</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1021</v>
+        <v>60</v>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pb, Zn</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1885,14 +1885,14 @@
         <v>45</v>
       </c>
       <c r="V19" t="n">
-        <v>47.78921</v>
+        <v>47.0005</v>
       </c>
       <c r="W19" t="n">
-        <v>-65.99773</v>
+        <v>-65.98999999999999</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1021</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=60</t>
         </is>
       </c>
     </row>
@@ -1902,11 +1902,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Kenny Lake</t>
+          <t>Taylor Village</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1278</v>
+        <v>57</v>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pb, Zn</t>
+          <t>Ti</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1950,23 +1950,23 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T20" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U20" t="n">
         <v>45</v>
       </c>
       <c r="V20" t="n">
-        <v>47.23226</v>
+        <v>45.93834</v>
       </c>
       <c r="W20" t="n">
-        <v>-66.2908</v>
+        <v>-64.55385</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1278</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=57</t>
         </is>
       </c>
     </row>
@@ -1976,11 +1976,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sloop Cove</t>
+          <t>South Glassville</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>31</v>
+        <v>1504</v>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2033,14 +2033,14 @@
         <v>45</v>
       </c>
       <c r="V21" t="n">
-        <v>44.68722</v>
+        <v>46.48057</v>
       </c>
       <c r="W21" t="n">
-        <v>-66.87302</v>
+        <v>-67.42028000000001</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=31</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1504</t>
         </is>
       </c>
     </row>
@@ -2050,11 +2050,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>South Glassville</t>
+          <t>Red Pine Brook</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1504</v>
+        <v>1408</v>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2107,14 +2107,14 @@
         <v>45</v>
       </c>
       <c r="V22" t="n">
-        <v>46.48057</v>
+        <v>47.4492</v>
       </c>
       <c r="W22" t="n">
-        <v>-67.42028000000001</v>
+        <v>-65.62412999999999</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1504</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1408</t>
         </is>
       </c>
     </row>
@@ -2124,11 +2124,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Green Creek North</t>
+          <t>Pender Brook</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1334</v>
+        <v>10</v>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Sb</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2181,14 +2181,14 @@
         <v>45</v>
       </c>
       <c r="V23" t="n">
-        <v>45.79059</v>
+        <v>45.57888</v>
       </c>
       <c r="W23" t="n">
-        <v>-64.44385</v>
+        <v>-66.30664</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1334</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=10</t>
         </is>
       </c>
     </row>
@@ -2198,11 +2198,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Payne Brook</t>
+          <t>Evandale Stock *</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1036</v>
+        <v>11</v>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ag, Pb, Zn</t>
+          <t>Ag, Au, Cu</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2255,14 +2255,14 @@
         <v>45</v>
       </c>
       <c r="V24" t="n">
-        <v>47.74032</v>
+        <v>45.58501</v>
       </c>
       <c r="W24" t="n">
-        <v>-65.91246</v>
+        <v>-66.09690999999999</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1036</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=11</t>
         </is>
       </c>
     </row>
@@ -2272,11 +2272,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Hayward Pinnacle</t>
+          <t>Joliffs Brook</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1575</v>
+        <v>555</v>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>Zn</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2329,14 +2329,14 @@
         <v>43</v>
       </c>
       <c r="V25" t="n">
-        <v>45.82761</v>
+        <v>45.73919</v>
       </c>
       <c r="W25" t="n">
-        <v>-64.9164</v>
+        <v>-65.75996000000001</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1575</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=555</t>
         </is>
       </c>
     </row>
@@ -2346,11 +2346,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Crory Farm</t>
+          <t>Martins Bluff</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>605</v>
+        <v>562</v>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
@@ -2359,11 +2359,7 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Cu, Pb, Zn</t>
-        </is>
-      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -2403,14 +2399,14 @@
         <v>43</v>
       </c>
       <c r="V26" t="n">
-        <v>45.08058</v>
+        <v>46.93142</v>
       </c>
       <c r="W26" t="n">
-        <v>-66.80913</v>
+        <v>-66.64663</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=605</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=562</t>
         </is>
       </c>
     </row>
@@ -2420,11 +2416,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Tennants Cove *</t>
+          <t>Ragged Falls &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>372</v>
+        <v>570</v>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
@@ -2435,7 +2431,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Th, U</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2468,23 +2464,23 @@
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T27" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U27" t="n">
         <v>43</v>
       </c>
       <c r="V27" t="n">
-        <v>45.58694</v>
+        <v>45.2353</v>
       </c>
       <c r="W27" t="n">
-        <v>-66.01414</v>
+        <v>-66.48052</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=372</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=570</t>
         </is>
       </c>
     </row>
@@ -2494,11 +2490,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ragged Falls &amp;quot;I&amp;quot;</t>
+          <t>Crory Farm</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>570</v>
+        <v>605</v>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
@@ -2509,7 +2505,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Th, U</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2542,23 +2538,23 @@
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T28" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U28" t="n">
         <v>43</v>
       </c>
       <c r="V28" t="n">
-        <v>45.2353</v>
+        <v>45.08058</v>
       </c>
       <c r="W28" t="n">
-        <v>-66.48052</v>
+        <v>-66.80913</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=570</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=605</t>
         </is>
       </c>
     </row>
@@ -2568,11 +2564,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Martins Bluff</t>
+          <t>Dickson Brook A,B,C</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>562</v>
+        <v>639</v>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
@@ -2581,7 +2577,11 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -2621,14 +2621,14 @@
         <v>43</v>
       </c>
       <c r="V29" t="n">
-        <v>46.93142</v>
+        <v>45.58364</v>
       </c>
       <c r="W29" t="n">
-        <v>-66.64663</v>
+        <v>-64.98524</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=562</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=639</t>
         </is>
       </c>
     </row>
@@ -2638,11 +2638,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Joliffs Brook</t>
+          <t>Three Bridge Brook East *</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>555</v>
+        <v>793</v>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Zn</t>
+          <t>Ag, Au, Pb, Zn</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2686,23 +2686,23 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T30" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U30" t="n">
         <v>43</v>
       </c>
       <c r="V30" t="n">
-        <v>45.73919</v>
+        <v>45.49419</v>
       </c>
       <c r="W30" t="n">
-        <v>-65.75996000000001</v>
+        <v>-66.48581</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=555</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=793</t>
         </is>
       </c>
     </row>
@@ -2712,11 +2712,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Dickson Brook A,B,C</t>
+          <t>Eel Ground</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>639</v>
+        <v>746</v>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2769,14 +2769,14 @@
         <v>43</v>
       </c>
       <c r="V31" t="n">
-        <v>45.58364</v>
+        <v>46.96447</v>
       </c>
       <c r="W31" t="n">
-        <v>-64.98524</v>
+        <v>-65.59441</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=639</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=746</t>
         </is>
       </c>
     </row>
@@ -2786,11 +2786,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Quaco Road &amp;quot;I&amp;quot;</t>
+          <t>Halls Hill</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>678</v>
+        <v>1324</v>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Cu, Zn</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2843,14 +2843,14 @@
         <v>43</v>
       </c>
       <c r="V32" t="n">
-        <v>45.38336</v>
+        <v>45.96809</v>
       </c>
       <c r="W32" t="n">
-        <v>-65.74996</v>
+        <v>-64.16996</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=678</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1324</t>
         </is>
       </c>
     </row>
@@ -2860,11 +2860,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Gowland Mountain *</t>
+          <t>Jacquet River M</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>643</v>
+        <v>955</v>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Ba, Cu</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2917,14 +2917,14 @@
         <v>43</v>
       </c>
       <c r="V33" t="n">
-        <v>45.81975</v>
+        <v>47.82559</v>
       </c>
       <c r="W33" t="n">
-        <v>-65.0483</v>
+        <v>-66.01662</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=643</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=955</t>
         </is>
       </c>
     </row>
@@ -2934,11 +2934,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Deed Brook</t>
+          <t>Letang Harbour North</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>717</v>
+        <v>1291</v>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2982,23 +2982,23 @@
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T34" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U34" t="n">
         <v>43</v>
       </c>
       <c r="V34" t="n">
-        <v>45.78808</v>
+        <v>45.08726</v>
       </c>
       <c r="W34" t="n">
-        <v>-64.85692</v>
+        <v>-66.7833</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=717</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1291</t>
         </is>
       </c>
     </row>
@@ -3008,11 +3008,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Irving</t>
+          <t>Dennis Stream - Upper &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1238</v>
+        <v>1306</v>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
@@ -3021,11 +3021,7 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Co, Cu, Ni</t>
-        </is>
-      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -3056,23 +3052,23 @@
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T35" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="U35" t="n">
         <v>43</v>
       </c>
       <c r="V35" t="n">
-        <v>45.19116</v>
+        <v>45.22199</v>
       </c>
       <c r="W35" t="n">
-        <v>-67.25942000000001</v>
+        <v>-67.27109</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1238</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1306</t>
         </is>
       </c>
     </row>
@@ -3082,11 +3078,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>St Stephen Ni - O Zone &amp;quot;I&amp;quot;</t>
+          <t>Gowland Mountain *</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1236</v>
+        <v>643</v>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
@@ -3097,7 +3093,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Co, Cu, Ni</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3130,23 +3126,23 @@
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T36" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U36" t="n">
         <v>43</v>
       </c>
       <c r="V36" t="n">
-        <v>45.23088</v>
+        <v>45.81975</v>
       </c>
       <c r="W36" t="n">
-        <v>-67.27692</v>
+        <v>-65.0483</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1236</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=643</t>
         </is>
       </c>
     </row>
@@ -3156,11 +3152,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Memramcook Gold &amp;quot;I&amp;quot;</t>
+          <t>Quaco Road &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>723</v>
+        <v>678</v>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
@@ -3171,7 +3167,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3204,23 +3200,23 @@
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T37" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U37" t="n">
         <v>43</v>
       </c>
       <c r="V37" t="n">
-        <v>45.96531</v>
+        <v>45.38336</v>
       </c>
       <c r="W37" t="n">
-        <v>-64.53885</v>
+        <v>-65.74996</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=723</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=678</t>
         </is>
       </c>
     </row>
@@ -3230,11 +3226,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Halls Hill</t>
+          <t>St Stephen Ni - O Zone &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1324</v>
+        <v>1236</v>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
@@ -3245,7 +3241,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cu, Zn</t>
+          <t>Co, Cu, Ni</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3278,23 +3274,23 @@
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T38" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U38" t="n">
         <v>43</v>
       </c>
       <c r="V38" t="n">
-        <v>45.96809</v>
+        <v>45.23088</v>
       </c>
       <c r="W38" t="n">
-        <v>-64.16996</v>
+        <v>-67.27692</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1324</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1236</t>
         </is>
       </c>
     </row>
@@ -3304,11 +3300,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Letang Harbour North</t>
+          <t>Irving</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1291</v>
+        <v>1238</v>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
@@ -3319,7 +3315,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Co, Cu, Ni</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3352,23 +3348,23 @@
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T39" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U39" t="n">
         <v>43</v>
       </c>
       <c r="V39" t="n">
-        <v>45.08726</v>
+        <v>45.19116</v>
       </c>
       <c r="W39" t="n">
-        <v>-66.7833</v>
+        <v>-67.25942000000001</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1291</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1238</t>
         </is>
       </c>
     </row>
@@ -3378,11 +3374,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Dennis Stream - Upper &amp;quot;I&amp;quot;</t>
+          <t>Pabineau River North Manganese</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1306</v>
+        <v>1272</v>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
@@ -3391,7 +3387,11 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Mn</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -3422,23 +3422,23 @@
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T40" t="n">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="U40" t="n">
         <v>43</v>
       </c>
       <c r="V40" t="n">
-        <v>45.22199</v>
+        <v>47.49558</v>
       </c>
       <c r="W40" t="n">
-        <v>-67.27109</v>
+        <v>-65.90329</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1306</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1272</t>
         </is>
       </c>
     </row>
@@ -3448,11 +3448,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Jacquet River M</t>
+          <t>Bass River Cu-Ni</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>955</v>
+        <v>1254</v>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ba, Cu</t>
+          <t>Cu, Ni</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3505,14 +3505,14 @@
         <v>43</v>
       </c>
       <c r="V41" t="n">
-        <v>47.82559</v>
+        <v>47.46421</v>
       </c>
       <c r="W41" t="n">
-        <v>-66.01662</v>
+        <v>-65.56607</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=955</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1254</t>
         </is>
       </c>
     </row>
@@ -3522,11 +3522,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Eel Ground</t>
+          <t>Memramcook Gold &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>746</v>
+        <v>723</v>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
@@ -3537,7 +3537,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3570,23 +3570,23 @@
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T42" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U42" t="n">
         <v>43</v>
       </c>
       <c r="V42" t="n">
-        <v>46.96447</v>
+        <v>45.96531</v>
       </c>
       <c r="W42" t="n">
-        <v>-65.59441</v>
+        <v>-64.53885</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=746</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=723</t>
         </is>
       </c>
     </row>
@@ -3596,11 +3596,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Three Bridge Brook East *</t>
+          <t>Deed Brook</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>793</v>
+        <v>717</v>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ag, Au, Pb, Zn</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3644,23 +3644,23 @@
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T43" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="U43" t="n">
         <v>43</v>
       </c>
       <c r="V43" t="n">
-        <v>45.49419</v>
+        <v>45.78808</v>
       </c>
       <c r="W43" t="n">
-        <v>-66.48581</v>
+        <v>-64.85692</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=793</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=717</t>
         </is>
       </c>
     </row>
@@ -3670,11 +3670,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Pabineau River North Manganese</t>
+          <t>Hayward Pinnacle</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1272</v>
+        <v>1575</v>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>U</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3718,23 +3718,23 @@
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T44" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U44" t="n">
         <v>43</v>
       </c>
       <c r="V44" t="n">
-        <v>47.49558</v>
+        <v>45.82761</v>
       </c>
       <c r="W44" t="n">
-        <v>-65.90329</v>
+        <v>-64.9164</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1272</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1575</t>
         </is>
       </c>
     </row>
@@ -3744,11 +3744,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Bass River Cu-Ni</t>
+          <t>Tennants Cove *</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1254</v>
+        <v>372</v>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cu, Ni</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3801,14 +3801,14 @@
         <v>43</v>
       </c>
       <c r="V45" t="n">
-        <v>47.46421</v>
+        <v>45.58694</v>
       </c>
       <c r="W45" t="n">
-        <v>-65.56607</v>
+        <v>-66.01414</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1254</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=372</t>
         </is>
       </c>
     </row>
@@ -3892,11 +3892,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Lower Birch Island</t>
+          <t>Brunswick No. 12</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>172</v>
+        <v>54</v>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ba, Fe, Mn</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>88.8 Mt</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -3949,14 +3949,14 @@
         <v>38</v>
       </c>
       <c r="V47" t="n">
-        <v>46.56864</v>
+        <v>47.47889</v>
       </c>
       <c r="W47" t="n">
-        <v>-66.57080000000001</v>
+        <v>-65.89218</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=172</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=54</t>
         </is>
       </c>
     </row>
@@ -3966,11 +3966,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nigadoo River Mine</t>
+          <t>Anomaly 102 &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>128</v>
+        <v>1151</v>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ag, Cu, Pb, Zn</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>1.1 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -4023,14 +4023,14 @@
         <v>38</v>
       </c>
       <c r="V48" t="n">
-        <v>47.73307</v>
+        <v>46.47865</v>
       </c>
       <c r="W48" t="n">
-        <v>-65.80642</v>
+        <v>-66.72996999999999</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=128</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1151</t>
         </is>
       </c>
     </row>
@@ -4040,11 +4040,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Austin Brook</t>
+          <t>Nigadoo River Mine</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>69</v>
+        <v>128</v>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
@@ -4055,7 +4055,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ag, Fe, Pb, Zn</t>
+          <t>Ag, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>164 kt</t>
+          <t>1.1 Mt</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -4088,23 +4088,23 @@
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T49" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U49" t="n">
         <v>38</v>
       </c>
       <c r="V49" t="n">
-        <v>47.39779</v>
+        <v>47.73307</v>
       </c>
       <c r="W49" t="n">
-        <v>-65.82302</v>
+        <v>-65.80642</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=69</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=128</t>
         </is>
       </c>
     </row>
@@ -4114,11 +4114,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Brunswick No. 12</t>
+          <t>Lower Birch Island</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>54</v>
+        <v>172</v>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Ba, Fe, Mn</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>88.8 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
@@ -4171,14 +4171,14 @@
         <v>38</v>
       </c>
       <c r="V50" t="n">
-        <v>47.47889</v>
+        <v>46.56864</v>
       </c>
       <c r="W50" t="n">
-        <v>-65.89218</v>
+        <v>-66.57080000000001</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=54</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=172</t>
         </is>
       </c>
     </row>
@@ -4188,11 +4188,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Anomaly 102 &amp;quot;I&amp;quot;</t>
+          <t>Austin Brook</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1151</v>
+        <v>69</v>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Ag, Fe, Pb, Zn</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>164 kt</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
@@ -4236,23 +4236,23 @@
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T51" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U51" t="n">
         <v>38</v>
       </c>
       <c r="V51" t="n">
-        <v>46.47865</v>
+        <v>47.39779</v>
       </c>
       <c r="W51" t="n">
-        <v>-66.72996999999999</v>
+        <v>-65.82302</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1151</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=69</t>
         </is>
       </c>
     </row>
@@ -4262,11 +4262,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Black Point</t>
+          <t>Taylors Island</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1333</v>
+        <v>32</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pb, Zn</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4315,14 +4315,14 @@
         <v>37</v>
       </c>
       <c r="V52" t="n">
-        <v>45.79448</v>
+        <v>45.22336</v>
       </c>
       <c r="W52" t="n">
-        <v>-64.42218</v>
+        <v>-66.12747</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1333</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=32</t>
         </is>
       </c>
     </row>
@@ -4332,11 +4332,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Jeanne Mance</t>
+          <t>Henry Lake</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1249</v>
+        <v>1510</v>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
@@ -4385,14 +4385,14 @@
         <v>37</v>
       </c>
       <c r="V53" t="n">
-        <v>47.36337</v>
+        <v>45.39473</v>
       </c>
       <c r="W53" t="n">
-        <v>-65.44329999999999</v>
+        <v>-65.60417</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1249</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1510</t>
         </is>
       </c>
     </row>
@@ -4402,11 +4402,11 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Bulls Creek 2</t>
+          <t>Little Nictor Lake</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1072</v>
+        <v>94</v>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
@@ -4417,7 +4417,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ag, Au, Co, Cu</t>
+          <t>Zn</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4455,14 +4455,14 @@
         <v>37</v>
       </c>
       <c r="V54" t="n">
-        <v>46.08809</v>
+        <v>47.40642</v>
       </c>
       <c r="W54" t="n">
-        <v>-67.56498000000001</v>
+        <v>-66.84441</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1072</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=94</t>
         </is>
       </c>
     </row>
@@ -4472,11 +4472,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Bulls Creek 1</t>
+          <t>Bulls Creek 2</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
@@ -4487,7 +4487,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Ag, Au, Co, Cu</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4525,14 +4525,14 @@
         <v>37</v>
       </c>
       <c r="V55" t="n">
-        <v>46.08421</v>
+        <v>46.08809</v>
       </c>
       <c r="W55" t="n">
-        <v>-67.57774999999999</v>
+        <v>-67.56498000000001</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1071</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1072</t>
         </is>
       </c>
     </row>
@@ -4542,11 +4542,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Little Nictor Lake</t>
+          <t>Bulls Creek 1</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>94</v>
+        <v>1071</v>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
@@ -4557,7 +4557,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Zn</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4595,14 +4595,14 @@
         <v>37</v>
       </c>
       <c r="V56" t="n">
-        <v>47.40642</v>
+        <v>46.08421</v>
       </c>
       <c r="W56" t="n">
-        <v>-66.84441</v>
+        <v>-67.57774999999999</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=94</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1071</t>
         </is>
       </c>
     </row>
@@ -4612,11 +4612,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Gaspereau River</t>
+          <t>Church Showing</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1300</v>
+        <v>726</v>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
@@ -4665,14 +4665,14 @@
         <v>37</v>
       </c>
       <c r="V57" t="n">
-        <v>46.08059</v>
+        <v>44.88974</v>
       </c>
       <c r="W57" t="n">
-        <v>-64.20996</v>
+        <v>-66.95386000000001</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1300</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=726</t>
         </is>
       </c>
     </row>
@@ -4682,11 +4682,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Church Showing</t>
+          <t>Jeanne Mance</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>726</v>
+        <v>1249</v>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
@@ -4735,14 +4735,14 @@
         <v>37</v>
       </c>
       <c r="V58" t="n">
-        <v>44.88974</v>
+        <v>47.36337</v>
       </c>
       <c r="W58" t="n">
-        <v>-66.95386000000001</v>
+        <v>-65.44329999999999</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=726</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1249</t>
         </is>
       </c>
     </row>
@@ -4752,11 +4752,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Basaltic Island West *</t>
+          <t>Black Point</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1347</v>
+        <v>1333</v>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
@@ -4805,14 +4805,14 @@
         <v>37</v>
       </c>
       <c r="V59" t="n">
-        <v>45.1392</v>
+        <v>45.79448</v>
       </c>
       <c r="W59" t="n">
-        <v>-66.92413999999999</v>
+        <v>-64.42218</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1347</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1333</t>
         </is>
       </c>
     </row>
@@ -4822,11 +4822,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Grande Anse</t>
+          <t>Quispamsis Exit</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1370</v>
+        <v>1338</v>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Ag, Au, Cu, Pb</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4875,14 +4875,14 @@
         <v>37</v>
       </c>
       <c r="V60" t="n">
-        <v>45.79615</v>
+        <v>45.42378</v>
       </c>
       <c r="W60" t="n">
-        <v>-64.50107</v>
+        <v>-65.92708</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1370</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1338</t>
         </is>
       </c>
     </row>
@@ -4892,11 +4892,11 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Johnson Mills</t>
+          <t>Basaltic Island West *</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1371</v>
+        <v>1347</v>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Pb, Zn</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4945,14 +4945,14 @@
         <v>37</v>
       </c>
       <c r="V61" t="n">
-        <v>45.76365</v>
+        <v>45.1392</v>
       </c>
       <c r="W61" t="n">
-        <v>-64.52218000000001</v>
+        <v>-66.92413999999999</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1371</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1347</t>
         </is>
       </c>
     </row>
@@ -4962,11 +4962,11 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Moores Mills #2</t>
+          <t>Frye Island North</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1374</v>
+        <v>1353</v>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
@@ -4977,7 +4977,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ag, Cu, Pb</t>
+          <t>Ag, Cu, F, Pb, Sb, Zn</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5006,23 +5006,23 @@
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T62" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U62" t="n">
         <v>37</v>
       </c>
       <c r="V62" t="n">
-        <v>45.29977</v>
+        <v>45.04753</v>
       </c>
       <c r="W62" t="n">
-        <v>-67.2533</v>
+        <v>-66.84469</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1374</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1353</t>
         </is>
       </c>
     </row>
@@ -5032,11 +5032,11 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Scoudouc River Quarry</t>
+          <t>Gaspereau River</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1367</v>
+        <v>1300</v>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
@@ -5047,7 +5047,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pb, Zn</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5085,14 +5085,14 @@
         <v>37</v>
       </c>
       <c r="V63" t="n">
-        <v>46.19643</v>
+        <v>46.08059</v>
       </c>
       <c r="W63" t="n">
-        <v>-64.54385000000001</v>
+        <v>-64.20996</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1367</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1300</t>
         </is>
       </c>
     </row>
@@ -5102,11 +5102,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Black Point North</t>
+          <t>Cape Maringouin # 1</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1368</v>
+        <v>1360</v>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cu, Zn</t>
+          <t>Cu, Pb</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5155,14 +5155,14 @@
         <v>37</v>
       </c>
       <c r="V64" t="n">
-        <v>45.80448</v>
+        <v>45.73532</v>
       </c>
       <c r="W64" t="n">
-        <v>-64.41634999999999</v>
+        <v>-64.54191</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1368</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1360</t>
         </is>
       </c>
     </row>
@@ -5172,11 +5172,11 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Shediac River # 2</t>
+          <t>Cape Maringouin # 2</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>As</t>
+          <t>Ag, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5225,14 +5225,14 @@
         <v>37</v>
       </c>
       <c r="V65" t="n">
-        <v>46.2417</v>
+        <v>45.73782</v>
       </c>
       <c r="W65" t="n">
-        <v>-64.6858</v>
+        <v>-64.53246</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1365</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1361</t>
         </is>
       </c>
     </row>
@@ -5242,11 +5242,11 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Rockport Shore</t>
+          <t>Digdeguash Cu *</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1362</v>
+        <v>1344</v>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
@@ -5257,7 +5257,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Cu, Zn</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5295,14 +5295,14 @@
         <v>37</v>
       </c>
       <c r="V66" t="n">
-        <v>45.72365</v>
+        <v>45.18698</v>
       </c>
       <c r="W66" t="n">
-        <v>-64.50663</v>
+        <v>-66.93774999999999</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1362</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1344</t>
         </is>
       </c>
     </row>
@@ -5312,11 +5312,11 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Cape Maringouin # 2</t>
+          <t>Rockport Shore</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
@@ -5327,7 +5327,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ag, Cu, Pb, Zn</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5365,14 +5365,14 @@
         <v>37</v>
       </c>
       <c r="V67" t="n">
-        <v>45.73782</v>
+        <v>45.72365</v>
       </c>
       <c r="W67" t="n">
-        <v>-64.53246</v>
+        <v>-64.50663</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1361</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1362</t>
         </is>
       </c>
     </row>
@@ -5382,11 +5382,11 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Cape Maringouin # 1</t>
+          <t>Black Point North</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1360</v>
+        <v>1368</v>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cu, Pb</t>
+          <t>Cu, Zn</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5435,14 +5435,14 @@
         <v>37</v>
       </c>
       <c r="V68" t="n">
-        <v>45.73532</v>
+        <v>45.80448</v>
       </c>
       <c r="W68" t="n">
-        <v>-64.54191</v>
+        <v>-64.41634999999999</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1360</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1368</t>
         </is>
       </c>
     </row>
@@ -5452,11 +5452,11 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Frye Island North</t>
+          <t>Grande Anse</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1353</v>
+        <v>1370</v>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
@@ -5467,7 +5467,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ag, Cu, F, Pb, Sb, Zn</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5505,14 +5505,14 @@
         <v>37</v>
       </c>
       <c r="V69" t="n">
-        <v>45.04753</v>
+        <v>45.79615</v>
       </c>
       <c r="W69" t="n">
-        <v>-66.84469</v>
+        <v>-64.50107</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1353</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1370</t>
         </is>
       </c>
     </row>
@@ -5522,11 +5522,11 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Quispamsis Exit</t>
+          <t>Sinclair Hill</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1338</v>
+        <v>9</v>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
@@ -5537,7 +5537,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ag, Au, Cu, Pb</t>
+          <t>Ag, Au, Cu</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5575,14 +5575,14 @@
         <v>37</v>
       </c>
       <c r="V70" t="n">
-        <v>45.42378</v>
+        <v>45.63113</v>
       </c>
       <c r="W70" t="n">
-        <v>-65.92708</v>
+        <v>-64.92274999999999</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1338</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=9</t>
         </is>
       </c>
     </row>
@@ -5592,11 +5592,11 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Digdeguash Cu *</t>
+          <t>Scoudouc River Quarry</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1344</v>
+        <v>1367</v>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cu, Zn</t>
+          <t>Pb, Zn</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5645,14 +5645,14 @@
         <v>37</v>
       </c>
       <c r="V71" t="n">
-        <v>45.18698</v>
+        <v>46.19643</v>
       </c>
       <c r="W71" t="n">
-        <v>-66.93774999999999</v>
+        <v>-64.54385000000001</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1344</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1367</t>
         </is>
       </c>
     </row>
@@ -5662,11 +5662,11 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Sinclair Hill</t>
+          <t>Shediac River # 2</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>9</v>
+        <v>1365</v>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
@@ -5677,7 +5677,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ag, Au, Cu</t>
+          <t>As</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5715,14 +5715,14 @@
         <v>37</v>
       </c>
       <c r="V72" t="n">
-        <v>45.63113</v>
+        <v>46.2417</v>
       </c>
       <c r="W72" t="n">
-        <v>-64.92274999999999</v>
+        <v>-64.6858</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=9</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1365</t>
         </is>
       </c>
     </row>
@@ -5732,11 +5732,11 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Taylors Island</t>
+          <t>Johnson Mills</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>32</v>
+        <v>1371</v>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
@@ -5747,7 +5747,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5785,14 +5785,14 @@
         <v>37</v>
       </c>
       <c r="V73" t="n">
-        <v>45.22336</v>
+        <v>45.76365</v>
       </c>
       <c r="W73" t="n">
-        <v>-66.12747</v>
+        <v>-64.52218000000001</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=32</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1371</t>
         </is>
       </c>
     </row>
@@ -5802,11 +5802,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Henry Lake</t>
+          <t>Moores Mills #2</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1510</v>
+        <v>1374</v>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
@@ -5817,7 +5817,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Ag, Cu, Pb</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5846,23 +5846,23 @@
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T74" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U74" t="n">
         <v>37</v>
       </c>
       <c r="V74" t="n">
-        <v>45.39473</v>
+        <v>45.29977</v>
       </c>
       <c r="W74" t="n">
-        <v>-65.60417</v>
+        <v>-67.2533</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1510</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1374</t>
         </is>
       </c>
     </row>
@@ -5942,11 +5942,11 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Four Mile Lake B</t>
+          <t>Jacquet River Cu - A</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1175</v>
+        <v>462</v>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr"/>
@@ -5955,7 +5955,11 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
       <c r="H76" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -5991,14 +5995,14 @@
         <v>35</v>
       </c>
       <c r="V76" t="n">
-        <v>46.63643</v>
+        <v>47.85476</v>
       </c>
       <c r="W76" t="n">
-        <v>-66.58274</v>
+        <v>-66.01551000000001</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1175</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=462</t>
         </is>
       </c>
     </row>
@@ -6008,11 +6012,11 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Caledonia Mountain</t>
+          <t>Brewers Mills</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1609</v>
+        <v>904</v>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
@@ -6023,7 +6027,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ti, V</t>
+          <t>As, Au</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6052,23 +6056,23 @@
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T77" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U77" t="n">
         <v>35</v>
       </c>
       <c r="V77" t="n">
-        <v>45.8698</v>
+        <v>46.0692</v>
       </c>
       <c r="W77" t="n">
-        <v>-64.73159</v>
+        <v>-67.0283</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1609</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=904</t>
         </is>
       </c>
     </row>
@@ -6078,11 +6082,11 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Jacquet River Cu - Mitchell Rd</t>
+          <t>Jacquet River K</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>461</v>
+        <v>973</v>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
@@ -6127,14 +6131,14 @@
         <v>35</v>
       </c>
       <c r="V78" t="n">
-        <v>47.82725</v>
+        <v>47.83142</v>
       </c>
       <c r="W78" t="n">
-        <v>-66.00606999999999</v>
+        <v>-66.03246</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=461</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=973</t>
         </is>
       </c>
     </row>
@@ -6144,11 +6148,11 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Jacquet River Cu - A</t>
+          <t>Caledonia Mountain</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>462</v>
+        <v>1609</v>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
@@ -6159,7 +6163,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Ti, V</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6188,23 +6192,23 @@
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T79" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U79" t="n">
         <v>35</v>
       </c>
       <c r="V79" t="n">
-        <v>47.85476</v>
+        <v>45.8698</v>
       </c>
       <c r="W79" t="n">
-        <v>-66.01551000000001</v>
+        <v>-64.73159</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=462</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1609</t>
         </is>
       </c>
     </row>
@@ -6214,11 +6218,11 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Dumfries *</t>
+          <t>Centreville &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>535</v>
+        <v>263</v>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
@@ -6229,7 +6233,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -6267,14 +6271,14 @@
         <v>35</v>
       </c>
       <c r="V80" t="n">
-        <v>45.95029</v>
+        <v>46.44281</v>
       </c>
       <c r="W80" t="n">
-        <v>-67.12273999999999</v>
+        <v>-67.6808</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=535</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=263</t>
         </is>
       </c>
     </row>
@@ -6284,11 +6288,11 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Letete Mine</t>
+          <t>Waterville Prospect &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>311</v>
+        <v>1413</v>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
@@ -6299,12 +6303,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Au, Sb</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I81" t="b">
@@ -6315,15 +6319,11 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>1.9 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
+      <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="n">
         <v>0</v>
@@ -6332,23 +6332,23 @@
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T81" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U81" t="n">
         <v>35</v>
       </c>
       <c r="V81" t="n">
-        <v>45.06529</v>
+        <v>46.05921</v>
       </c>
       <c r="W81" t="n">
-        <v>-66.91136</v>
+        <v>-67.30663</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=311</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1413</t>
         </is>
       </c>
     </row>
@@ -6358,11 +6358,11 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Silver Island</t>
+          <t>Indian Brook</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>586</v>
+        <v>262</v>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
@@ -6371,11 +6371,7 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Ag, Pb, Zn</t>
-        </is>
-      </c>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -6411,14 +6407,14 @@
         <v>35</v>
       </c>
       <c r="V82" t="n">
-        <v>45.12114</v>
+        <v>46.73226</v>
       </c>
       <c r="W82" t="n">
-        <v>-66.8458</v>
+        <v>-67.42440999999999</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=586</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=262</t>
         </is>
       </c>
     </row>
@@ -6428,11 +6424,11 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Forty Five River &amp;quot;I&amp;quot;</t>
+          <t>Brummagen Brook Bog</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>647</v>
+        <v>188</v>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
@@ -6443,7 +6439,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -6472,23 +6468,23 @@
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T83" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U83" t="n">
         <v>35</v>
       </c>
       <c r="V83" t="n">
-        <v>45.74309</v>
+        <v>46.39003</v>
       </c>
       <c r="W83" t="n">
-        <v>-64.93053</v>
+        <v>-67.29386</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=647</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=188</t>
         </is>
       </c>
     </row>
@@ -6498,11 +6494,11 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Phyllis Creek &amp;quot;I&amp;quot;</t>
+          <t>Pecks Point South</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>655</v>
+        <v>1329</v>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
@@ -6513,7 +6509,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Ag, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -6551,14 +6547,14 @@
         <v>35</v>
       </c>
       <c r="V84" t="n">
-        <v>45.94808</v>
+        <v>45.73809</v>
       </c>
       <c r="W84" t="n">
-        <v>-66.69441</v>
+        <v>-64.48524</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=655</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1329</t>
         </is>
       </c>
     </row>
@@ -6568,11 +6564,11 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Pirate Lake</t>
+          <t>Dumfries *</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>516</v>
+        <v>535</v>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
@@ -6583,7 +6579,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -6621,14 +6617,14 @@
         <v>35</v>
       </c>
       <c r="V85" t="n">
-        <v>45.72697</v>
+        <v>45.95029</v>
       </c>
       <c r="W85" t="n">
-        <v>-67.67525000000001</v>
+        <v>-67.12273999999999</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=516</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=535</t>
         </is>
       </c>
     </row>
@@ -6638,11 +6634,11 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Pecks Point South</t>
+          <t>Pirate Lake</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1329</v>
+        <v>516</v>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
@@ -6653,7 +6649,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Ag, Cu, Pb, Zn</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6691,14 +6687,14 @@
         <v>35</v>
       </c>
       <c r="V86" t="n">
-        <v>45.73809</v>
+        <v>45.72697</v>
       </c>
       <c r="W86" t="n">
-        <v>-64.48524</v>
+        <v>-67.67525000000001</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1329</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=516</t>
         </is>
       </c>
     </row>
@@ -6708,11 +6704,11 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>East Quoddy Head</t>
+          <t>Elmtree 7B</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>737</v>
+        <v>854</v>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
@@ -6723,7 +6719,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pb</t>
+          <t>Cu, Ni</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -6752,23 +6748,23 @@
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr"/>
       <c r="S87" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T87" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U87" t="n">
         <v>35</v>
       </c>
       <c r="V87" t="n">
-        <v>44.95391</v>
+        <v>47.78253</v>
       </c>
       <c r="W87" t="n">
-        <v>-66.90831</v>
+        <v>-65.87246</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=737</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=854</t>
         </is>
       </c>
     </row>
@@ -6778,11 +6774,11 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Meadow Brook Cove</t>
+          <t>Four Mile Lake B</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>727</v>
+        <v>1175</v>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
@@ -6791,11 +6787,7 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Fe, Zn</t>
-        </is>
-      </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -6831,14 +6823,14 @@
         <v>35</v>
       </c>
       <c r="V88" t="n">
-        <v>44.88281</v>
+        <v>46.63643</v>
       </c>
       <c r="W88" t="n">
-        <v>-66.90774999999999</v>
+        <v>-66.58274</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=727</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1175</t>
         </is>
       </c>
     </row>
@@ -6848,11 +6840,11 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Jacquet River K</t>
+          <t>Meadow Brook Cove</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>973</v>
+        <v>727</v>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
@@ -6861,7 +6853,11 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Fe, Zn</t>
+        </is>
+      </c>
       <c r="H89" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -6897,14 +6893,14 @@
         <v>35</v>
       </c>
       <c r="V89" t="n">
-        <v>47.83142</v>
+        <v>44.88281</v>
       </c>
       <c r="W89" t="n">
-        <v>-66.03246</v>
+        <v>-66.90774999999999</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=973</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=727</t>
         </is>
       </c>
     </row>
@@ -6914,11 +6910,11 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Little Southwest Miramichi</t>
+          <t>East Quoddy Head</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>621</v>
+        <v>737</v>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr"/>
@@ -6927,7 +6923,11 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Pb</t>
+        </is>
+      </c>
       <c r="H90" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -6963,14 +6963,14 @@
         <v>35</v>
       </c>
       <c r="V90" t="n">
-        <v>46.89643</v>
+        <v>44.95391</v>
       </c>
       <c r="W90" t="n">
-        <v>-66.34998</v>
+        <v>-66.90831</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=621</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=737</t>
         </is>
       </c>
     </row>
@@ -6980,11 +6980,11 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Waterside Manganese</t>
+          <t>Silver Island</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>645</v>
+        <v>586</v>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
@@ -6995,7 +6995,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Ag, Pb, Zn</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -7024,23 +7024,23 @@
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr"/>
       <c r="S91" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T91" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U91" t="n">
         <v>35</v>
       </c>
       <c r="V91" t="n">
-        <v>45.63058</v>
+        <v>45.12114</v>
       </c>
       <c r="W91" t="n">
-        <v>-64.82858</v>
+        <v>-66.8458</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=645</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=586</t>
         </is>
       </c>
     </row>
@@ -7050,11 +7050,11 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Brewers Mills</t>
+          <t>Phyllis Creek &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>904</v>
+        <v>655</v>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr"/>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>As, Au</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -7103,14 +7103,14 @@
         <v>35</v>
       </c>
       <c r="V92" t="n">
-        <v>46.0692</v>
+        <v>45.94808</v>
       </c>
       <c r="W92" t="n">
-        <v>-67.0283</v>
+        <v>-66.69441</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=904</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=655</t>
         </is>
       </c>
     </row>
@@ -7120,11 +7120,11 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Elmtree 7B</t>
+          <t>Jacquet River Cu - Mitchell Rd</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>854</v>
+        <v>461</v>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
@@ -7133,11 +7133,7 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>Cu, Ni</t>
-        </is>
-      </c>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -7164,23 +7160,23 @@
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr"/>
       <c r="S93" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T93" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U93" t="n">
         <v>35</v>
       </c>
       <c r="V93" t="n">
-        <v>47.78253</v>
+        <v>47.82725</v>
       </c>
       <c r="W93" t="n">
-        <v>-65.87246</v>
+        <v>-66.00606999999999</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=854</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=461</t>
         </is>
       </c>
     </row>
@@ -7190,11 +7186,11 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>MacIntosh Brook</t>
+          <t>Maple Ridge</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>192</v>
+        <v>152</v>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
@@ -7205,7 +7201,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Mo, W</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -7234,23 +7230,23 @@
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr"/>
       <c r="S94" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T94" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U94" t="n">
         <v>35</v>
       </c>
       <c r="V94" t="n">
-        <v>46.35335</v>
+        <v>46.10003</v>
       </c>
       <c r="W94" t="n">
-        <v>-67.27636</v>
+        <v>-67.21413</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=192</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=152</t>
         </is>
       </c>
     </row>
@@ -7260,11 +7256,11 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Maple Ridge</t>
+          <t>MacIntosh Brook</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>152</v>
+        <v>192</v>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
@@ -7275,7 +7271,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Mo, W</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -7304,23 +7300,23 @@
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="inlineStr"/>
       <c r="S95" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T95" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U95" t="n">
         <v>35</v>
       </c>
       <c r="V95" t="n">
-        <v>46.10003</v>
+        <v>46.35335</v>
       </c>
       <c r="W95" t="n">
-        <v>-67.21413</v>
+        <v>-67.27636</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=152</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=192</t>
         </is>
       </c>
     </row>
@@ -7330,11 +7326,11 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Indian Brook</t>
+          <t>Letete Mine</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>262</v>
+        <v>311</v>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
@@ -7343,10 +7339,14 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I96" t="b">
@@ -7357,11 +7357,15 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>1.9 Mt</t>
         </is>
       </c>
       <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="n">
         <v>0</v>
@@ -7370,23 +7374,23 @@
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr"/>
       <c r="S96" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T96" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U96" t="n">
         <v>35</v>
       </c>
       <c r="V96" t="n">
-        <v>46.73226</v>
+        <v>45.06529</v>
       </c>
       <c r="W96" t="n">
-        <v>-67.42440999999999</v>
+        <v>-66.91136</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=262</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=311</t>
         </is>
       </c>
     </row>
@@ -7396,11 +7400,11 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Centreville &amp;quot;I&amp;quot;</t>
+          <t>Forty Five River &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>263</v>
+        <v>647</v>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
@@ -7411,7 +7415,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -7440,23 +7444,23 @@
       <c r="Q97" t="inlineStr"/>
       <c r="R97" t="inlineStr"/>
       <c r="S97" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T97" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U97" t="n">
         <v>35</v>
       </c>
       <c r="V97" t="n">
-        <v>46.44281</v>
+        <v>45.74309</v>
       </c>
       <c r="W97" t="n">
-        <v>-67.6808</v>
+        <v>-64.93053</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=263</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=647</t>
         </is>
       </c>
     </row>
@@ -7466,11 +7470,11 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Brummagen Brook Bog</t>
+          <t>Waterside Manganese</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>188</v>
+        <v>645</v>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
@@ -7510,23 +7514,23 @@
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr"/>
       <c r="S98" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T98" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U98" t="n">
         <v>35</v>
       </c>
       <c r="V98" t="n">
-        <v>46.39003</v>
+        <v>45.63058</v>
       </c>
       <c r="W98" t="n">
-        <v>-67.29386</v>
+        <v>-64.82858</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=188</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=645</t>
         </is>
       </c>
     </row>
@@ -7536,11 +7540,11 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Waterville Prospect &amp;quot;I&amp;quot;</t>
+          <t>Little Southwest Miramichi</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1413</v>
+        <v>621</v>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr"/>
@@ -7549,11 +7553,7 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>Au, Sb</t>
-        </is>
-      </c>
+      <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -7589,14 +7589,14 @@
         <v>35</v>
       </c>
       <c r="V99" t="n">
-        <v>46.05921</v>
+        <v>46.89643</v>
       </c>
       <c r="W99" t="n">
-        <v>-67.30663</v>
+        <v>-66.34998</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1413</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=621</t>
         </is>
       </c>
     </row>
@@ -7606,11 +7606,11 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Meridian Brook Crossing</t>
+          <t>Shepody Mountain Manganese</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>630</v>
+        <v>721</v>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr"/>
@@ -7619,7 +7619,11 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Mn</t>
+        </is>
+      </c>
       <c r="H100" t="inlineStr">
         <is>
           <t>Past Producer</t>
@@ -7646,23 +7650,23 @@
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr"/>
       <c r="S100" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T100" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="U100" t="n">
         <v>30</v>
       </c>
       <c r="V100" t="n">
-        <v>47.26747</v>
+        <v>45.80502</v>
       </c>
       <c r="W100" t="n">
-        <v>-66.68077</v>
+        <v>-64.65774</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=630</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=721</t>
         </is>
       </c>
     </row>
@@ -7672,11 +7676,11 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Shepody Mountain Manganese</t>
+          <t>South Hamilton Road</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>721</v>
+        <v>1412</v>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr"/>
@@ -7687,7 +7691,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Ag, Au, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -7716,23 +7720,23 @@
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr"/>
       <c r="S101" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T101" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U101" t="n">
         <v>30</v>
       </c>
       <c r="V101" t="n">
-        <v>45.80502</v>
+        <v>45.56892</v>
       </c>
       <c r="W101" t="n">
-        <v>-64.65774</v>
+        <v>-66.16552</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=721</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1412</t>
         </is>
       </c>
     </row>
@@ -7812,11 +7816,11 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>South Hamilton Road</t>
+          <t>Meridian Brook Crossing</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1412</v>
+        <v>630</v>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
@@ -7825,11 +7829,7 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>Ag, Au, Cu, Pb, Zn</t>
-        </is>
-      </c>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
           <t>Past Producer</t>
@@ -7856,23 +7856,23 @@
       <c r="Q103" t="inlineStr"/>
       <c r="R103" t="inlineStr"/>
       <c r="S103" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T103" t="n">
-        <v>325</v>
+        <v>100</v>
       </c>
       <c r="U103" t="n">
         <v>30</v>
       </c>
       <c r="V103" t="n">
-        <v>45.56892</v>
+        <v>47.26747</v>
       </c>
       <c r="W103" t="n">
-        <v>-66.16552</v>
+        <v>-66.68077</v>
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1412</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=630</t>
         </is>
       </c>
     </row>

--- a/site/nb_leads.xlsx
+++ b/site/nb_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X105"/>
+  <dimension ref="A1:X101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -570,11 +570,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sloop Cove</t>
+          <t>Shin Creek</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
@@ -585,7 +585,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Ag, Mo, W</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -627,14 +627,14 @@
         <v>45</v>
       </c>
       <c r="V2" t="n">
-        <v>44.68722</v>
+        <v>45.55224</v>
       </c>
       <c r="W2" t="n">
-        <v>-66.87302</v>
+        <v>-66.63357999999999</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=31</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=8</t>
         </is>
       </c>
     </row>
@@ -644,11 +644,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Quispamsis</t>
+          <t>Evandale Stock *</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -659,7 +659,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ag, Au, Cu, Pb, Zn</t>
+          <t>Ag, Au, Cu</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -701,14 +701,14 @@
         <v>45</v>
       </c>
       <c r="V3" t="n">
-        <v>45.42362</v>
+        <v>45.58501</v>
       </c>
       <c r="W3" t="n">
-        <v>-65.95802</v>
+        <v>-66.09690999999999</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=4</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=11</t>
         </is>
       </c>
     </row>
@@ -718,11 +718,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Melanson Brook E</t>
+          <t>Quispamsis</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1026</v>
+        <v>4</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -733,7 +733,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ag, Pb, Zn</t>
+          <t>Ag, Au, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -775,14 +775,14 @@
         <v>45</v>
       </c>
       <c r="V4" t="n">
-        <v>47.73447</v>
+        <v>45.42362</v>
       </c>
       <c r="W4" t="n">
-        <v>-65.98719</v>
+        <v>-65.95802</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1026</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=4</t>
         </is>
       </c>
     </row>
@@ -792,11 +792,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nigadoo 8</t>
+          <t>Pender Brook</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1028</v>
+        <v>10</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -807,7 +807,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ag, Au, Pb, Zn</t>
+          <t>Sb</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -840,23 +840,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T5" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U5" t="n">
         <v>45</v>
       </c>
       <c r="V5" t="n">
-        <v>47.74616</v>
+        <v>45.57888</v>
       </c>
       <c r="W5" t="n">
-        <v>-65.88711000000001</v>
+        <v>-66.30664</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1028</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=10</t>
         </is>
       </c>
     </row>
@@ -866,11 +866,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Antinouri Lake West B</t>
+          <t>Taylor Village</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1021</v>
+        <v>57</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -881,7 +881,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pb, Zn</t>
+          <t>Ti</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -923,14 +923,14 @@
         <v>45</v>
       </c>
       <c r="V6" t="n">
-        <v>47.78921</v>
+        <v>45.93834</v>
       </c>
       <c r="W6" t="n">
-        <v>-65.99773</v>
+        <v>-64.55385</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1021</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=57</t>
         </is>
       </c>
     </row>
@@ -940,11 +940,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Payne Brook</t>
+          <t>Quisibis Mountain</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1036</v>
+        <v>58</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -955,7 +955,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ag, Pb, Zn</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -997,14 +997,14 @@
         <v>45</v>
       </c>
       <c r="V7" t="n">
-        <v>47.74032</v>
+        <v>47.42337</v>
       </c>
       <c r="W7" t="n">
-        <v>-65.91246</v>
+        <v>-67.96913000000001</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1036</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=58</t>
         </is>
       </c>
     </row>
@@ -1014,11 +1014,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Belledune Pond</t>
+          <t>Levesque Gulch</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>72</v>
+        <v>1115</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ag, Cu, Pb, Zn</t>
+          <t>Au, Cu, Sb</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1062,23 +1062,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T8" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U8" t="n">
         <v>45</v>
       </c>
       <c r="V8" t="n">
-        <v>47.82638</v>
+        <v>47.6649</v>
       </c>
       <c r="W8" t="n">
-        <v>-65.97922</v>
+        <v>-66.69267000000001</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=72</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1115</t>
         </is>
       </c>
     </row>
@@ -1088,11 +1088,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>St. Leonard Iron-Manganese</t>
+          <t>Antinouri Lake West A</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Ag, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1145,14 +1145,14 @@
         <v>45</v>
       </c>
       <c r="V9" t="n">
-        <v>47.2053</v>
+        <v>47.78952</v>
       </c>
       <c r="W9" t="n">
-        <v>-67.88663</v>
+        <v>-65.98515</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=101</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=85</t>
         </is>
       </c>
     </row>
@@ -1236,11 +1236,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Antinouri Lake West A</t>
+          <t>St. Leonard Iron-Manganese</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ag, Cu, Pb, Zn</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1293,14 +1293,14 @@
         <v>45</v>
       </c>
       <c r="V11" t="n">
-        <v>47.78952</v>
+        <v>47.2053</v>
       </c>
       <c r="W11" t="n">
-        <v>-65.98515</v>
+        <v>-67.88663</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=85</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=101</t>
         </is>
       </c>
     </row>
@@ -1310,11 +1310,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Levesque Gulch</t>
+          <t>Belledune Pond</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1115</v>
+        <v>72</v>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Au, Cu, Sb</t>
+          <t>Ag, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1358,23 +1358,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T12" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U12" t="n">
         <v>45</v>
       </c>
       <c r="V12" t="n">
-        <v>47.6649</v>
+        <v>47.82638</v>
       </c>
       <c r="W12" t="n">
-        <v>-66.69267000000001</v>
+        <v>-65.97922</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1115</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=72</t>
         </is>
       </c>
     </row>
@@ -1384,11 +1384,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Gordon Meadow Brook East</t>
+          <t>Red Pine Brook</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1252</v>
+        <v>1408</v>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ag, Pb, Zn</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1441,14 +1441,14 @@
         <v>45</v>
       </c>
       <c r="V13" t="n">
-        <v>47.39279</v>
+        <v>47.4492</v>
       </c>
       <c r="W13" t="n">
-        <v>-65.68568999999999</v>
+        <v>-65.62412999999999</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1252</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1408</t>
         </is>
       </c>
     </row>
@@ -1458,11 +1458,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kenny Lake</t>
+          <t>Little Sevogle River 1</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1278</v>
+        <v>60</v>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pb, Zn</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1506,23 +1506,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T14" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U14" t="n">
         <v>45</v>
       </c>
       <c r="V14" t="n">
-        <v>47.23226</v>
+        <v>47.0005</v>
       </c>
       <c r="W14" t="n">
-        <v>-66.2908</v>
+        <v>-65.98999999999999</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1278</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=60</t>
         </is>
       </c>
     </row>
@@ -1532,11 +1532,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Green Creek North</t>
+          <t>Peekaboo Corner *</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1334</v>
+        <v>27</v>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
@@ -1589,14 +1589,14 @@
         <v>45</v>
       </c>
       <c r="V15" t="n">
-        <v>45.79059</v>
+        <v>45.65473</v>
       </c>
       <c r="W15" t="n">
-        <v>-64.44385</v>
+        <v>-65.71941</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1334</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=27</t>
         </is>
       </c>
     </row>
@@ -1606,11 +1606,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Peekaboo Corner *</t>
+          <t>Gordon Meadow Brook East</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>27</v>
+        <v>1252</v>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Ag, Pb, Zn</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1663,14 +1663,14 @@
         <v>45</v>
       </c>
       <c r="V16" t="n">
-        <v>45.65473</v>
+        <v>47.39279</v>
       </c>
       <c r="W16" t="n">
-        <v>-65.71941</v>
+        <v>-65.68568999999999</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=27</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1252</t>
         </is>
       </c>
     </row>
@@ -1680,11 +1680,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Shin Creek</t>
+          <t>Nigadoo 8</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>1028</v>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ag, Mo, W</t>
+          <t>Ag, Au, Pb, Zn</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1728,23 +1728,23 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T17" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U17" t="n">
         <v>45</v>
       </c>
       <c r="V17" t="n">
-        <v>45.55224</v>
+        <v>47.74616</v>
       </c>
       <c r="W17" t="n">
-        <v>-66.63357999999999</v>
+        <v>-65.88711000000001</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=8</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1028</t>
         </is>
       </c>
     </row>
@@ -1754,11 +1754,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Quisibis Mountain</t>
+          <t>Melanson Brook E</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>58</v>
+        <v>1026</v>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Ag, Pb, Zn</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1811,14 +1811,14 @@
         <v>45</v>
       </c>
       <c r="V18" t="n">
-        <v>47.42337</v>
+        <v>47.73447</v>
       </c>
       <c r="W18" t="n">
-        <v>-67.96913000000001</v>
+        <v>-65.98719</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=58</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1026</t>
         </is>
       </c>
     </row>
@@ -1828,11 +1828,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Little Sevogle River 1</t>
+          <t>Antinouri Lake West B</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>1021</v>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Pb, Zn</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1885,14 +1885,14 @@
         <v>45</v>
       </c>
       <c r="V19" t="n">
-        <v>47.0005</v>
+        <v>47.78921</v>
       </c>
       <c r="W19" t="n">
-        <v>-65.98999999999999</v>
+        <v>-65.99773</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=60</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1021</t>
         </is>
       </c>
     </row>
@@ -1902,11 +1902,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Taylor Village</t>
+          <t>Sloop Cove</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ti</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1959,14 +1959,14 @@
         <v>45</v>
       </c>
       <c r="V20" t="n">
-        <v>45.93834</v>
+        <v>44.68722</v>
       </c>
       <c r="W20" t="n">
-        <v>-64.55385</v>
+        <v>-66.87302</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=57</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=31</t>
         </is>
       </c>
     </row>
@@ -2050,11 +2050,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Red Pine Brook</t>
+          <t>Green Creek North</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1408</v>
+        <v>1334</v>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2107,14 +2107,14 @@
         <v>45</v>
       </c>
       <c r="V22" t="n">
-        <v>47.4492</v>
+        <v>45.79059</v>
       </c>
       <c r="W22" t="n">
-        <v>-65.62412999999999</v>
+        <v>-64.44385</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1408</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1334</t>
         </is>
       </c>
     </row>
@@ -2124,11 +2124,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pender Brook</t>
+          <t>Payne Brook</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>10</v>
+        <v>1036</v>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sb</t>
+          <t>Ag, Pb, Zn</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2181,14 +2181,14 @@
         <v>45</v>
       </c>
       <c r="V23" t="n">
-        <v>45.57888</v>
+        <v>47.74032</v>
       </c>
       <c r="W23" t="n">
-        <v>-66.30664</v>
+        <v>-65.91246</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=10</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1036</t>
         </is>
       </c>
     </row>
@@ -2198,11 +2198,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Evandale Stock *</t>
+          <t>Hayward Pinnacle</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>11</v>
+        <v>1575</v>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ag, Au, Cu</t>
+          <t>U</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Developed Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I24" t="b">
@@ -2252,17 +2252,17 @@
         <v>325</v>
       </c>
       <c r="U24" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="V24" t="n">
-        <v>45.58501</v>
+        <v>45.82761</v>
       </c>
       <c r="W24" t="n">
-        <v>-66.09690999999999</v>
+        <v>-64.9164</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=11</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1575</t>
         </is>
       </c>
     </row>
@@ -2272,11 +2272,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Joliffs Brook</t>
+          <t>Crory Farm</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>555</v>
+        <v>605</v>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Zn</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2329,14 +2329,14 @@
         <v>43</v>
       </c>
       <c r="V25" t="n">
-        <v>45.73919</v>
+        <v>45.08058</v>
       </c>
       <c r="W25" t="n">
-        <v>-65.75996000000001</v>
+        <v>-66.80913</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=555</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=605</t>
         </is>
       </c>
     </row>
@@ -2346,11 +2346,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Martins Bluff</t>
+          <t>Tennants Cove *</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>562</v>
+        <v>372</v>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
@@ -2359,7 +2359,11 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Cu, Pb, Zn</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -2399,14 +2403,14 @@
         <v>43</v>
       </c>
       <c r="V26" t="n">
-        <v>46.93142</v>
+        <v>45.58694</v>
       </c>
       <c r="W26" t="n">
-        <v>-66.64663</v>
+        <v>-66.01414</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=562</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=372</t>
         </is>
       </c>
     </row>
@@ -2490,11 +2494,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Crory Farm</t>
+          <t>Martins Bluff</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>605</v>
+        <v>562</v>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
@@ -2503,11 +2507,7 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Cu, Pb, Zn</t>
-        </is>
-      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -2547,14 +2547,14 @@
         <v>43</v>
       </c>
       <c r="V28" t="n">
-        <v>45.08058</v>
+        <v>46.93142</v>
       </c>
       <c r="W28" t="n">
-        <v>-66.80913</v>
+        <v>-66.64663</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=605</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=562</t>
         </is>
       </c>
     </row>
@@ -2564,11 +2564,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Dickson Brook A,B,C</t>
+          <t>Joliffs Brook</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>639</v>
+        <v>555</v>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Zn</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2621,14 +2621,14 @@
         <v>43</v>
       </c>
       <c r="V29" t="n">
-        <v>45.58364</v>
+        <v>45.73919</v>
       </c>
       <c r="W29" t="n">
-        <v>-64.98524</v>
+        <v>-65.75996000000001</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=639</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=555</t>
         </is>
       </c>
     </row>
@@ -2638,11 +2638,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Three Bridge Brook East *</t>
+          <t>Dickson Brook A,B,C</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>793</v>
+        <v>639</v>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ag, Au, Pb, Zn</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2686,23 +2686,23 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T30" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U30" t="n">
         <v>43</v>
       </c>
       <c r="V30" t="n">
-        <v>45.49419</v>
+        <v>45.58364</v>
       </c>
       <c r="W30" t="n">
-        <v>-66.48581</v>
+        <v>-64.98524</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=793</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=639</t>
         </is>
       </c>
     </row>
@@ -2712,11 +2712,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Eel Ground</t>
+          <t>Quaco Road &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>746</v>
+        <v>678</v>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2769,14 +2769,14 @@
         <v>43</v>
       </c>
       <c r="V31" t="n">
-        <v>46.96447</v>
+        <v>45.38336</v>
       </c>
       <c r="W31" t="n">
-        <v>-65.59441</v>
+        <v>-65.74996</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=746</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=678</t>
         </is>
       </c>
     </row>
@@ -2786,11 +2786,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Halls Hill</t>
+          <t>Gowland Mountain *</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1324</v>
+        <v>643</v>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cu, Zn</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2843,14 +2843,14 @@
         <v>43</v>
       </c>
       <c r="V32" t="n">
-        <v>45.96809</v>
+        <v>45.81975</v>
       </c>
       <c r="W32" t="n">
-        <v>-64.16996</v>
+        <v>-65.0483</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1324</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=643</t>
         </is>
       </c>
     </row>
@@ -2860,11 +2860,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Jacquet River M</t>
+          <t>Deed Brook</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>955</v>
+        <v>717</v>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ba, Cu</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2908,23 +2908,23 @@
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T33" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U33" t="n">
         <v>43</v>
       </c>
       <c r="V33" t="n">
-        <v>47.82559</v>
+        <v>45.78808</v>
       </c>
       <c r="W33" t="n">
-        <v>-66.01662</v>
+        <v>-64.85692</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=955</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=717</t>
         </is>
       </c>
     </row>
@@ -2934,11 +2934,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Letang Harbour North</t>
+          <t>Irving</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1291</v>
+        <v>1238</v>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Co, Cu, Ni</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2982,23 +2982,23 @@
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T34" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U34" t="n">
         <v>43</v>
       </c>
       <c r="V34" t="n">
-        <v>45.08726</v>
+        <v>45.19116</v>
       </c>
       <c r="W34" t="n">
-        <v>-66.7833</v>
+        <v>-67.25942000000001</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1291</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1238</t>
         </is>
       </c>
     </row>
@@ -3008,11 +3008,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Dennis Stream - Upper &amp;quot;I&amp;quot;</t>
+          <t>St Stephen Ni - O Zone &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1306</v>
+        <v>1236</v>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
@@ -3021,7 +3021,11 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Co, Cu, Ni</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -3052,23 +3056,23 @@
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T35" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="U35" t="n">
         <v>43</v>
       </c>
       <c r="V35" t="n">
-        <v>45.22199</v>
+        <v>45.23088</v>
       </c>
       <c r="W35" t="n">
-        <v>-67.27109</v>
+        <v>-67.27692</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1306</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1236</t>
         </is>
       </c>
     </row>
@@ -3078,11 +3082,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Gowland Mountain *</t>
+          <t>Memramcook Gold &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>643</v>
+        <v>723</v>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
@@ -3093,7 +3097,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3126,23 +3130,23 @@
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T36" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U36" t="n">
         <v>43</v>
       </c>
       <c r="V36" t="n">
-        <v>45.81975</v>
+        <v>45.96531</v>
       </c>
       <c r="W36" t="n">
-        <v>-65.0483</v>
+        <v>-64.53885</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=643</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=723</t>
         </is>
       </c>
     </row>
@@ -3152,11 +3156,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Quaco Road &amp;quot;I&amp;quot;</t>
+          <t>Halls Hill</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>678</v>
+        <v>1324</v>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
@@ -3167,7 +3171,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Cu, Zn</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3209,14 +3213,14 @@
         <v>43</v>
       </c>
       <c r="V37" t="n">
-        <v>45.38336</v>
+        <v>45.96809</v>
       </c>
       <c r="W37" t="n">
-        <v>-65.74996</v>
+        <v>-64.16996</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=678</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1324</t>
         </is>
       </c>
     </row>
@@ -3226,11 +3230,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>St Stephen Ni - O Zone &amp;quot;I&amp;quot;</t>
+          <t>Letang Harbour North</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1236</v>
+        <v>1291</v>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
@@ -3241,7 +3245,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Co, Cu, Ni</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3274,23 +3278,23 @@
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T38" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U38" t="n">
         <v>43</v>
       </c>
       <c r="V38" t="n">
-        <v>45.23088</v>
+        <v>45.08726</v>
       </c>
       <c r="W38" t="n">
-        <v>-67.27692</v>
+        <v>-66.7833</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1236</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1291</t>
         </is>
       </c>
     </row>
@@ -3300,11 +3304,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Irving</t>
+          <t>Dennis Stream - Upper &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1238</v>
+        <v>1306</v>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
@@ -3313,11 +3317,7 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Co, Cu, Ni</t>
-        </is>
-      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -3348,23 +3348,23 @@
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T39" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="U39" t="n">
         <v>43</v>
       </c>
       <c r="V39" t="n">
-        <v>45.19116</v>
+        <v>45.22199</v>
       </c>
       <c r="W39" t="n">
-        <v>-67.25942000000001</v>
+        <v>-67.27109</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1238</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1306</t>
         </is>
       </c>
     </row>
@@ -3374,11 +3374,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Pabineau River North Manganese</t>
+          <t>Jacquet River M</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1272</v>
+        <v>955</v>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
@@ -3389,7 +3389,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Ba, Cu</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3422,23 +3422,23 @@
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T40" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U40" t="n">
         <v>43</v>
       </c>
       <c r="V40" t="n">
-        <v>47.49558</v>
+        <v>47.82559</v>
       </c>
       <c r="W40" t="n">
-        <v>-65.90329</v>
+        <v>-66.01662</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1272</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=955</t>
         </is>
       </c>
     </row>
@@ -3448,11 +3448,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Bass River Cu-Ni</t>
+          <t>Eel Ground</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1254</v>
+        <v>746</v>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cu, Ni</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3505,14 +3505,14 @@
         <v>43</v>
       </c>
       <c r="V41" t="n">
-        <v>47.46421</v>
+        <v>46.96447</v>
       </c>
       <c r="W41" t="n">
-        <v>-65.56607</v>
+        <v>-65.59441</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1254</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=746</t>
         </is>
       </c>
     </row>
@@ -3522,11 +3522,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Memramcook Gold &amp;quot;I&amp;quot;</t>
+          <t>Three Bridge Brook East *</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>723</v>
+        <v>793</v>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
@@ -3537,7 +3537,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Ag, Au, Pb, Zn</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3570,23 +3570,23 @@
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T42" t="n">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="U42" t="n">
         <v>43</v>
       </c>
       <c r="V42" t="n">
-        <v>45.96531</v>
+        <v>45.49419</v>
       </c>
       <c r="W42" t="n">
-        <v>-64.53885</v>
+        <v>-66.48581</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=723</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=793</t>
         </is>
       </c>
     </row>
@@ -3596,11 +3596,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Deed Brook</t>
+          <t>Pabineau River North Manganese</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>717</v>
+        <v>1272</v>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3644,23 +3644,23 @@
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T43" t="n">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="U43" t="n">
         <v>43</v>
       </c>
       <c r="V43" t="n">
-        <v>45.78808</v>
+        <v>47.49558</v>
       </c>
       <c r="W43" t="n">
-        <v>-64.85692</v>
+        <v>-65.90329</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=717</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1272</t>
         </is>
       </c>
     </row>
@@ -3670,11 +3670,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Hayward Pinnacle</t>
+          <t>Bass River Cu-Ni</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1575</v>
+        <v>1254</v>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>Cu, Ni</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3727,14 +3727,14 @@
         <v>43</v>
       </c>
       <c r="V44" t="n">
-        <v>45.82761</v>
+        <v>47.46421</v>
       </c>
       <c r="W44" t="n">
-        <v>-64.9164</v>
+        <v>-65.56607</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1575</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1254</t>
         </is>
       </c>
     </row>
@@ -3744,11 +3744,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Tennants Cove *</t>
+          <t>McDougall Brook</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>372</v>
+        <v>520</v>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
@@ -3759,12 +3759,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I45" t="b">
@@ -3798,17 +3798,17 @@
         <v>325</v>
       </c>
       <c r="U45" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="V45" t="n">
-        <v>45.58694</v>
+        <v>45.53197</v>
       </c>
       <c r="W45" t="n">
-        <v>-66.01414</v>
+        <v>-66.71081</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=372</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=520</t>
         </is>
       </c>
     </row>
@@ -3818,11 +3818,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>McDougall Brook</t>
+          <t>Lower Birch Island</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>520</v>
+        <v>172</v>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
@@ -3833,7 +3833,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Ba, Fe, Mn</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3875,14 +3875,14 @@
         <v>38</v>
       </c>
       <c r="V46" t="n">
-        <v>45.53197</v>
+        <v>46.56864</v>
       </c>
       <c r="W46" t="n">
-        <v>-66.71081</v>
+        <v>-66.57080000000001</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=520</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=172</t>
         </is>
       </c>
     </row>
@@ -3892,11 +3892,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Brunswick No. 12</t>
+          <t>Nigadoo River Mine</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>54</v>
+        <v>128</v>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Ag, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>88.8 Mt</t>
+          <t>1.1 Mt</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -3949,14 +3949,14 @@
         <v>38</v>
       </c>
       <c r="V47" t="n">
-        <v>47.47889</v>
+        <v>47.73307</v>
       </c>
       <c r="W47" t="n">
-        <v>-65.89218</v>
+        <v>-65.80642</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=54</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=128</t>
         </is>
       </c>
     </row>
@@ -3966,11 +3966,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Anomaly 102 &amp;quot;I&amp;quot;</t>
+          <t>Austin Brook</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1151</v>
+        <v>69</v>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Ag, Fe, Pb, Zn</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>164 kt</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -4014,23 +4014,23 @@
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T48" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U48" t="n">
         <v>38</v>
       </c>
       <c r="V48" t="n">
-        <v>46.47865</v>
+        <v>47.39779</v>
       </c>
       <c r="W48" t="n">
-        <v>-66.72996999999999</v>
+        <v>-65.82302</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1151</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=69</t>
         </is>
       </c>
     </row>
@@ -4040,11 +4040,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nigadoo River Mine</t>
+          <t>Brunswick No. 12</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>128</v>
+        <v>54</v>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
@@ -4055,7 +4055,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ag, Cu, Pb, Zn</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>1.1 Mt</t>
+          <t>88.8 Mt</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -4097,14 +4097,14 @@
         <v>38</v>
       </c>
       <c r="V49" t="n">
-        <v>47.73307</v>
+        <v>47.47889</v>
       </c>
       <c r="W49" t="n">
-        <v>-65.80642</v>
+        <v>-65.89218</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=128</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=54</t>
         </is>
       </c>
     </row>
@@ -4114,11 +4114,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Lower Birch Island</t>
+          <t>Anomaly 102 &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>172</v>
+        <v>1151</v>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ba, Fe, Mn</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4171,14 +4171,14 @@
         <v>38</v>
       </c>
       <c r="V50" t="n">
-        <v>46.56864</v>
+        <v>46.47865</v>
       </c>
       <c r="W50" t="n">
-        <v>-66.57080000000001</v>
+        <v>-66.72996999999999</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=172</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1151</t>
         </is>
       </c>
     </row>
@@ -4188,11 +4188,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Austin Brook</t>
+          <t>Black Point</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>69</v>
+        <v>1333</v>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ag, Fe, Pb, Zn</t>
+          <t>Pb, Zn</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Developed Prospect</t>
         </is>
       </c>
       <c r="I51" t="b">
@@ -4219,15 +4219,11 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>164 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
+      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="n">
         <v>0</v>
@@ -4236,23 +4232,23 @@
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T51" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U51" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V51" t="n">
-        <v>47.39779</v>
+        <v>45.79448</v>
       </c>
       <c r="W51" t="n">
-        <v>-65.82302</v>
+        <v>-64.42218</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=69</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1333</t>
         </is>
       </c>
     </row>
@@ -4262,11 +4258,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Taylors Island</t>
+          <t>Jeanne Mance</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>32</v>
+        <v>1249</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
@@ -4277,7 +4273,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4315,14 +4311,14 @@
         <v>37</v>
       </c>
       <c r="V52" t="n">
-        <v>45.22336</v>
+        <v>47.36337</v>
       </c>
       <c r="W52" t="n">
-        <v>-66.12747</v>
+        <v>-65.44329999999999</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=32</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1249</t>
         </is>
       </c>
     </row>
@@ -4332,11 +4328,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Henry Lake</t>
+          <t>Little Nictor Lake</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1510</v>
+        <v>94</v>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
@@ -4347,7 +4343,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Zn</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4385,14 +4381,14 @@
         <v>37</v>
       </c>
       <c r="V53" t="n">
-        <v>45.39473</v>
+        <v>47.40642</v>
       </c>
       <c r="W53" t="n">
-        <v>-65.60417</v>
+        <v>-66.84441</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1510</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=94</t>
         </is>
       </c>
     </row>
@@ -4402,11 +4398,11 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Little Nictor Lake</t>
+          <t>Gaspereau River</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>94</v>
+        <v>1300</v>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
@@ -4417,7 +4413,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Zn</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4455,14 +4451,14 @@
         <v>37</v>
       </c>
       <c r="V54" t="n">
-        <v>47.40642</v>
+        <v>46.08059</v>
       </c>
       <c r="W54" t="n">
-        <v>-66.84441</v>
+        <v>-64.20996</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=94</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1300</t>
         </is>
       </c>
     </row>
@@ -4472,11 +4468,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Bulls Creek 2</t>
+          <t>Church Showing</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1072</v>
+        <v>726</v>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
@@ -4487,7 +4483,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ag, Au, Co, Cu</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4525,14 +4521,14 @@
         <v>37</v>
       </c>
       <c r="V55" t="n">
-        <v>46.08809</v>
+        <v>44.88974</v>
       </c>
       <c r="W55" t="n">
-        <v>-67.56498000000001</v>
+        <v>-66.95386000000001</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1072</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=726</t>
         </is>
       </c>
     </row>
@@ -4542,11 +4538,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Bulls Creek 1</t>
+          <t>Basaltic Island West *</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1071</v>
+        <v>1347</v>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
@@ -4557,7 +4553,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Pb, Zn</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4595,14 +4591,14 @@
         <v>37</v>
       </c>
       <c r="V56" t="n">
-        <v>46.08421</v>
+        <v>45.1392</v>
       </c>
       <c r="W56" t="n">
-        <v>-67.57774999999999</v>
+        <v>-66.92413999999999</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1071</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1347</t>
         </is>
       </c>
     </row>
@@ -4612,11 +4608,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Church Showing</t>
+          <t>Grande Anse</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>726</v>
+        <v>1370</v>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
@@ -4627,7 +4623,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4665,14 +4661,14 @@
         <v>37</v>
       </c>
       <c r="V57" t="n">
-        <v>44.88974</v>
+        <v>45.79615</v>
       </c>
       <c r="W57" t="n">
-        <v>-66.95386000000001</v>
+        <v>-64.50107</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=726</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1370</t>
         </is>
       </c>
     </row>
@@ -4682,11 +4678,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Jeanne Mance</t>
+          <t>Johnson Mills</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1249</v>
+        <v>1371</v>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
@@ -4735,14 +4731,14 @@
         <v>37</v>
       </c>
       <c r="V58" t="n">
-        <v>47.36337</v>
+        <v>45.76365</v>
       </c>
       <c r="W58" t="n">
-        <v>-65.44329999999999</v>
+        <v>-64.52218000000001</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1249</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1371</t>
         </is>
       </c>
     </row>
@@ -4752,11 +4748,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Black Point</t>
+          <t>Moores Mills #2</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1333</v>
+        <v>1374</v>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
@@ -4767,7 +4763,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pb, Zn</t>
+          <t>Ag, Cu, Pb</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4796,23 +4792,23 @@
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T59" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U59" t="n">
         <v>37</v>
       </c>
       <c r="V59" t="n">
-        <v>45.79448</v>
+        <v>45.29977</v>
       </c>
       <c r="W59" t="n">
-        <v>-64.42218</v>
+        <v>-67.2533</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1333</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1374</t>
         </is>
       </c>
     </row>
@@ -4822,11 +4818,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Quispamsis Exit</t>
+          <t>Scoudouc River Quarry</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1338</v>
+        <v>1367</v>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
@@ -4837,7 +4833,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ag, Au, Cu, Pb</t>
+          <t>Pb, Zn</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4875,14 +4871,14 @@
         <v>37</v>
       </c>
       <c r="V60" t="n">
-        <v>45.42378</v>
+        <v>46.19643</v>
       </c>
       <c r="W60" t="n">
-        <v>-65.92708</v>
+        <v>-64.54385000000001</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1338</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1367</t>
         </is>
       </c>
     </row>
@@ -4892,11 +4888,11 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Basaltic Island West *</t>
+          <t>Black Point North</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1347</v>
+        <v>1368</v>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
@@ -4907,7 +4903,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pb, Zn</t>
+          <t>Cu, Zn</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4945,14 +4941,14 @@
         <v>37</v>
       </c>
       <c r="V61" t="n">
-        <v>45.1392</v>
+        <v>45.80448</v>
       </c>
       <c r="W61" t="n">
-        <v>-66.92413999999999</v>
+        <v>-64.41634999999999</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1347</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1368</t>
         </is>
       </c>
     </row>
@@ -4962,11 +4958,11 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Frye Island North</t>
+          <t>Shediac River # 2</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1353</v>
+        <v>1365</v>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
@@ -4977,7 +4973,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ag, Cu, F, Pb, Sb, Zn</t>
+          <t>As</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5015,14 +5011,14 @@
         <v>37</v>
       </c>
       <c r="V62" t="n">
-        <v>45.04753</v>
+        <v>46.2417</v>
       </c>
       <c r="W62" t="n">
-        <v>-66.84469</v>
+        <v>-64.6858</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1353</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1365</t>
         </is>
       </c>
     </row>
@@ -5032,11 +5028,11 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Gaspereau River</t>
+          <t>Rockport Shore</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1300</v>
+        <v>1362</v>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
@@ -5047,7 +5043,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5085,14 +5081,14 @@
         <v>37</v>
       </c>
       <c r="V63" t="n">
-        <v>46.08059</v>
+        <v>45.72365</v>
       </c>
       <c r="W63" t="n">
-        <v>-64.20996</v>
+        <v>-64.50663</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1300</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1362</t>
         </is>
       </c>
     </row>
@@ -5102,11 +5098,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Cape Maringouin # 1</t>
+          <t>Cape Maringouin # 2</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
@@ -5117,7 +5113,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cu, Pb</t>
+          <t>Ag, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5155,14 +5151,14 @@
         <v>37</v>
       </c>
       <c r="V64" t="n">
-        <v>45.73532</v>
+        <v>45.73782</v>
       </c>
       <c r="W64" t="n">
-        <v>-64.54191</v>
+        <v>-64.53246</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1360</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1361</t>
         </is>
       </c>
     </row>
@@ -5172,11 +5168,11 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Cape Maringouin # 2</t>
+          <t>Cape Maringouin # 1</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
@@ -5187,7 +5183,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ag, Cu, Pb, Zn</t>
+          <t>Cu, Pb</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5225,14 +5221,14 @@
         <v>37</v>
       </c>
       <c r="V65" t="n">
-        <v>45.73782</v>
+        <v>45.73532</v>
       </c>
       <c r="W65" t="n">
-        <v>-64.53246</v>
+        <v>-64.54191</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1361</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1360</t>
         </is>
       </c>
     </row>
@@ -5242,11 +5238,11 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Digdeguash Cu *</t>
+          <t>Frye Island North</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1344</v>
+        <v>1353</v>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
@@ -5257,7 +5253,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cu, Zn</t>
+          <t>Ag, Cu, F, Pb, Sb, Zn</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5295,14 +5291,14 @@
         <v>37</v>
       </c>
       <c r="V66" t="n">
-        <v>45.18698</v>
+        <v>45.04753</v>
       </c>
       <c r="W66" t="n">
-        <v>-66.93774999999999</v>
+        <v>-66.84469</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1344</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1353</t>
         </is>
       </c>
     </row>
@@ -5312,11 +5308,11 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Rockport Shore</t>
+          <t>Quispamsis Exit</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1362</v>
+        <v>1338</v>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
@@ -5327,7 +5323,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Ag, Au, Cu, Pb</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5365,14 +5361,14 @@
         <v>37</v>
       </c>
       <c r="V67" t="n">
-        <v>45.72365</v>
+        <v>45.42378</v>
       </c>
       <c r="W67" t="n">
-        <v>-64.50663</v>
+        <v>-65.92708</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1362</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1338</t>
         </is>
       </c>
     </row>
@@ -5382,11 +5378,11 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Black Point North</t>
+          <t>Digdeguash Cu *</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1368</v>
+        <v>1344</v>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
@@ -5435,14 +5431,14 @@
         <v>37</v>
       </c>
       <c r="V68" t="n">
-        <v>45.80448</v>
+        <v>45.18698</v>
       </c>
       <c r="W68" t="n">
-        <v>-64.41634999999999</v>
+        <v>-66.93774999999999</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1368</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1344</t>
         </is>
       </c>
     </row>
@@ -5452,11 +5448,11 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Grande Anse</t>
+          <t>Sinclair Hill</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1370</v>
+        <v>9</v>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
@@ -5467,7 +5463,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Ag, Au, Cu</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5505,14 +5501,14 @@
         <v>37</v>
       </c>
       <c r="V69" t="n">
-        <v>45.79615</v>
+        <v>45.63113</v>
       </c>
       <c r="W69" t="n">
-        <v>-64.50107</v>
+        <v>-64.92274999999999</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1370</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=9</t>
         </is>
       </c>
     </row>
@@ -5522,11 +5518,11 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Sinclair Hill</t>
+          <t>Taylors Island</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
@@ -5537,7 +5533,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ag, Au, Cu</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5575,14 +5571,14 @@
         <v>37</v>
       </c>
       <c r="V70" t="n">
-        <v>45.63113</v>
+        <v>45.22336</v>
       </c>
       <c r="W70" t="n">
-        <v>-64.92274999999999</v>
+        <v>-66.12747</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=9</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=32</t>
         </is>
       </c>
     </row>
@@ -5592,11 +5588,11 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Scoudouc River Quarry</t>
+          <t>Henry Lake</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1367</v>
+        <v>1510</v>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
@@ -5607,7 +5603,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pb, Zn</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5645,14 +5641,14 @@
         <v>37</v>
       </c>
       <c r="V71" t="n">
-        <v>46.19643</v>
+        <v>45.39473</v>
       </c>
       <c r="W71" t="n">
-        <v>-64.54385000000001</v>
+        <v>-65.60417</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1367</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1510</t>
         </is>
       </c>
     </row>
@@ -5662,11 +5658,11 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Shediac River # 2</t>
+          <t>Little John Lake</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1365</v>
+        <v>1396</v>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
@@ -5677,7 +5673,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>As</t>
+          <t>Au, Cu, Pb</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5706,23 +5702,23 @@
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T72" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U72" t="n">
         <v>37</v>
       </c>
       <c r="V72" t="n">
-        <v>46.2417</v>
+        <v>45.34976</v>
       </c>
       <c r="W72" t="n">
-        <v>-64.6858</v>
+        <v>-66.31052</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1365</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1396</t>
         </is>
       </c>
     </row>
@@ -5732,11 +5728,11 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Johnson Mills</t>
+          <t>Four Mile Lake B</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1371</v>
+        <v>1175</v>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
@@ -5745,14 +5741,10 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Cu</t>
-        </is>
-      </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Developed Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I73" t="b">
@@ -5782,17 +5774,17 @@
         <v>325</v>
       </c>
       <c r="U73" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="V73" t="n">
-        <v>45.76365</v>
+        <v>46.63643</v>
       </c>
       <c r="W73" t="n">
-        <v>-64.52218000000001</v>
+        <v>-66.58274</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1371</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1175</t>
         </is>
       </c>
     </row>
@@ -5802,11 +5794,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Moores Mills #2</t>
+          <t>Caledonia Mountain</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1374</v>
+        <v>1609</v>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
@@ -5817,12 +5809,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ag, Cu, Pb</t>
+          <t>Ti, V</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Developed Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I74" t="b">
@@ -5846,23 +5838,23 @@
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T74" t="n">
-        <v>175</v>
+        <v>275</v>
       </c>
       <c r="U74" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="V74" t="n">
-        <v>45.29977</v>
+        <v>45.8698</v>
       </c>
       <c r="W74" t="n">
-        <v>-67.2533</v>
+        <v>-64.73159</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1374</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1609</t>
         </is>
       </c>
     </row>
@@ -5872,11 +5864,11 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Little John Lake</t>
+          <t>Jacquet River Cu - Mitchell Rd</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1396</v>
+        <v>461</v>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
@@ -5885,14 +5877,10 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Au, Cu, Pb</t>
-        </is>
-      </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Developed Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I75" t="b">
@@ -5916,23 +5904,23 @@
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T75" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U75" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="V75" t="n">
-        <v>45.34976</v>
+        <v>47.82725</v>
       </c>
       <c r="W75" t="n">
-        <v>-66.31052</v>
+        <v>-66.00606999999999</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1396</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=461</t>
         </is>
       </c>
     </row>
@@ -6012,11 +6000,11 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Brewers Mills</t>
+          <t>Dumfries *</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>904</v>
+        <v>535</v>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
@@ -6027,7 +6015,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>As, Au</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6065,14 +6053,14 @@
         <v>35</v>
       </c>
       <c r="V77" t="n">
-        <v>46.0692</v>
+        <v>45.95029</v>
       </c>
       <c r="W77" t="n">
-        <v>-67.0283</v>
+        <v>-67.12273999999999</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=904</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=535</t>
         </is>
       </c>
     </row>
@@ -6082,11 +6070,11 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Jacquet River K</t>
+          <t>Letete Mine</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>973</v>
+        <v>311</v>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
@@ -6095,10 +6083,14 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I78" t="b">
@@ -6109,11 +6101,15 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>1.9 Mt</t>
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="n">
         <v>0</v>
@@ -6122,23 +6118,23 @@
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T78" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U78" t="n">
         <v>35</v>
       </c>
       <c r="V78" t="n">
-        <v>47.83142</v>
+        <v>45.06529</v>
       </c>
       <c r="W78" t="n">
-        <v>-66.03246</v>
+        <v>-66.91136</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=973</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=311</t>
         </is>
       </c>
     </row>
@@ -6148,11 +6144,11 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Caledonia Mountain</t>
+          <t>Silver Island</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1609</v>
+        <v>586</v>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
@@ -6163,7 +6159,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ti, V</t>
+          <t>Ag, Pb, Zn</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6192,23 +6188,23 @@
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T79" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U79" t="n">
         <v>35</v>
       </c>
       <c r="V79" t="n">
-        <v>45.8698</v>
+        <v>45.12114</v>
       </c>
       <c r="W79" t="n">
-        <v>-64.73159</v>
+        <v>-66.8458</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1609</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=586</t>
         </is>
       </c>
     </row>
@@ -6218,11 +6214,11 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Centreville &amp;quot;I&amp;quot;</t>
+          <t>Forty Five River &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>263</v>
+        <v>647</v>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
@@ -6233,7 +6229,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -6262,23 +6258,23 @@
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T80" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U80" t="n">
         <v>35</v>
       </c>
       <c r="V80" t="n">
-        <v>46.44281</v>
+        <v>45.74309</v>
       </c>
       <c r="W80" t="n">
-        <v>-67.6808</v>
+        <v>-64.93053</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=263</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=647</t>
         </is>
       </c>
     </row>
@@ -6288,11 +6284,11 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Waterville Prospect &amp;quot;I&amp;quot;</t>
+          <t>Phyllis Creek &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1413</v>
+        <v>655</v>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
@@ -6303,7 +6299,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Au, Sb</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -6341,14 +6337,14 @@
         <v>35</v>
       </c>
       <c r="V81" t="n">
-        <v>46.05921</v>
+        <v>45.94808</v>
       </c>
       <c r="W81" t="n">
-        <v>-67.30663</v>
+        <v>-66.69441</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1413</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=655</t>
         </is>
       </c>
     </row>
@@ -6358,11 +6354,11 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Indian Brook</t>
+          <t>Pirate Lake</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>262</v>
+        <v>516</v>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
@@ -6371,7 +6367,11 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
       <c r="H82" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -6407,14 +6407,14 @@
         <v>35</v>
       </c>
       <c r="V82" t="n">
-        <v>46.73226</v>
+        <v>45.72697</v>
       </c>
       <c r="W82" t="n">
-        <v>-67.42440999999999</v>
+        <v>-67.67525000000001</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=262</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=516</t>
         </is>
       </c>
     </row>
@@ -6424,11 +6424,11 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Brummagen Brook Bog</t>
+          <t>Pecks Point South</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>188</v>
+        <v>1329</v>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
@@ -6439,7 +6439,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Ag, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -6477,14 +6477,14 @@
         <v>35</v>
       </c>
       <c r="V83" t="n">
-        <v>46.39003</v>
+        <v>45.73809</v>
       </c>
       <c r="W83" t="n">
-        <v>-67.29386</v>
+        <v>-64.48524</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=188</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1329</t>
         </is>
       </c>
     </row>
@@ -6494,11 +6494,11 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Pecks Point South</t>
+          <t>East Quoddy Head</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1329</v>
+        <v>737</v>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
@@ -6509,7 +6509,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ag, Cu, Pb, Zn</t>
+          <t>Pb</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -6547,14 +6547,14 @@
         <v>35</v>
       </c>
       <c r="V84" t="n">
-        <v>45.73809</v>
+        <v>44.95391</v>
       </c>
       <c r="W84" t="n">
-        <v>-64.48524</v>
+        <v>-66.90831</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1329</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=737</t>
         </is>
       </c>
     </row>
@@ -6564,11 +6564,11 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Dumfries *</t>
+          <t>Meadow Brook Cove</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>535</v>
+        <v>727</v>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>Fe, Zn</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -6617,14 +6617,14 @@
         <v>35</v>
       </c>
       <c r="V85" t="n">
-        <v>45.95029</v>
+        <v>44.88281</v>
       </c>
       <c r="W85" t="n">
-        <v>-67.12273999999999</v>
+        <v>-66.90774999999999</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=535</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=727</t>
         </is>
       </c>
     </row>
@@ -6634,11 +6634,11 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Pirate Lake</t>
+          <t>Jacquet River K</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>516</v>
+        <v>973</v>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
@@ -6647,11 +6647,7 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Cu</t>
-        </is>
-      </c>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -6687,14 +6683,14 @@
         <v>35</v>
       </c>
       <c r="V86" t="n">
-        <v>45.72697</v>
+        <v>47.83142</v>
       </c>
       <c r="W86" t="n">
-        <v>-67.67525000000001</v>
+        <v>-66.03246</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=516</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=973</t>
         </is>
       </c>
     </row>
@@ -6704,11 +6700,11 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Elmtree 7B</t>
+          <t>Little Southwest Miramichi</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>854</v>
+        <v>621</v>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
@@ -6717,11 +6713,7 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Cu, Ni</t>
-        </is>
-      </c>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -6748,23 +6740,23 @@
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr"/>
       <c r="S87" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T87" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U87" t="n">
         <v>35</v>
       </c>
       <c r="V87" t="n">
-        <v>47.78253</v>
+        <v>46.89643</v>
       </c>
       <c r="W87" t="n">
-        <v>-65.87246</v>
+        <v>-66.34998</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=854</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=621</t>
         </is>
       </c>
     </row>
@@ -6774,11 +6766,11 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Four Mile Lake B</t>
+          <t>Waterside Manganese</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1175</v>
+        <v>645</v>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
@@ -6787,7 +6779,11 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Mn</t>
+        </is>
+      </c>
       <c r="H88" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -6814,23 +6810,23 @@
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr"/>
       <c r="S88" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T88" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U88" t="n">
         <v>35</v>
       </c>
       <c r="V88" t="n">
-        <v>46.63643</v>
+        <v>45.63058</v>
       </c>
       <c r="W88" t="n">
-        <v>-66.58274</v>
+        <v>-64.82858</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1175</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=645</t>
         </is>
       </c>
     </row>
@@ -6840,11 +6836,11 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Meadow Brook Cove</t>
+          <t>Brewers Mills</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>727</v>
+        <v>904</v>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
@@ -6855,7 +6851,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Fe, Zn</t>
+          <t>As, Au</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6893,14 +6889,14 @@
         <v>35</v>
       </c>
       <c r="V89" t="n">
-        <v>44.88281</v>
+        <v>46.0692</v>
       </c>
       <c r="W89" t="n">
-        <v>-66.90774999999999</v>
+        <v>-67.0283</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=727</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=904</t>
         </is>
       </c>
     </row>
@@ -6910,11 +6906,11 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>East Quoddy Head</t>
+          <t>Elmtree 7B</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>737</v>
+        <v>854</v>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr"/>
@@ -6925,7 +6921,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Pb</t>
+          <t>Cu, Ni</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6954,23 +6950,23 @@
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr"/>
       <c r="S90" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T90" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U90" t="n">
         <v>35</v>
       </c>
       <c r="V90" t="n">
-        <v>44.95391</v>
+        <v>47.78253</v>
       </c>
       <c r="W90" t="n">
-        <v>-66.90831</v>
+        <v>-65.87246</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=737</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=854</t>
         </is>
       </c>
     </row>
@@ -6980,11 +6976,11 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Silver Island</t>
+          <t>MacIntosh Brook</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>586</v>
+        <v>192</v>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
@@ -6995,7 +6991,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ag, Pb, Zn</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -7024,23 +7020,23 @@
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr"/>
       <c r="S91" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T91" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U91" t="n">
         <v>35</v>
       </c>
       <c r="V91" t="n">
-        <v>45.12114</v>
+        <v>46.35335</v>
       </c>
       <c r="W91" t="n">
-        <v>-66.8458</v>
+        <v>-67.27636</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=586</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=192</t>
         </is>
       </c>
     </row>
@@ -7050,11 +7046,11 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Phyllis Creek &amp;quot;I&amp;quot;</t>
+          <t>Maple Ridge</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>655</v>
+        <v>152</v>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr"/>
@@ -7065,7 +7061,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Mo, W</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -7103,14 +7099,14 @@
         <v>35</v>
       </c>
       <c r="V92" t="n">
-        <v>45.94808</v>
+        <v>46.10003</v>
       </c>
       <c r="W92" t="n">
-        <v>-66.69441</v>
+        <v>-67.21413</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=655</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=152</t>
         </is>
       </c>
     </row>
@@ -7120,11 +7116,11 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Jacquet River Cu - Mitchell Rd</t>
+          <t>Indian Brook</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>461</v>
+        <v>262</v>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
@@ -7169,14 +7165,14 @@
         <v>35</v>
       </c>
       <c r="V93" t="n">
-        <v>47.82725</v>
+        <v>46.73226</v>
       </c>
       <c r="W93" t="n">
-        <v>-66.00606999999999</v>
+        <v>-67.42440999999999</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=461</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=262</t>
         </is>
       </c>
     </row>
@@ -7186,11 +7182,11 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Maple Ridge</t>
+          <t>Centreville &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>152</v>
+        <v>263</v>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
@@ -7201,7 +7197,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Mo, W</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -7239,14 +7235,14 @@
         <v>35</v>
       </c>
       <c r="V94" t="n">
-        <v>46.10003</v>
+        <v>46.44281</v>
       </c>
       <c r="W94" t="n">
-        <v>-67.21413</v>
+        <v>-67.6808</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=152</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=263</t>
         </is>
       </c>
     </row>
@@ -7256,11 +7252,11 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>MacIntosh Brook</t>
+          <t>Brummagen Brook Bog</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
@@ -7271,7 +7267,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -7300,23 +7296,23 @@
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="inlineStr"/>
       <c r="S95" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T95" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U95" t="n">
         <v>35</v>
       </c>
       <c r="V95" t="n">
-        <v>46.35335</v>
+        <v>46.39003</v>
       </c>
       <c r="W95" t="n">
-        <v>-67.27636</v>
+        <v>-67.29386</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=192</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=188</t>
         </is>
       </c>
     </row>
@@ -7326,11 +7322,11 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Letete Mine</t>
+          <t>Waterville Prospect &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>311</v>
+        <v>1413</v>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
@@ -7341,12 +7337,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Au, Sb</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I96" t="b">
@@ -7357,15 +7353,11 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>1.9 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
+      <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="n">
         <v>0</v>
@@ -7374,23 +7366,23 @@
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr"/>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T96" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U96" t="n">
         <v>35</v>
       </c>
       <c r="V96" t="n">
-        <v>45.06529</v>
+        <v>46.05921</v>
       </c>
       <c r="W96" t="n">
-        <v>-66.91136</v>
+        <v>-67.30663</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=311</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1413</t>
         </is>
       </c>
     </row>
@@ -7400,11 +7392,11 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Forty Five River &amp;quot;I&amp;quot;</t>
+          <t>Shepody Mountain Manganese</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>647</v>
+        <v>721</v>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
@@ -7415,12 +7407,12 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I97" t="b">
@@ -7444,23 +7436,23 @@
       <c r="Q97" t="inlineStr"/>
       <c r="R97" t="inlineStr"/>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T97" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="U97" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="V97" t="n">
-        <v>45.74309</v>
+        <v>45.80502</v>
       </c>
       <c r="W97" t="n">
-        <v>-64.93053</v>
+        <v>-64.65774</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=647</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=721</t>
         </is>
       </c>
     </row>
@@ -7470,11 +7462,11 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Waterside Manganese</t>
+          <t>Memramcook East</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>645</v>
+        <v>320</v>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
@@ -7485,12 +7477,12 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Ba</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I98" t="b">
@@ -7514,23 +7506,23 @@
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr"/>
       <c r="S98" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T98" t="n">
-        <v>225</v>
+        <v>275</v>
       </c>
       <c r="U98" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="V98" t="n">
-        <v>45.63058</v>
+        <v>46.01558</v>
       </c>
       <c r="W98" t="n">
-        <v>-64.82858</v>
+        <v>-64.52218999999999</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=645</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=320</t>
         </is>
       </c>
     </row>
@@ -7540,11 +7532,11 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Little Southwest Miramichi</t>
+          <t>South Hamilton Road</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>621</v>
+        <v>1412</v>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr"/>
@@ -7553,10 +7545,14 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Ag, Au, Cu, Pb, Zn</t>
+        </is>
+      </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I99" t="b">
@@ -7586,17 +7582,17 @@
         <v>325</v>
       </c>
       <c r="U99" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="V99" t="n">
-        <v>46.89643</v>
+        <v>45.56892</v>
       </c>
       <c r="W99" t="n">
-        <v>-66.34998</v>
+        <v>-66.16552</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=621</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1412</t>
         </is>
       </c>
     </row>
@@ -7606,11 +7602,11 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Shepody Mountain Manganese</t>
+          <t>Gaspereau Station</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>721</v>
+        <v>328</v>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr"/>
@@ -7621,7 +7617,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Mo, Pb, Zn</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -7650,23 +7646,23 @@
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr"/>
       <c r="S100" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T100" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U100" t="n">
         <v>30</v>
       </c>
       <c r="V100" t="n">
-        <v>45.80502</v>
+        <v>45.48947</v>
       </c>
       <c r="W100" t="n">
-        <v>-64.65774</v>
+        <v>-66.47469</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=721</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=328</t>
         </is>
       </c>
     </row>
@@ -7676,11 +7672,11 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>South Hamilton Road</t>
+          <t>Collins Lake</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1412</v>
+        <v>1299</v>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr"/>
@@ -7691,12 +7687,12 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ag, Au, Cu, Pb, Zn</t>
+          <t>Pb, Zn</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I101" t="b">
@@ -7707,11 +7703,15 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>1.9 Mt</t>
         </is>
       </c>
       <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
       <c r="N101" t="inlineStr"/>
       <c r="O101" t="n">
         <v>0</v>
@@ -7726,295 +7726,15 @@
         <v>325</v>
       </c>
       <c r="U101" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="V101" t="n">
-        <v>45.56892</v>
+        <v>46.10254</v>
       </c>
       <c r="W101" t="n">
-        <v>-66.16552</v>
+        <v>-64.11969000000001</v>
       </c>
       <c r="X101" t="inlineStr">
-        <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1412</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="n">
-        <v>101</v>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Memramcook East</t>
-        </is>
-      </c>
-      <c r="C102" t="n">
-        <v>320</v>
-      </c>
-      <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Other metallic</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>Ba</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Past Producer</t>
-        </is>
-      </c>
-      <c r="I102" t="b">
-        <v>1</v>
-      </c>
-      <c r="J102" t="b">
-        <v>0</v>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
-      <c r="O102" t="n">
-        <v>0</v>
-      </c>
-      <c r="P102" t="inlineStr"/>
-      <c r="Q102" t="inlineStr"/>
-      <c r="R102" t="inlineStr"/>
-      <c r="S102" t="n">
-        <v>11</v>
-      </c>
-      <c r="T102" t="n">
-        <v>275</v>
-      </c>
-      <c r="U102" t="n">
-        <v>30</v>
-      </c>
-      <c r="V102" t="n">
-        <v>46.01558</v>
-      </c>
-      <c r="W102" t="n">
-        <v>-64.52218999999999</v>
-      </c>
-      <c r="X102" t="inlineStr">
-        <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=320</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="n">
-        <v>102</v>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Meridian Brook Crossing</t>
-        </is>
-      </c>
-      <c r="C103" t="n">
-        <v>630</v>
-      </c>
-      <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>Other metallic</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Past Producer</t>
-        </is>
-      </c>
-      <c r="I103" t="b">
-        <v>1</v>
-      </c>
-      <c r="J103" t="b">
-        <v>0</v>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
-      <c r="O103" t="n">
-        <v>0</v>
-      </c>
-      <c r="P103" t="inlineStr"/>
-      <c r="Q103" t="inlineStr"/>
-      <c r="R103" t="inlineStr"/>
-      <c r="S103" t="n">
-        <v>4</v>
-      </c>
-      <c r="T103" t="n">
-        <v>100</v>
-      </c>
-      <c r="U103" t="n">
-        <v>30</v>
-      </c>
-      <c r="V103" t="n">
-        <v>47.26747</v>
-      </c>
-      <c r="W103" t="n">
-        <v>-66.68077</v>
-      </c>
-      <c r="X103" t="inlineStr">
-        <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=630</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="n">
-        <v>103</v>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Gaspereau Station</t>
-        </is>
-      </c>
-      <c r="C104" t="n">
-        <v>328</v>
-      </c>
-      <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>Other metallic</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>Mo, Pb, Zn</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Past Producer</t>
-        </is>
-      </c>
-      <c r="I104" t="b">
-        <v>1</v>
-      </c>
-      <c r="J104" t="b">
-        <v>0</v>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
-      <c r="O104" t="n">
-        <v>0</v>
-      </c>
-      <c r="P104" t="inlineStr"/>
-      <c r="Q104" t="inlineStr"/>
-      <c r="R104" t="inlineStr"/>
-      <c r="S104" t="n">
-        <v>13</v>
-      </c>
-      <c r="T104" t="n">
-        <v>325</v>
-      </c>
-      <c r="U104" t="n">
-        <v>30</v>
-      </c>
-      <c r="V104" t="n">
-        <v>45.48947</v>
-      </c>
-      <c r="W104" t="n">
-        <v>-66.47469</v>
-      </c>
-      <c r="X104" t="inlineStr">
-        <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=328</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="n">
-        <v>104</v>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Collins Lake</t>
-        </is>
-      </c>
-      <c r="C105" t="n">
-        <v>1299</v>
-      </c>
-      <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>Other metallic</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>Pb, Zn</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Occurrence</t>
-        </is>
-      </c>
-      <c r="I105" t="b">
-        <v>1</v>
-      </c>
-      <c r="J105" t="b">
-        <v>0</v>
-      </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>1.9 Mt</t>
-        </is>
-      </c>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr"/>
-      <c r="O105" t="n">
-        <v>0</v>
-      </c>
-      <c r="P105" t="inlineStr"/>
-      <c r="Q105" t="inlineStr"/>
-      <c r="R105" t="inlineStr"/>
-      <c r="S105" t="n">
-        <v>13</v>
-      </c>
-      <c r="T105" t="n">
-        <v>325</v>
-      </c>
-      <c r="U105" t="n">
-        <v>27</v>
-      </c>
-      <c r="V105" t="n">
-        <v>46.10254</v>
-      </c>
-      <c r="W105" t="n">
-        <v>-64.11969000000001</v>
-      </c>
-      <c r="X105" t="inlineStr">
         <is>
           <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1299</t>
         </is>

--- a/site/nb_leads.xlsx
+++ b/site/nb_leads.xlsx
@@ -570,11 +570,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Shin Creek</t>
+          <t>Sloop Cove</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
@@ -585,7 +585,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ag, Mo, W</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -627,14 +627,14 @@
         <v>45</v>
       </c>
       <c r="V2" t="n">
-        <v>45.55224</v>
+        <v>44.68722</v>
       </c>
       <c r="W2" t="n">
-        <v>-66.63357999999999</v>
+        <v>-66.87302</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=8</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=31</t>
         </is>
       </c>
     </row>
@@ -644,11 +644,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Evandale Stock *</t>
+          <t>Quispamsis</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -659,7 +659,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ag, Au, Cu</t>
+          <t>Ag, Au, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -701,14 +701,14 @@
         <v>45</v>
       </c>
       <c r="V3" t="n">
-        <v>45.58501</v>
+        <v>45.42362</v>
       </c>
       <c r="W3" t="n">
-        <v>-66.09690999999999</v>
+        <v>-65.95802</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=11</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=4</t>
         </is>
       </c>
     </row>
@@ -718,11 +718,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Quispamsis</t>
+          <t>Melanson Brook E</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>1026</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -733,7 +733,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ag, Au, Cu, Pb, Zn</t>
+          <t>Ag, Pb, Zn</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -775,14 +775,14 @@
         <v>45</v>
       </c>
       <c r="V4" t="n">
-        <v>45.42362</v>
+        <v>47.73447</v>
       </c>
       <c r="W4" t="n">
-        <v>-65.95802</v>
+        <v>-65.98719</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=4</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1026</t>
         </is>
       </c>
     </row>
@@ -792,11 +792,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pender Brook</t>
+          <t>Nigadoo 8</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>1028</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -807,7 +807,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sb</t>
+          <t>Ag, Au, Pb, Zn</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -840,23 +840,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T5" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U5" t="n">
         <v>45</v>
       </c>
       <c r="V5" t="n">
-        <v>45.57888</v>
+        <v>47.74616</v>
       </c>
       <c r="W5" t="n">
-        <v>-66.30664</v>
+        <v>-65.88711000000001</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=10</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1028</t>
         </is>
       </c>
     </row>
@@ -866,11 +866,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Taylor Village</t>
+          <t>Antinouri Lake West B</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>57</v>
+        <v>1021</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -881,7 +881,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ti</t>
+          <t>Pb, Zn</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -923,14 +923,14 @@
         <v>45</v>
       </c>
       <c r="V6" t="n">
-        <v>45.93834</v>
+        <v>47.78921</v>
       </c>
       <c r="W6" t="n">
-        <v>-64.55385</v>
+        <v>-65.99773</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=57</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1021</t>
         </is>
       </c>
     </row>
@@ -940,11 +940,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Quisibis Mountain</t>
+          <t>Payne Brook</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>58</v>
+        <v>1036</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -955,7 +955,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Ag, Pb, Zn</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -997,14 +997,14 @@
         <v>45</v>
       </c>
       <c r="V7" t="n">
-        <v>47.42337</v>
+        <v>47.74032</v>
       </c>
       <c r="W7" t="n">
-        <v>-67.96913000000001</v>
+        <v>-65.91246</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=58</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1036</t>
         </is>
       </c>
     </row>
@@ -1014,11 +1014,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Levesque Gulch</t>
+          <t>Belledune Pond</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1115</v>
+        <v>72</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Au, Cu, Sb</t>
+          <t>Ag, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1062,23 +1062,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T8" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U8" t="n">
         <v>45</v>
       </c>
       <c r="V8" t="n">
-        <v>47.6649</v>
+        <v>47.82638</v>
       </c>
       <c r="W8" t="n">
-        <v>-66.69267000000001</v>
+        <v>-65.97922</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1115</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=72</t>
         </is>
       </c>
     </row>
@@ -1088,11 +1088,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Antinouri Lake West A</t>
+          <t>St. Leonard Iron-Manganese</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ag, Cu, Pb, Zn</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1145,14 +1145,14 @@
         <v>45</v>
       </c>
       <c r="V9" t="n">
-        <v>47.78952</v>
+        <v>47.2053</v>
       </c>
       <c r="W9" t="n">
-        <v>-65.98515</v>
+        <v>-67.88663</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=85</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=101</t>
         </is>
       </c>
     </row>
@@ -1236,11 +1236,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>St. Leonard Iron-Manganese</t>
+          <t>Antinouri Lake West A</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Ag, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1293,14 +1293,14 @@
         <v>45</v>
       </c>
       <c r="V11" t="n">
-        <v>47.2053</v>
+        <v>47.78952</v>
       </c>
       <c r="W11" t="n">
-        <v>-67.88663</v>
+        <v>-65.98515</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=101</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=85</t>
         </is>
       </c>
     </row>
@@ -1310,11 +1310,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Belledune Pond</t>
+          <t>Levesque Gulch</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>72</v>
+        <v>1115</v>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ag, Cu, Pb, Zn</t>
+          <t>Au, Cu, Sb</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1358,23 +1358,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T12" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U12" t="n">
         <v>45</v>
       </c>
       <c r="V12" t="n">
-        <v>47.82638</v>
+        <v>47.6649</v>
       </c>
       <c r="W12" t="n">
-        <v>-65.97922</v>
+        <v>-66.69267000000001</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=72</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1115</t>
         </is>
       </c>
     </row>
@@ -1384,11 +1384,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Red Pine Brook</t>
+          <t>Gordon Meadow Brook East</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1408</v>
+        <v>1252</v>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Ag, Pb, Zn</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1441,14 +1441,14 @@
         <v>45</v>
       </c>
       <c r="V13" t="n">
-        <v>47.4492</v>
+        <v>47.39279</v>
       </c>
       <c r="W13" t="n">
-        <v>-65.62412999999999</v>
+        <v>-65.68568999999999</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1408</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1252</t>
         </is>
       </c>
     </row>
@@ -1458,11 +1458,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Little Sevogle River 1</t>
+          <t>Green Creek North</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>60</v>
+        <v>1334</v>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1515,14 +1515,14 @@
         <v>45</v>
       </c>
       <c r="V14" t="n">
-        <v>47.0005</v>
+        <v>45.79059</v>
       </c>
       <c r="W14" t="n">
-        <v>-65.98999999999999</v>
+        <v>-64.44385</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=60</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1334</t>
         </is>
       </c>
     </row>
@@ -1606,11 +1606,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Gordon Meadow Brook East</t>
+          <t>Shin Creek</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1252</v>
+        <v>8</v>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ag, Pb, Zn</t>
+          <t>Ag, Mo, W</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1663,14 +1663,14 @@
         <v>45</v>
       </c>
       <c r="V16" t="n">
-        <v>47.39279</v>
+        <v>45.55224</v>
       </c>
       <c r="W16" t="n">
-        <v>-65.68568999999999</v>
+        <v>-66.63357999999999</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1252</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=8</t>
         </is>
       </c>
     </row>
@@ -1680,11 +1680,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nigadoo 8</t>
+          <t>Quisibis Mountain</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1028</v>
+        <v>58</v>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ag, Au, Pb, Zn</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1728,23 +1728,23 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T17" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U17" t="n">
         <v>45</v>
       </c>
       <c r="V17" t="n">
-        <v>47.74616</v>
+        <v>47.42337</v>
       </c>
       <c r="W17" t="n">
-        <v>-65.88711000000001</v>
+        <v>-67.96913000000001</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1028</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=58</t>
         </is>
       </c>
     </row>
@@ -1754,11 +1754,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Melanson Brook E</t>
+          <t>Little Sevogle River 1</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1026</v>
+        <v>60</v>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ag, Pb, Zn</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1811,14 +1811,14 @@
         <v>45</v>
       </c>
       <c r="V18" t="n">
-        <v>47.73447</v>
+        <v>47.0005</v>
       </c>
       <c r="W18" t="n">
-        <v>-65.98719</v>
+        <v>-65.98999999999999</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1026</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=60</t>
         </is>
       </c>
     </row>
@@ -1828,11 +1828,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Antinouri Lake West B</t>
+          <t>Taylor Village</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1021</v>
+        <v>57</v>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pb, Zn</t>
+          <t>Ti</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1885,14 +1885,14 @@
         <v>45</v>
       </c>
       <c r="V19" t="n">
-        <v>47.78921</v>
+        <v>45.93834</v>
       </c>
       <c r="W19" t="n">
-        <v>-65.99773</v>
+        <v>-64.55385</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1021</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=57</t>
         </is>
       </c>
     </row>
@@ -1902,11 +1902,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sloop Cove</t>
+          <t>South Glassville</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>31</v>
+        <v>1504</v>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1959,14 +1959,14 @@
         <v>45</v>
       </c>
       <c r="V20" t="n">
-        <v>44.68722</v>
+        <v>46.48057</v>
       </c>
       <c r="W20" t="n">
-        <v>-66.87302</v>
+        <v>-67.42028000000001</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=31</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1504</t>
         </is>
       </c>
     </row>
@@ -1976,11 +1976,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>South Glassville</t>
+          <t>Red Pine Brook</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1504</v>
+        <v>1408</v>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2033,14 +2033,14 @@
         <v>45</v>
       </c>
       <c r="V21" t="n">
-        <v>46.48057</v>
+        <v>47.4492</v>
       </c>
       <c r="W21" t="n">
-        <v>-67.42028000000001</v>
+        <v>-65.62412999999999</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1504</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1408</t>
         </is>
       </c>
     </row>
@@ -2050,11 +2050,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Green Creek North</t>
+          <t>Pender Brook</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1334</v>
+        <v>10</v>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Sb</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2107,14 +2107,14 @@
         <v>45</v>
       </c>
       <c r="V22" t="n">
-        <v>45.79059</v>
+        <v>45.57888</v>
       </c>
       <c r="W22" t="n">
-        <v>-64.44385</v>
+        <v>-66.30664</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1334</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=10</t>
         </is>
       </c>
     </row>
@@ -2124,11 +2124,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Payne Brook</t>
+          <t>Evandale Stock *</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1036</v>
+        <v>11</v>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ag, Pb, Zn</t>
+          <t>Ag, Au, Cu</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2181,14 +2181,14 @@
         <v>45</v>
       </c>
       <c r="V23" t="n">
-        <v>47.74032</v>
+        <v>45.58501</v>
       </c>
       <c r="W23" t="n">
-        <v>-65.91246</v>
+        <v>-66.09690999999999</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1036</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=11</t>
         </is>
       </c>
     </row>
@@ -2198,11 +2198,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Hayward Pinnacle</t>
+          <t>Joliffs Brook</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1575</v>
+        <v>555</v>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>Zn</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2255,14 +2255,14 @@
         <v>43</v>
       </c>
       <c r="V24" t="n">
-        <v>45.82761</v>
+        <v>45.73919</v>
       </c>
       <c r="W24" t="n">
-        <v>-64.9164</v>
+        <v>-65.75996000000001</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1575</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=555</t>
         </is>
       </c>
     </row>
@@ -2272,11 +2272,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Crory Farm</t>
+          <t>Martins Bluff</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>605</v>
+        <v>562</v>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
@@ -2285,11 +2285,7 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Cu, Pb, Zn</t>
-        </is>
-      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -2329,14 +2325,14 @@
         <v>43</v>
       </c>
       <c r="V25" t="n">
-        <v>45.08058</v>
+        <v>46.93142</v>
       </c>
       <c r="W25" t="n">
-        <v>-66.80913</v>
+        <v>-66.64663</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=605</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=562</t>
         </is>
       </c>
     </row>
@@ -2346,11 +2342,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tennants Cove *</t>
+          <t>Ragged Falls &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>372</v>
+        <v>570</v>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
@@ -2361,7 +2357,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Th, U</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2394,23 +2390,23 @@
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T26" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U26" t="n">
         <v>43</v>
       </c>
       <c r="V26" t="n">
-        <v>45.58694</v>
+        <v>45.2353</v>
       </c>
       <c r="W26" t="n">
-        <v>-66.01414</v>
+        <v>-66.48052</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=372</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=570</t>
         </is>
       </c>
     </row>
@@ -2420,11 +2416,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ragged Falls &amp;quot;I&amp;quot;</t>
+          <t>Crory Farm</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>570</v>
+        <v>605</v>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
@@ -2435,7 +2431,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Th, U</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2468,23 +2464,23 @@
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T27" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U27" t="n">
         <v>43</v>
       </c>
       <c r="V27" t="n">
-        <v>45.2353</v>
+        <v>45.08058</v>
       </c>
       <c r="W27" t="n">
-        <v>-66.48052</v>
+        <v>-66.80913</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=570</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=605</t>
         </is>
       </c>
     </row>
@@ -2494,11 +2490,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Martins Bluff</t>
+          <t>Dickson Brook A,B,C</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>562</v>
+        <v>639</v>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
@@ -2507,7 +2503,11 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -2547,14 +2547,14 @@
         <v>43</v>
       </c>
       <c r="V28" t="n">
-        <v>46.93142</v>
+        <v>45.58364</v>
       </c>
       <c r="W28" t="n">
-        <v>-66.64663</v>
+        <v>-64.98524</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=562</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=639</t>
         </is>
       </c>
     </row>
@@ -2564,11 +2564,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Joliffs Brook</t>
+          <t>Three Bridge Brook East *</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>555</v>
+        <v>793</v>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Zn</t>
+          <t>Ag, Au, Pb, Zn</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2612,23 +2612,23 @@
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T29" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U29" t="n">
         <v>43</v>
       </c>
       <c r="V29" t="n">
-        <v>45.73919</v>
+        <v>45.49419</v>
       </c>
       <c r="W29" t="n">
-        <v>-65.75996000000001</v>
+        <v>-66.48581</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=555</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=793</t>
         </is>
       </c>
     </row>
@@ -2638,11 +2638,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Dickson Brook A,B,C</t>
+          <t>Eel Ground</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>639</v>
+        <v>746</v>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2695,14 +2695,14 @@
         <v>43</v>
       </c>
       <c r="V30" t="n">
-        <v>45.58364</v>
+        <v>46.96447</v>
       </c>
       <c r="W30" t="n">
-        <v>-64.98524</v>
+        <v>-65.59441</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=639</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=746</t>
         </is>
       </c>
     </row>
@@ -2712,11 +2712,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Quaco Road &amp;quot;I&amp;quot;</t>
+          <t>Halls Hill</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>678</v>
+        <v>1324</v>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Cu, Zn</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2769,14 +2769,14 @@
         <v>43</v>
       </c>
       <c r="V31" t="n">
-        <v>45.38336</v>
+        <v>45.96809</v>
       </c>
       <c r="W31" t="n">
-        <v>-65.74996</v>
+        <v>-64.16996</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=678</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1324</t>
         </is>
       </c>
     </row>
@@ -2786,11 +2786,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Gowland Mountain *</t>
+          <t>Jacquet River M</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>643</v>
+        <v>955</v>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Ba, Cu</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2843,14 +2843,14 @@
         <v>43</v>
       </c>
       <c r="V32" t="n">
-        <v>45.81975</v>
+        <v>47.82559</v>
       </c>
       <c r="W32" t="n">
-        <v>-65.0483</v>
+        <v>-66.01662</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=643</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=955</t>
         </is>
       </c>
     </row>
@@ -2860,11 +2860,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Deed Brook</t>
+          <t>Letang Harbour North</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>717</v>
+        <v>1291</v>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2908,23 +2908,23 @@
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T33" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U33" t="n">
         <v>43</v>
       </c>
       <c r="V33" t="n">
-        <v>45.78808</v>
+        <v>45.08726</v>
       </c>
       <c r="W33" t="n">
-        <v>-64.85692</v>
+        <v>-66.7833</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=717</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1291</t>
         </is>
       </c>
     </row>
@@ -2934,11 +2934,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Irving</t>
+          <t>Dennis Stream - Upper &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1238</v>
+        <v>1306</v>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
@@ -2947,11 +2947,7 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Co, Cu, Ni</t>
-        </is>
-      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -2982,23 +2978,23 @@
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T34" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="U34" t="n">
         <v>43</v>
       </c>
       <c r="V34" t="n">
-        <v>45.19116</v>
+        <v>45.22199</v>
       </c>
       <c r="W34" t="n">
-        <v>-67.25942000000001</v>
+        <v>-67.27109</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1238</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1306</t>
         </is>
       </c>
     </row>
@@ -3008,11 +3004,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>St Stephen Ni - O Zone &amp;quot;I&amp;quot;</t>
+          <t>Gowland Mountain *</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1236</v>
+        <v>643</v>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
@@ -3023,7 +3019,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Co, Cu, Ni</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3056,23 +3052,23 @@
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T35" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U35" t="n">
         <v>43</v>
       </c>
       <c r="V35" t="n">
-        <v>45.23088</v>
+        <v>45.81975</v>
       </c>
       <c r="W35" t="n">
-        <v>-67.27692</v>
+        <v>-65.0483</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1236</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=643</t>
         </is>
       </c>
     </row>
@@ -3082,11 +3078,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Memramcook Gold &amp;quot;I&amp;quot;</t>
+          <t>Quaco Road &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>723</v>
+        <v>678</v>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
@@ -3097,7 +3093,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3130,23 +3126,23 @@
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T36" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U36" t="n">
         <v>43</v>
       </c>
       <c r="V36" t="n">
-        <v>45.96531</v>
+        <v>45.38336</v>
       </c>
       <c r="W36" t="n">
-        <v>-64.53885</v>
+        <v>-65.74996</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=723</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=678</t>
         </is>
       </c>
     </row>
@@ -3156,11 +3152,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Halls Hill</t>
+          <t>St Stephen Ni - O Zone &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1324</v>
+        <v>1236</v>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
@@ -3171,7 +3167,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cu, Zn</t>
+          <t>Co, Cu, Ni</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3204,23 +3200,23 @@
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T37" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U37" t="n">
         <v>43</v>
       </c>
       <c r="V37" t="n">
-        <v>45.96809</v>
+        <v>45.23088</v>
       </c>
       <c r="W37" t="n">
-        <v>-64.16996</v>
+        <v>-67.27692</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1324</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1236</t>
         </is>
       </c>
     </row>
@@ -3230,11 +3226,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Letang Harbour North</t>
+          <t>Irving</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1291</v>
+        <v>1238</v>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
@@ -3245,7 +3241,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Co, Cu, Ni</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3278,23 +3274,23 @@
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T38" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U38" t="n">
         <v>43</v>
       </c>
       <c r="V38" t="n">
-        <v>45.08726</v>
+        <v>45.19116</v>
       </c>
       <c r="W38" t="n">
-        <v>-66.7833</v>
+        <v>-67.25942000000001</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1291</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1238</t>
         </is>
       </c>
     </row>
@@ -3304,11 +3300,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Dennis Stream - Upper &amp;quot;I&amp;quot;</t>
+          <t>Pabineau River North Manganese</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1306</v>
+        <v>1272</v>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
@@ -3317,7 +3313,11 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Mn</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -3348,23 +3348,23 @@
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T39" t="n">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="U39" t="n">
         <v>43</v>
       </c>
       <c r="V39" t="n">
-        <v>45.22199</v>
+        <v>47.49558</v>
       </c>
       <c r="W39" t="n">
-        <v>-67.27109</v>
+        <v>-65.90329</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1306</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1272</t>
         </is>
       </c>
     </row>
@@ -3374,11 +3374,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Jacquet River M</t>
+          <t>Bass River Cu-Ni</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>955</v>
+        <v>1254</v>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
@@ -3389,7 +3389,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ba, Cu</t>
+          <t>Cu, Ni</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3431,14 +3431,14 @@
         <v>43</v>
       </c>
       <c r="V40" t="n">
-        <v>47.82559</v>
+        <v>47.46421</v>
       </c>
       <c r="W40" t="n">
-        <v>-66.01662</v>
+        <v>-65.56607</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=955</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1254</t>
         </is>
       </c>
     </row>
@@ -3448,11 +3448,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Eel Ground</t>
+          <t>Memramcook Gold &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>746</v>
+        <v>723</v>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3496,23 +3496,23 @@
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T41" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U41" t="n">
         <v>43</v>
       </c>
       <c r="V41" t="n">
-        <v>46.96447</v>
+        <v>45.96531</v>
       </c>
       <c r="W41" t="n">
-        <v>-65.59441</v>
+        <v>-64.53885</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=746</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=723</t>
         </is>
       </c>
     </row>
@@ -3522,11 +3522,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Three Bridge Brook East *</t>
+          <t>Deed Brook</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>793</v>
+        <v>717</v>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
@@ -3537,7 +3537,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ag, Au, Pb, Zn</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3570,23 +3570,23 @@
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T42" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="U42" t="n">
         <v>43</v>
       </c>
       <c r="V42" t="n">
-        <v>45.49419</v>
+        <v>45.78808</v>
       </c>
       <c r="W42" t="n">
-        <v>-66.48581</v>
+        <v>-64.85692</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=793</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=717</t>
         </is>
       </c>
     </row>
@@ -3596,11 +3596,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Pabineau River North Manganese</t>
+          <t>Hayward Pinnacle</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1272</v>
+        <v>1575</v>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>U</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3644,23 +3644,23 @@
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T43" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U43" t="n">
         <v>43</v>
       </c>
       <c r="V43" t="n">
-        <v>47.49558</v>
+        <v>45.82761</v>
       </c>
       <c r="W43" t="n">
-        <v>-65.90329</v>
+        <v>-64.9164</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1272</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1575</t>
         </is>
       </c>
     </row>
@@ -3670,11 +3670,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Bass River Cu-Ni</t>
+          <t>Tennants Cove *</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1254</v>
+        <v>372</v>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cu, Ni</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3727,14 +3727,14 @@
         <v>43</v>
       </c>
       <c r="V44" t="n">
-        <v>47.46421</v>
+        <v>45.58694</v>
       </c>
       <c r="W44" t="n">
-        <v>-65.56607</v>
+        <v>-66.01414</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1254</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=372</t>
         </is>
       </c>
     </row>
@@ -3818,11 +3818,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Lower Birch Island</t>
+          <t>Brunswick No. 12</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>172</v>
+        <v>54</v>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
@@ -3833,7 +3833,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ba, Fe, Mn</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>88.8 Mt</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
@@ -3875,14 +3875,14 @@
         <v>38</v>
       </c>
       <c r="V46" t="n">
-        <v>46.56864</v>
+        <v>47.47889</v>
       </c>
       <c r="W46" t="n">
-        <v>-66.57080000000001</v>
+        <v>-65.89218</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=172</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=54</t>
         </is>
       </c>
     </row>
@@ -3892,11 +3892,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nigadoo River Mine</t>
+          <t>Anomaly 102 &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>128</v>
+        <v>1151</v>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ag, Cu, Pb, Zn</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>1.1 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -3949,14 +3949,14 @@
         <v>38</v>
       </c>
       <c r="V47" t="n">
-        <v>47.73307</v>
+        <v>46.47865</v>
       </c>
       <c r="W47" t="n">
-        <v>-65.80642</v>
+        <v>-66.72996999999999</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=128</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1151</t>
         </is>
       </c>
     </row>
@@ -3966,11 +3966,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Austin Brook</t>
+          <t>Nigadoo River Mine</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>69</v>
+        <v>128</v>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ag, Fe, Pb, Zn</t>
+          <t>Ag, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>164 kt</t>
+          <t>1.1 Mt</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -4014,23 +4014,23 @@
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T48" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U48" t="n">
         <v>38</v>
       </c>
       <c r="V48" t="n">
-        <v>47.39779</v>
+        <v>47.73307</v>
       </c>
       <c r="W48" t="n">
-        <v>-65.82302</v>
+        <v>-65.80642</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=69</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=128</t>
         </is>
       </c>
     </row>
@@ -4040,11 +4040,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Brunswick No. 12</t>
+          <t>Lower Birch Island</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>54</v>
+        <v>172</v>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
@@ -4055,7 +4055,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Ba, Fe, Mn</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>88.8 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -4097,14 +4097,14 @@
         <v>38</v>
       </c>
       <c r="V49" t="n">
-        <v>47.47889</v>
+        <v>46.56864</v>
       </c>
       <c r="W49" t="n">
-        <v>-65.89218</v>
+        <v>-66.57080000000001</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=54</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=172</t>
         </is>
       </c>
     </row>
@@ -4114,11 +4114,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Anomaly 102 &amp;quot;I&amp;quot;</t>
+          <t>Austin Brook</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1151</v>
+        <v>69</v>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Ag, Fe, Pb, Zn</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>164 kt</t>
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
@@ -4162,23 +4162,23 @@
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T50" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U50" t="n">
         <v>38</v>
       </c>
       <c r="V50" t="n">
-        <v>46.47865</v>
+        <v>47.39779</v>
       </c>
       <c r="W50" t="n">
-        <v>-66.72996999999999</v>
+        <v>-65.82302</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1151</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=69</t>
         </is>
       </c>
     </row>
@@ -4188,11 +4188,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Black Point</t>
+          <t>Taylors Island</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1333</v>
+        <v>32</v>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pb, Zn</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4241,14 +4241,14 @@
         <v>37</v>
       </c>
       <c r="V51" t="n">
-        <v>45.79448</v>
+        <v>45.22336</v>
       </c>
       <c r="W51" t="n">
-        <v>-64.42218</v>
+        <v>-66.12747</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1333</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=32</t>
         </is>
       </c>
     </row>
@@ -4258,11 +4258,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Jeanne Mance</t>
+          <t>Henry Lake</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1249</v>
+        <v>1510</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
@@ -4311,14 +4311,14 @@
         <v>37</v>
       </c>
       <c r="V52" t="n">
-        <v>47.36337</v>
+        <v>45.39473</v>
       </c>
       <c r="W52" t="n">
-        <v>-65.44329999999999</v>
+        <v>-65.60417</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1249</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1510</t>
         </is>
       </c>
     </row>
@@ -4398,11 +4398,11 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Gaspereau River</t>
+          <t>Church Showing</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1300</v>
+        <v>726</v>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
@@ -4451,14 +4451,14 @@
         <v>37</v>
       </c>
       <c r="V54" t="n">
-        <v>46.08059</v>
+        <v>44.88974</v>
       </c>
       <c r="W54" t="n">
-        <v>-64.20996</v>
+        <v>-66.95386000000001</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1300</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=726</t>
         </is>
       </c>
     </row>
@@ -4468,11 +4468,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Church Showing</t>
+          <t>Jeanne Mance</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>726</v>
+        <v>1249</v>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
@@ -4521,14 +4521,14 @@
         <v>37</v>
       </c>
       <c r="V55" t="n">
-        <v>44.88974</v>
+        <v>47.36337</v>
       </c>
       <c r="W55" t="n">
-        <v>-66.95386000000001</v>
+        <v>-65.44329999999999</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=726</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1249</t>
         </is>
       </c>
     </row>
@@ -4538,11 +4538,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Basaltic Island West *</t>
+          <t>Black Point</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1347</v>
+        <v>1333</v>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
@@ -4591,14 +4591,14 @@
         <v>37</v>
       </c>
       <c r="V56" t="n">
-        <v>45.1392</v>
+        <v>45.79448</v>
       </c>
       <c r="W56" t="n">
-        <v>-66.92413999999999</v>
+        <v>-64.42218</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1347</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1333</t>
         </is>
       </c>
     </row>
@@ -4608,11 +4608,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Grande Anse</t>
+          <t>Quispamsis Exit</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1370</v>
+        <v>1338</v>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
@@ -4623,7 +4623,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Ag, Au, Cu, Pb</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4661,14 +4661,14 @@
         <v>37</v>
       </c>
       <c r="V57" t="n">
-        <v>45.79615</v>
+        <v>45.42378</v>
       </c>
       <c r="W57" t="n">
-        <v>-64.50107</v>
+        <v>-65.92708</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1370</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1338</t>
         </is>
       </c>
     </row>
@@ -4678,11 +4678,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Johnson Mills</t>
+          <t>Basaltic Island West *</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1371</v>
+        <v>1347</v>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Pb, Zn</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4731,14 +4731,14 @@
         <v>37</v>
       </c>
       <c r="V58" t="n">
-        <v>45.76365</v>
+        <v>45.1392</v>
       </c>
       <c r="W58" t="n">
-        <v>-64.52218000000001</v>
+        <v>-66.92413999999999</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1371</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1347</t>
         </is>
       </c>
     </row>
@@ -4748,11 +4748,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Moores Mills #2</t>
+          <t>Frye Island North</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1374</v>
+        <v>1353</v>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
@@ -4763,7 +4763,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ag, Cu, Pb</t>
+          <t>Ag, Cu, F, Pb, Sb, Zn</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4792,23 +4792,23 @@
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T59" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U59" t="n">
         <v>37</v>
       </c>
       <c r="V59" t="n">
-        <v>45.29977</v>
+        <v>45.04753</v>
       </c>
       <c r="W59" t="n">
-        <v>-67.2533</v>
+        <v>-66.84469</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1374</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1353</t>
         </is>
       </c>
     </row>
@@ -4818,11 +4818,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Scoudouc River Quarry</t>
+          <t>Gaspereau River</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1367</v>
+        <v>1300</v>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
@@ -4833,7 +4833,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pb, Zn</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4871,14 +4871,14 @@
         <v>37</v>
       </c>
       <c r="V60" t="n">
-        <v>46.19643</v>
+        <v>46.08059</v>
       </c>
       <c r="W60" t="n">
-        <v>-64.54385000000001</v>
+        <v>-64.20996</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1367</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1300</t>
         </is>
       </c>
     </row>
@@ -4888,11 +4888,11 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Black Point North</t>
+          <t>Cape Maringouin # 1</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1368</v>
+        <v>1360</v>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cu, Zn</t>
+          <t>Cu, Pb</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4941,14 +4941,14 @@
         <v>37</v>
       </c>
       <c r="V61" t="n">
-        <v>45.80448</v>
+        <v>45.73532</v>
       </c>
       <c r="W61" t="n">
-        <v>-64.41634999999999</v>
+        <v>-64.54191</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1368</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1360</t>
         </is>
       </c>
     </row>
@@ -4958,11 +4958,11 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Shediac River # 2</t>
+          <t>Cape Maringouin # 2</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
@@ -4973,7 +4973,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>As</t>
+          <t>Ag, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5011,14 +5011,14 @@
         <v>37</v>
       </c>
       <c r="V62" t="n">
-        <v>46.2417</v>
+        <v>45.73782</v>
       </c>
       <c r="W62" t="n">
-        <v>-64.6858</v>
+        <v>-64.53246</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1365</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1361</t>
         </is>
       </c>
     </row>
@@ -5028,11 +5028,11 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Rockport Shore</t>
+          <t>Digdeguash Cu *</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1362</v>
+        <v>1344</v>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
@@ -5043,7 +5043,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Cu, Zn</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5081,14 +5081,14 @@
         <v>37</v>
       </c>
       <c r="V63" t="n">
-        <v>45.72365</v>
+        <v>45.18698</v>
       </c>
       <c r="W63" t="n">
-        <v>-64.50663</v>
+        <v>-66.93774999999999</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1362</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1344</t>
         </is>
       </c>
     </row>
@@ -5098,11 +5098,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Cape Maringouin # 2</t>
+          <t>Rockport Shore</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
@@ -5113,7 +5113,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ag, Cu, Pb, Zn</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5151,14 +5151,14 @@
         <v>37</v>
       </c>
       <c r="V64" t="n">
-        <v>45.73782</v>
+        <v>45.72365</v>
       </c>
       <c r="W64" t="n">
-        <v>-64.53246</v>
+        <v>-64.50663</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1361</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1362</t>
         </is>
       </c>
     </row>
@@ -5168,11 +5168,11 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Cape Maringouin # 1</t>
+          <t>Black Point North</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1360</v>
+        <v>1368</v>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cu, Pb</t>
+          <t>Cu, Zn</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5221,14 +5221,14 @@
         <v>37</v>
       </c>
       <c r="V65" t="n">
-        <v>45.73532</v>
+        <v>45.80448</v>
       </c>
       <c r="W65" t="n">
-        <v>-64.54191</v>
+        <v>-64.41634999999999</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1360</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1368</t>
         </is>
       </c>
     </row>
@@ -5238,11 +5238,11 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Frye Island North</t>
+          <t>Grande Anse</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1353</v>
+        <v>1370</v>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ag, Cu, F, Pb, Sb, Zn</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5291,14 +5291,14 @@
         <v>37</v>
       </c>
       <c r="V66" t="n">
-        <v>45.04753</v>
+        <v>45.79615</v>
       </c>
       <c r="W66" t="n">
-        <v>-66.84469</v>
+        <v>-64.50107</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1353</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1370</t>
         </is>
       </c>
     </row>
@@ -5308,11 +5308,11 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Quispamsis Exit</t>
+          <t>Sinclair Hill</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1338</v>
+        <v>9</v>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
@@ -5323,7 +5323,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ag, Au, Cu, Pb</t>
+          <t>Ag, Au, Cu</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5361,14 +5361,14 @@
         <v>37</v>
       </c>
       <c r="V67" t="n">
-        <v>45.42378</v>
+        <v>45.63113</v>
       </c>
       <c r="W67" t="n">
-        <v>-65.92708</v>
+        <v>-64.92274999999999</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1338</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=9</t>
         </is>
       </c>
     </row>
@@ -5378,11 +5378,11 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Digdeguash Cu *</t>
+          <t>Scoudouc River Quarry</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1344</v>
+        <v>1367</v>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
@@ -5393,7 +5393,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cu, Zn</t>
+          <t>Pb, Zn</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5431,14 +5431,14 @@
         <v>37</v>
       </c>
       <c r="V68" t="n">
-        <v>45.18698</v>
+        <v>46.19643</v>
       </c>
       <c r="W68" t="n">
-        <v>-66.93774999999999</v>
+        <v>-64.54385000000001</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1344</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1367</t>
         </is>
       </c>
     </row>
@@ -5448,11 +5448,11 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Sinclair Hill</t>
+          <t>Shediac River # 2</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>9</v>
+        <v>1365</v>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
@@ -5463,7 +5463,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ag, Au, Cu</t>
+          <t>As</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5501,14 +5501,14 @@
         <v>37</v>
       </c>
       <c r="V69" t="n">
-        <v>45.63113</v>
+        <v>46.2417</v>
       </c>
       <c r="W69" t="n">
-        <v>-64.92274999999999</v>
+        <v>-64.6858</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=9</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1365</t>
         </is>
       </c>
     </row>
@@ -5518,11 +5518,11 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Taylors Island</t>
+          <t>Johnson Mills</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>32</v>
+        <v>1371</v>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
@@ -5533,7 +5533,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5571,14 +5571,14 @@
         <v>37</v>
       </c>
       <c r="V70" t="n">
-        <v>45.22336</v>
+        <v>45.76365</v>
       </c>
       <c r="W70" t="n">
-        <v>-66.12747</v>
+        <v>-64.52218000000001</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=32</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1371</t>
         </is>
       </c>
     </row>
@@ -5588,11 +5588,11 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Henry Lake</t>
+          <t>Moores Mills #2</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1510</v>
+        <v>1374</v>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
@@ -5603,7 +5603,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Ag, Cu, Pb</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5632,23 +5632,23 @@
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T71" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U71" t="n">
         <v>37</v>
       </c>
       <c r="V71" t="n">
-        <v>45.39473</v>
+        <v>45.29977</v>
       </c>
       <c r="W71" t="n">
-        <v>-65.60417</v>
+        <v>-67.2533</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1510</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1374</t>
         </is>
       </c>
     </row>
@@ -5728,11 +5728,11 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Four Mile Lake B</t>
+          <t>Jacquet River Cu - A</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1175</v>
+        <v>462</v>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
@@ -5741,7 +5741,11 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
       <c r="H73" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -5777,14 +5781,14 @@
         <v>35</v>
       </c>
       <c r="V73" t="n">
-        <v>46.63643</v>
+        <v>47.85476</v>
       </c>
       <c r="W73" t="n">
-        <v>-66.58274</v>
+        <v>-66.01551000000001</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1175</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=462</t>
         </is>
       </c>
     </row>
@@ -5794,11 +5798,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Caledonia Mountain</t>
+          <t>Brewers Mills</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1609</v>
+        <v>904</v>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
@@ -5809,7 +5813,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ti, V</t>
+          <t>As, Au</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5838,23 +5842,23 @@
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T74" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U74" t="n">
         <v>35</v>
       </c>
       <c r="V74" t="n">
-        <v>45.8698</v>
+        <v>46.0692</v>
       </c>
       <c r="W74" t="n">
-        <v>-64.73159</v>
+        <v>-67.0283</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1609</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=904</t>
         </is>
       </c>
     </row>
@@ -5864,11 +5868,11 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Jacquet River Cu - Mitchell Rd</t>
+          <t>Jacquet River K</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>461</v>
+        <v>973</v>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
@@ -5913,14 +5917,14 @@
         <v>35</v>
       </c>
       <c r="V75" t="n">
-        <v>47.82725</v>
+        <v>47.83142</v>
       </c>
       <c r="W75" t="n">
-        <v>-66.00606999999999</v>
+        <v>-66.03246</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=461</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=973</t>
         </is>
       </c>
     </row>
@@ -5930,11 +5934,11 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Jacquet River Cu - A</t>
+          <t>Caledonia Mountain</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>462</v>
+        <v>1609</v>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr"/>
@@ -5945,7 +5949,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Ti, V</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5974,23 +5978,23 @@
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T76" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U76" t="n">
         <v>35</v>
       </c>
       <c r="V76" t="n">
-        <v>47.85476</v>
+        <v>45.8698</v>
       </c>
       <c r="W76" t="n">
-        <v>-66.01551000000001</v>
+        <v>-64.73159</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=462</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1609</t>
         </is>
       </c>
     </row>
@@ -6000,11 +6004,11 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Dumfries *</t>
+          <t>Centreville &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>535</v>
+        <v>263</v>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
@@ -6015,7 +6019,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6053,14 +6057,14 @@
         <v>35</v>
       </c>
       <c r="V77" t="n">
-        <v>45.95029</v>
+        <v>46.44281</v>
       </c>
       <c r="W77" t="n">
-        <v>-67.12273999999999</v>
+        <v>-67.6808</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=535</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=263</t>
         </is>
       </c>
     </row>
@@ -6070,11 +6074,11 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Letete Mine</t>
+          <t>Waterville Prospect &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>311</v>
+        <v>1413</v>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
@@ -6085,12 +6089,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Au, Sb</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I78" t="b">
@@ -6101,15 +6105,11 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>1.9 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
+      <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="n">
         <v>0</v>
@@ -6118,23 +6118,23 @@
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T78" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U78" t="n">
         <v>35</v>
       </c>
       <c r="V78" t="n">
-        <v>45.06529</v>
+        <v>46.05921</v>
       </c>
       <c r="W78" t="n">
-        <v>-66.91136</v>
+        <v>-67.30663</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=311</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1413</t>
         </is>
       </c>
     </row>
@@ -6144,11 +6144,11 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Silver Island</t>
+          <t>Indian Brook</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>586</v>
+        <v>262</v>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
@@ -6157,11 +6157,7 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Ag, Pb, Zn</t>
-        </is>
-      </c>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -6197,14 +6193,14 @@
         <v>35</v>
       </c>
       <c r="V79" t="n">
-        <v>45.12114</v>
+        <v>46.73226</v>
       </c>
       <c r="W79" t="n">
-        <v>-66.8458</v>
+        <v>-67.42440999999999</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=586</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=262</t>
         </is>
       </c>
     </row>
@@ -6214,11 +6210,11 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Forty Five River &amp;quot;I&amp;quot;</t>
+          <t>Brummagen Brook Bog</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>647</v>
+        <v>188</v>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
@@ -6229,7 +6225,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -6258,23 +6254,23 @@
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T80" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U80" t="n">
         <v>35</v>
       </c>
       <c r="V80" t="n">
-        <v>45.74309</v>
+        <v>46.39003</v>
       </c>
       <c r="W80" t="n">
-        <v>-64.93053</v>
+        <v>-67.29386</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=647</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=188</t>
         </is>
       </c>
     </row>
@@ -6284,11 +6280,11 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Phyllis Creek &amp;quot;I&amp;quot;</t>
+          <t>Pecks Point South</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>655</v>
+        <v>1329</v>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
@@ -6299,7 +6295,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Ag, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -6337,14 +6333,14 @@
         <v>35</v>
       </c>
       <c r="V81" t="n">
-        <v>45.94808</v>
+        <v>45.73809</v>
       </c>
       <c r="W81" t="n">
-        <v>-66.69441</v>
+        <v>-64.48524</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=655</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1329</t>
         </is>
       </c>
     </row>
@@ -6354,11 +6350,11 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Pirate Lake</t>
+          <t>Dumfries *</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>516</v>
+        <v>535</v>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
@@ -6369,7 +6365,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -6407,14 +6403,14 @@
         <v>35</v>
       </c>
       <c r="V82" t="n">
-        <v>45.72697</v>
+        <v>45.95029</v>
       </c>
       <c r="W82" t="n">
-        <v>-67.67525000000001</v>
+        <v>-67.12273999999999</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=516</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=535</t>
         </is>
       </c>
     </row>
@@ -6424,11 +6420,11 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Pecks Point South</t>
+          <t>Pirate Lake</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1329</v>
+        <v>516</v>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
@@ -6439,7 +6435,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Ag, Cu, Pb, Zn</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -6477,14 +6473,14 @@
         <v>35</v>
       </c>
       <c r="V83" t="n">
-        <v>45.73809</v>
+        <v>45.72697</v>
       </c>
       <c r="W83" t="n">
-        <v>-64.48524</v>
+        <v>-67.67525000000001</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1329</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=516</t>
         </is>
       </c>
     </row>
@@ -6494,11 +6490,11 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>East Quoddy Head</t>
+          <t>Elmtree 7B</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>737</v>
+        <v>854</v>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
@@ -6509,7 +6505,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pb</t>
+          <t>Cu, Ni</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -6538,23 +6534,23 @@
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr"/>
       <c r="S84" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T84" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U84" t="n">
         <v>35</v>
       </c>
       <c r="V84" t="n">
-        <v>44.95391</v>
+        <v>47.78253</v>
       </c>
       <c r="W84" t="n">
-        <v>-66.90831</v>
+        <v>-65.87246</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=737</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=854</t>
         </is>
       </c>
     </row>
@@ -6564,11 +6560,11 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Meadow Brook Cove</t>
+          <t>Four Mile Lake B</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>727</v>
+        <v>1175</v>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
@@ -6577,11 +6573,7 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Fe, Zn</t>
-        </is>
-      </c>
+      <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -6617,14 +6609,14 @@
         <v>35</v>
       </c>
       <c r="V85" t="n">
-        <v>44.88281</v>
+        <v>46.63643</v>
       </c>
       <c r="W85" t="n">
-        <v>-66.90774999999999</v>
+        <v>-66.58274</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=727</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1175</t>
         </is>
       </c>
     </row>
@@ -6634,11 +6626,11 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Jacquet River K</t>
+          <t>Meadow Brook Cove</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>973</v>
+        <v>727</v>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
@@ -6647,7 +6639,11 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Fe, Zn</t>
+        </is>
+      </c>
       <c r="H86" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -6683,14 +6679,14 @@
         <v>35</v>
       </c>
       <c r="V86" t="n">
-        <v>47.83142</v>
+        <v>44.88281</v>
       </c>
       <c r="W86" t="n">
-        <v>-66.03246</v>
+        <v>-66.90774999999999</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=973</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=727</t>
         </is>
       </c>
     </row>
@@ -6700,11 +6696,11 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Little Southwest Miramichi</t>
+          <t>East Quoddy Head</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>621</v>
+        <v>737</v>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
@@ -6713,7 +6709,11 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Pb</t>
+        </is>
+      </c>
       <c r="H87" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -6749,14 +6749,14 @@
         <v>35</v>
       </c>
       <c r="V87" t="n">
-        <v>46.89643</v>
+        <v>44.95391</v>
       </c>
       <c r="W87" t="n">
-        <v>-66.34998</v>
+        <v>-66.90831</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=621</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=737</t>
         </is>
       </c>
     </row>
@@ -6766,11 +6766,11 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Waterside Manganese</t>
+          <t>Silver Island</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>645</v>
+        <v>586</v>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
@@ -6781,7 +6781,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Ag, Pb, Zn</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -6810,23 +6810,23 @@
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr"/>
       <c r="S88" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T88" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U88" t="n">
         <v>35</v>
       </c>
       <c r="V88" t="n">
-        <v>45.63058</v>
+        <v>45.12114</v>
       </c>
       <c r="W88" t="n">
-        <v>-64.82858</v>
+        <v>-66.8458</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=645</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=586</t>
         </is>
       </c>
     </row>
@@ -6836,11 +6836,11 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Brewers Mills</t>
+          <t>Phyllis Creek &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>904</v>
+        <v>655</v>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>As, Au</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6889,14 +6889,14 @@
         <v>35</v>
       </c>
       <c r="V89" t="n">
-        <v>46.0692</v>
+        <v>45.94808</v>
       </c>
       <c r="W89" t="n">
-        <v>-67.0283</v>
+        <v>-66.69441</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=904</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=655</t>
         </is>
       </c>
     </row>
@@ -6906,11 +6906,11 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Elmtree 7B</t>
+          <t>Jacquet River Cu - Mitchell Rd</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>854</v>
+        <v>461</v>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr"/>
@@ -6919,11 +6919,7 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Cu, Ni</t>
-        </is>
-      </c>
+      <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -6950,23 +6946,23 @@
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr"/>
       <c r="S90" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T90" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U90" t="n">
         <v>35</v>
       </c>
       <c r="V90" t="n">
-        <v>47.78253</v>
+        <v>47.82725</v>
       </c>
       <c r="W90" t="n">
-        <v>-65.87246</v>
+        <v>-66.00606999999999</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=854</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=461</t>
         </is>
       </c>
     </row>
@@ -6976,11 +6972,11 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>MacIntosh Brook</t>
+          <t>Maple Ridge</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>192</v>
+        <v>152</v>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
@@ -6991,7 +6987,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Mo, W</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -7020,23 +7016,23 @@
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr"/>
       <c r="S91" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T91" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U91" t="n">
         <v>35</v>
       </c>
       <c r="V91" t="n">
-        <v>46.35335</v>
+        <v>46.10003</v>
       </c>
       <c r="W91" t="n">
-        <v>-67.27636</v>
+        <v>-67.21413</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=192</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=152</t>
         </is>
       </c>
     </row>
@@ -7046,11 +7042,11 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Maple Ridge</t>
+          <t>MacIntosh Brook</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>152</v>
+        <v>192</v>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr"/>
@@ -7061,7 +7057,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Mo, W</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -7090,23 +7086,23 @@
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr"/>
       <c r="S92" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T92" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U92" t="n">
         <v>35</v>
       </c>
       <c r="V92" t="n">
-        <v>46.10003</v>
+        <v>46.35335</v>
       </c>
       <c r="W92" t="n">
-        <v>-67.21413</v>
+        <v>-67.27636</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=152</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=192</t>
         </is>
       </c>
     </row>
@@ -7116,11 +7112,11 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Indian Brook</t>
+          <t>Letete Mine</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>262</v>
+        <v>311</v>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
@@ -7129,10 +7125,14 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I93" t="b">
@@ -7143,11 +7143,15 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>1.9 Mt</t>
         </is>
       </c>
       <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="n">
         <v>0</v>
@@ -7156,23 +7160,23 @@
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr"/>
       <c r="S93" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T93" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U93" t="n">
         <v>35</v>
       </c>
       <c r="V93" t="n">
-        <v>46.73226</v>
+        <v>45.06529</v>
       </c>
       <c r="W93" t="n">
-        <v>-67.42440999999999</v>
+        <v>-66.91136</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=262</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=311</t>
         </is>
       </c>
     </row>
@@ -7182,11 +7186,11 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Centreville &amp;quot;I&amp;quot;</t>
+          <t>Forty Five River &amp;quot;I&amp;quot;</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>263</v>
+        <v>647</v>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
@@ -7197,7 +7201,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -7226,23 +7230,23 @@
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr"/>
       <c r="S94" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T94" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U94" t="n">
         <v>35</v>
       </c>
       <c r="V94" t="n">
-        <v>46.44281</v>
+        <v>45.74309</v>
       </c>
       <c r="W94" t="n">
-        <v>-67.6808</v>
+        <v>-64.93053</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=263</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=647</t>
         </is>
       </c>
     </row>
@@ -7252,11 +7256,11 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Brummagen Brook Bog</t>
+          <t>Waterside Manganese</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>188</v>
+        <v>645</v>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
@@ -7296,23 +7300,23 @@
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="inlineStr"/>
       <c r="S95" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T95" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U95" t="n">
         <v>35</v>
       </c>
       <c r="V95" t="n">
-        <v>46.39003</v>
+        <v>45.63058</v>
       </c>
       <c r="W95" t="n">
-        <v>-67.29386</v>
+        <v>-64.82858</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=188</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=645</t>
         </is>
       </c>
     </row>
@@ -7322,11 +7326,11 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Waterville Prospect &amp;quot;I&amp;quot;</t>
+          <t>Little Southwest Miramichi</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1413</v>
+        <v>621</v>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
@@ -7335,11 +7339,7 @@
           <t>Other metallic</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Au, Sb</t>
-        </is>
-      </c>
+      <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
           <t>Deposit</t>
@@ -7375,14 +7375,14 @@
         <v>35</v>
       </c>
       <c r="V96" t="n">
-        <v>46.05921</v>
+        <v>46.89643</v>
       </c>
       <c r="W96" t="n">
-        <v>-67.30663</v>
+        <v>-66.34998</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1413</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=621</t>
         </is>
       </c>
     </row>
@@ -7462,11 +7462,11 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Memramcook East</t>
+          <t>South Hamilton Road</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>320</v>
+        <v>1412</v>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
@@ -7477,7 +7477,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ba</t>
+          <t>Ag, Au, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -7506,23 +7506,23 @@
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr"/>
       <c r="S98" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T98" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U98" t="n">
         <v>30</v>
       </c>
       <c r="V98" t="n">
-        <v>46.01558</v>
+        <v>45.56892</v>
       </c>
       <c r="W98" t="n">
-        <v>-64.52218999999999</v>
+        <v>-66.16552</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=320</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1412</t>
         </is>
       </c>
     </row>
@@ -7532,11 +7532,11 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>South Hamilton Road</t>
+          <t>Memramcook East</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1412</v>
+        <v>320</v>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr"/>
@@ -7547,7 +7547,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Ag, Au, Cu, Pb, Zn</t>
+          <t>Ba</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -7576,23 +7576,23 @@
       <c r="Q99" t="inlineStr"/>
       <c r="R99" t="inlineStr"/>
       <c r="S99" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T99" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U99" t="n">
         <v>30</v>
       </c>
       <c r="V99" t="n">
-        <v>45.56892</v>
+        <v>46.01558</v>
       </c>
       <c r="W99" t="n">
-        <v>-66.16552</v>
+        <v>-64.52218999999999</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=1412</t>
+          <t>http://dnr-mrn.gnb.ca/MineralOccurrence/default.aspx?componentID=5&amp;urn=320</t>
         </is>
       </c>
     </row>
